--- a/DecompositionLU/docs/old_versions_statistics.xlsx
+++ b/DecompositionLU/docs/old_versions_statistics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38446831-696D-48D3-81BF-B42E86B87FF7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3B3464-4063-4D09-A0A0-01E212975C0A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Таблица" sheetId="1" r:id="rId1"/>
@@ -908,13 +908,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -923,13 +926,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -944,35 +947,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -995,8 +977,26 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -15494,17 +15494,17 @@
       <c r="N3" s="6"/>
     </row>
     <row r="5" spans="1:23" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="60" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="67"/>
-      <c r="G5" s="61" t="s">
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="62"/>
+      <c r="G5" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="61"/>
+      <c r="H5" s="67"/>
       <c r="S5" s="5"/>
       <c r="T5" s="14"/>
       <c r="U5" s="14"/>
@@ -15515,14 +15515,14 @@
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
       <c r="S6" s="14"/>
       <c r="T6" s="14"/>
       <c r="U6" s="14"/>
@@ -15545,8 +15545,8 @@
       <c r="E7" s="8">
         <v>10000</v>
       </c>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
       <c r="S7" s="14"/>
       <c r="T7" s="14"/>
       <c r="U7" s="14"/>
@@ -15554,15 +15554,15 @@
       <c r="W7" s="14"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
@@ -15638,13 +15638,13 @@
       <c r="W11" s="5"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A12" s="64" t="s">
+      <c r="A12" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
       <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
@@ -15657,7 +15657,7 @@
       <c r="C13" s="10">
         <v>232</v>
       </c>
-      <c r="D13" s="68" t="s">
+      <c r="D13" s="69" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="10">
@@ -15675,7 +15675,7 @@
       <c r="C14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="69"/>
+      <c r="D14" s="70"/>
       <c r="E14" s="10" t="s">
         <v>10</v>
       </c>
@@ -15693,30 +15693,30 @@
       <c r="C15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="70"/>
+      <c r="D15" s="71"/>
       <c r="E15" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="71" t="s">
+      <c r="A18" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="71"/>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="63" t="s">
+      <c r="B19" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
@@ -15736,13 +15736,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="64" t="s">
+      <c r="A21" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="64"/>
-      <c r="C21" s="64"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
@@ -15795,17 +15795,17 @@
         <v>35</v>
       </c>
       <c r="G24" s="18"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="60"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="66"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="64" t="s">
+      <c r="A25" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="64"/>
-      <c r="C25" s="64"/>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
       <c r="G25" s="19"/>
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
@@ -15890,15 +15890,15 @@
       <c r="I30" s="18"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="65" t="s">
+      <c r="A31" s="60" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="66"/>
-      <c r="C31" s="67"/>
-      <c r="D31" s="72" t="s">
+      <c r="B31" s="61"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="63" t="s">
         <v>91</v>
       </c>
-      <c r="E31" s="72" t="s">
+      <c r="E31" s="63" t="s">
         <v>91</v>
       </c>
       <c r="G31" s="20"/>
@@ -15909,12 +15909,12 @@
       <c r="A32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="63" t="s">
+      <c r="B32" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="63"/>
-      <c r="D32" s="63"/>
-      <c r="E32" s="63"/>
+      <c r="C32" s="64"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="64"/>
       <c r="G32" s="23"/>
       <c r="H32" s="18"/>
       <c r="I32" s="18"/>
@@ -15940,13 +15940,13 @@
       <c r="I33" s="18"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="64" t="s">
+      <c r="A34" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="64"/>
-      <c r="C34" s="64"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
+      <c r="B34" s="65"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="65"/>
       <c r="G34" s="23"/>
       <c r="H34" s="18"/>
       <c r="I34" s="18"/>
@@ -16012,13 +16012,13 @@
       <c r="I37" s="18"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="64" t="s">
+      <c r="A38" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="64"/>
-      <c r="C38" s="64"/>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
+      <c r="B38" s="65"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
       <c r="G38" s="23"/>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
@@ -16084,23 +16084,23 @@
       <c r="I41" s="18"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="62" t="s">
+      <c r="B42" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="62"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="62"/>
+      <c r="C42" s="68"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="68"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="65" t="s">
+      <c r="A44" s="60" t="s">
         <v>82</v>
       </c>
-      <c r="B44" s="66"/>
-      <c r="C44" s="67"/>
-      <c r="D44" s="72" t="s">
+      <c r="B44" s="61"/>
+      <c r="C44" s="62"/>
+      <c r="D44" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="E44" s="72" t="s">
+      <c r="E44" s="63" t="s">
         <v>91</v>
       </c>
     </row>
@@ -16108,12 +16108,12 @@
       <c r="A45" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B45" s="63" t="s">
+      <c r="B45" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="C45" s="63"/>
-      <c r="D45" s="63"/>
-      <c r="E45" s="63"/>
+      <c r="C45" s="64"/>
+      <c r="D45" s="64"/>
+      <c r="E45" s="64"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
@@ -16133,13 +16133,13 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="64" t="s">
+      <c r="A47" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B47" s="64"/>
-      <c r="C47" s="64"/>
-      <c r="D47" s="64"/>
-      <c r="E47" s="64"/>
+      <c r="B47" s="65"/>
+      <c r="C47" s="65"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="65"/>
       <c r="G47" s="1" t="s">
         <v>95</v>
       </c>
@@ -16217,13 +16217,13 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="64" t="s">
+      <c r="A51" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B51" s="64"/>
-      <c r="C51" s="64"/>
-      <c r="D51" s="64"/>
-      <c r="E51" s="64"/>
+      <c r="B51" s="65"/>
+      <c r="C51" s="65"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="65"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
@@ -16282,15 +16282,15 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="65" t="s">
+      <c r="A57" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="B57" s="66"/>
-      <c r="C57" s="67"/>
-      <c r="D57" s="72" t="s">
+      <c r="B57" s="61"/>
+      <c r="C57" s="62"/>
+      <c r="D57" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="E57" s="72" t="s">
+      <c r="E57" s="63" t="s">
         <v>91</v>
       </c>
     </row>
@@ -16298,12 +16298,12 @@
       <c r="A58" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B58" s="63" t="s">
+      <c r="B58" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="63"/>
-      <c r="D58" s="63"/>
-      <c r="E58" s="63"/>
+      <c r="C58" s="64"/>
+      <c r="D58" s="64"/>
+      <c r="E58" s="64"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
@@ -16323,13 +16323,13 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="64" t="s">
+      <c r="A60" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="64"/>
-      <c r="C60" s="64"/>
-      <c r="D60" s="64"/>
-      <c r="E60" s="64"/>
+      <c r="B60" s="65"/>
+      <c r="C60" s="65"/>
+      <c r="D60" s="65"/>
+      <c r="E60" s="65"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
@@ -16383,13 +16383,13 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="64" t="s">
+      <c r="A64" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B64" s="64"/>
-      <c r="C64" s="64"/>
-      <c r="D64" s="64"/>
-      <c r="E64" s="64"/>
+      <c r="B64" s="65"/>
+      <c r="C64" s="65"/>
+      <c r="D64" s="65"/>
+      <c r="E64" s="65"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
@@ -16449,18 +16449,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A31:C31"/>
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="G5:H8"/>
     <mergeCell ref="B42:E42"/>
@@ -16476,6 +16464,18 @@
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A64:E64"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
@@ -16505,24 +16505,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="71"/>
-      <c r="M1" s="72" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="N1" s="72"/>
+      <c r="N1" s="63"/>
       <c r="O1" s="36"/>
       <c r="P1" s="35"/>
       <c r="Q1" s="35"/>
@@ -16537,14 +16537,14 @@
       <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="74" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="83" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="81"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="85"/>
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
@@ -16569,7 +16569,7 @@
       <c r="Z2" s="30"/>
     </row>
     <row r="3" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="75"/>
+      <c r="A3" s="74"/>
       <c r="B3" s="29" t="s">
         <v>77</v>
       </c>
@@ -16603,7 +16603,7 @@
       <c r="Z3" s="30"/>
     </row>
     <row r="4" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="75"/>
+      <c r="A4" s="74"/>
       <c r="B4" s="15">
         <v>1</v>
       </c>
@@ -16637,7 +16637,7 @@
       <c r="Z4" s="30"/>
     </row>
     <row r="5" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="75"/>
+      <c r="A5" s="74"/>
       <c r="B5" s="15">
         <v>2</v>
       </c>
@@ -16671,7 +16671,7 @@
       <c r="Z5" s="30"/>
     </row>
     <row r="6" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="75"/>
+      <c r="A6" s="74"/>
       <c r="B6" s="15">
         <v>4</v>
       </c>
@@ -16694,7 +16694,7 @@
       <c r="O6" s="38"/>
     </row>
     <row r="7" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="75"/>
+      <c r="A7" s="74"/>
       <c r="B7" s="15">
         <v>6</v>
       </c>
@@ -16717,7 +16717,7 @@
       <c r="O7" s="38"/>
     </row>
     <row r="8" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="75"/>
+      <c r="A8" s="74"/>
       <c r="B8" s="15">
         <v>8</v>
       </c>
@@ -16740,7 +16740,7 @@
       <c r="O8" s="38"/>
     </row>
     <row r="9" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="75"/>
+      <c r="A9" s="74"/>
       <c r="B9" s="15">
         <v>10</v>
       </c>
@@ -16763,7 +16763,7 @@
       <c r="O9" s="38"/>
     </row>
     <row r="10" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="75"/>
+      <c r="A10" s="74"/>
       <c r="B10" s="15">
         <v>12</v>
       </c>
@@ -16786,7 +16786,7 @@
       <c r="O10" s="38"/>
     </row>
     <row r="11" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="75"/>
+      <c r="A11" s="74"/>
       <c r="B11" s="15">
         <v>16</v>
       </c>
@@ -16811,37 +16811,37 @@
       <c r="Q11" s="27"/>
     </row>
     <row r="12" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="75"/>
+      <c r="A12" s="74"/>
       <c r="B12" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="C12" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="73"/>
-      <c r="K12" s="73"/>
-      <c r="L12" s="73"/>
-      <c r="M12" s="73"/>
-      <c r="N12" s="74"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="75"/>
+      <c r="K12" s="75"/>
+      <c r="L12" s="75"/>
+      <c r="M12" s="75"/>
+      <c r="N12" s="86"/>
       <c r="O12" s="39"/>
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
     </row>
     <row r="13" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="74" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="79" t="s">
+      <c r="B13" s="83" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="80"/>
-      <c r="D13" s="81"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="85"/>
       <c r="E13" s="32"/>
       <c r="F13" s="31"/>
       <c r="G13" s="31"/>
@@ -16857,7 +16857,7 @@
       <c r="Q13" s="23"/>
     </row>
     <row r="14" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="75"/>
+      <c r="A14" s="74"/>
       <c r="B14" s="13" t="s">
         <v>77</v>
       </c>
@@ -16882,7 +16882,7 @@
       <c r="Q14" s="23"/>
     </row>
     <row r="15" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="75"/>
+      <c r="A15" s="74"/>
       <c r="B15" s="15">
         <v>1</v>
       </c>
@@ -16907,7 +16907,7 @@
       <c r="Q15" s="27"/>
     </row>
     <row r="16" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="75"/>
+      <c r="A16" s="74"/>
       <c r="B16" s="15">
         <v>2</v>
       </c>
@@ -16932,7 +16932,7 @@
       <c r="Q16" s="23"/>
     </row>
     <row r="17" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="75"/>
+      <c r="A17" s="74"/>
       <c r="B17" s="15">
         <v>4</v>
       </c>
@@ -16957,7 +16957,7 @@
       <c r="Q17" s="23"/>
     </row>
     <row r="18" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="75"/>
+      <c r="A18" s="74"/>
       <c r="B18" s="15">
         <v>6</v>
       </c>
@@ -16982,7 +16982,7 @@
       <c r="Q18" s="23"/>
     </row>
     <row r="19" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="75"/>
+      <c r="A19" s="74"/>
       <c r="B19" s="15">
         <v>8</v>
       </c>
@@ -17005,7 +17005,7 @@
       <c r="O19" s="38"/>
     </row>
     <row r="20" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="75"/>
+      <c r="A20" s="74"/>
       <c r="B20" s="15">
         <v>10</v>
       </c>
@@ -17028,7 +17028,7 @@
       <c r="O20" s="38"/>
     </row>
     <row r="21" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="75"/>
+      <c r="A21" s="74"/>
       <c r="B21" s="15">
         <v>12</v>
       </c>
@@ -17051,73 +17051,73 @@
       <c r="O21" s="38"/>
     </row>
     <row r="22" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="75"/>
-      <c r="B22" s="76" t="s">
+      <c r="A22" s="74"/>
+      <c r="B22" s="87" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="77" t="s">
+      <c r="C22" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="77"/>
-      <c r="M22" s="77"/>
-      <c r="N22" s="78"/>
+      <c r="D22" s="88"/>
+      <c r="E22" s="88"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="88"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="88"/>
+      <c r="K22" s="88"/>
+      <c r="L22" s="88"/>
+      <c r="M22" s="88"/>
+      <c r="N22" s="89"/>
       <c r="O22" s="38"/>
     </row>
     <row r="23" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="75"/>
-      <c r="B23" s="76"/>
-      <c r="C23" s="77"/>
-      <c r="D23" s="77"/>
-      <c r="E23" s="77"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="77"/>
-      <c r="K23" s="77"/>
-      <c r="L23" s="77"/>
-      <c r="M23" s="77"/>
-      <c r="N23" s="78"/>
+      <c r="A23" s="74"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="88"/>
+      <c r="K23" s="88"/>
+      <c r="L23" s="88"/>
+      <c r="M23" s="88"/>
+      <c r="N23" s="89"/>
       <c r="O23" s="38"/>
     </row>
     <row r="24" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="71" t="s">
+      <c r="A24" s="72" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="71"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="71"/>
-      <c r="K24" s="71"/>
-      <c r="L24" s="71"/>
-      <c r="M24" s="72" t="s">
+      <c r="B24" s="72"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="N24" s="72"/>
+      <c r="N24" s="63"/>
       <c r="O24" s="38"/>
     </row>
     <row r="25" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="83" t="s">
+      <c r="A25" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="79" t="s">
+      <c r="B25" s="83" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="80"/>
-      <c r="D25" s="81"/>
+      <c r="C25" s="84"/>
+      <c r="D25" s="85"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
       <c r="G25" s="31"/>
@@ -17131,7 +17131,7 @@
       <c r="O25" s="27"/>
     </row>
     <row r="26" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="84"/>
+      <c r="A26" s="78"/>
       <c r="B26" s="42" t="s">
         <v>77</v>
       </c>
@@ -17154,7 +17154,7 @@
       <c r="O26" s="27"/>
     </row>
     <row r="27" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="84"/>
+      <c r="A27" s="78"/>
       <c r="B27" s="15">
         <v>1</v>
       </c>
@@ -17177,7 +17177,7 @@
       <c r="O27" s="27"/>
     </row>
     <row r="28" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="84"/>
+      <c r="A28" s="78"/>
       <c r="B28" s="15">
         <v>2</v>
       </c>
@@ -17200,7 +17200,7 @@
       <c r="O28" s="27"/>
     </row>
     <row r="29" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="84"/>
+      <c r="A29" s="78"/>
       <c r="B29" s="15">
         <v>4</v>
       </c>
@@ -17223,7 +17223,7 @@
       <c r="O29" s="27"/>
     </row>
     <row r="30" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="84"/>
+      <c r="A30" s="78"/>
       <c r="B30" s="15">
         <v>6</v>
       </c>
@@ -17246,7 +17246,7 @@
       <c r="O30" s="27"/>
     </row>
     <row r="31" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="84"/>
+      <c r="A31" s="78"/>
       <c r="B31" s="15">
         <v>8</v>
       </c>
@@ -17269,7 +17269,7 @@
       <c r="O31" s="27"/>
     </row>
     <row r="32" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="84"/>
+      <c r="A32" s="78"/>
       <c r="B32" s="15">
         <v>10</v>
       </c>
@@ -17292,7 +17292,7 @@
       <c r="O32" s="27"/>
     </row>
     <row r="33" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="84"/>
+      <c r="A33" s="78"/>
       <c r="B33" s="15">
         <v>12</v>
       </c>
@@ -17315,7 +17315,7 @@
       <c r="O33" s="27"/>
     </row>
     <row r="34" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="84"/>
+      <c r="A34" s="78"/>
       <c r="B34" s="15">
         <v>16</v>
       </c>
@@ -17338,12 +17338,12 @@
       <c r="O34" s="27"/>
     </row>
     <row r="35" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="84"/>
-      <c r="B35" s="79" t="s">
+      <c r="A35" s="78"/>
+      <c r="B35" s="83" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="80"/>
-      <c r="D35" s="81"/>
+      <c r="C35" s="84"/>
+      <c r="D35" s="85"/>
       <c r="E35" s="31"/>
       <c r="F35" s="31"/>
       <c r="G35" s="31"/>
@@ -17357,7 +17357,7 @@
       <c r="O35" s="27"/>
     </row>
     <row r="36" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="84"/>
+      <c r="A36" s="78"/>
       <c r="B36" s="42" t="s">
         <v>77</v>
       </c>
@@ -17381,7 +17381,7 @@
       <c r="P36" s="1"/>
     </row>
     <row r="37" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="84"/>
+      <c r="A37" s="78"/>
       <c r="B37" s="42">
         <v>1</v>
       </c>
@@ -17407,7 +17407,7 @@
       <c r="P37" s="1"/>
     </row>
     <row r="38" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="84"/>
+      <c r="A38" s="78"/>
       <c r="B38" s="42">
         <v>2</v>
       </c>
@@ -17433,7 +17433,7 @@
       <c r="P38" s="1"/>
     </row>
     <row r="39" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="84"/>
+      <c r="A39" s="78"/>
       <c r="B39" s="42">
         <v>4</v>
       </c>
@@ -17459,7 +17459,7 @@
       <c r="P39" s="1"/>
     </row>
     <row r="40" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="84"/>
+      <c r="A40" s="78"/>
       <c r="B40" s="42">
         <v>6</v>
       </c>
@@ -17485,7 +17485,7 @@
       <c r="P40" s="1"/>
     </row>
     <row r="41" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="84"/>
+      <c r="A41" s="78"/>
       <c r="B41" s="42">
         <v>8</v>
       </c>
@@ -17511,7 +17511,7 @@
       <c r="P41" s="1"/>
     </row>
     <row r="42" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="84"/>
+      <c r="A42" s="78"/>
       <c r="B42" s="42">
         <v>10</v>
       </c>
@@ -17537,7 +17537,7 @@
       <c r="P42" s="1"/>
     </row>
     <row r="43" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="84"/>
+      <c r="A43" s="78"/>
       <c r="B43" s="42">
         <v>12</v>
       </c>
@@ -17563,7 +17563,7 @@
       <c r="P43" s="1"/>
     </row>
     <row r="44" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="84"/>
+      <c r="A44" s="78"/>
       <c r="B44" s="42">
         <v>16</v>
       </c>
@@ -17589,12 +17589,12 @@
       <c r="P44" s="1"/>
     </row>
     <row r="45" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="84"/>
-      <c r="B45" s="79" t="s">
+      <c r="A45" s="78"/>
+      <c r="B45" s="83" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="80"/>
-      <c r="D45" s="81"/>
+      <c r="C45" s="84"/>
+      <c r="D45" s="85"/>
       <c r="E45" s="43"/>
       <c r="F45" s="43"/>
       <c r="G45" s="43"/>
@@ -17609,7 +17609,7 @@
       <c r="P45" s="1"/>
     </row>
     <row r="46" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="84"/>
+      <c r="A46" s="78"/>
       <c r="B46" s="42" t="s">
         <v>77</v>
       </c>
@@ -17633,7 +17633,7 @@
       <c r="P46" s="1"/>
     </row>
     <row r="47" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="84"/>
+      <c r="A47" s="78"/>
       <c r="B47" s="42">
         <v>1</v>
       </c>
@@ -17659,7 +17659,7 @@
       <c r="P47" s="1"/>
     </row>
     <row r="48" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="84"/>
+      <c r="A48" s="78"/>
       <c r="B48" s="42">
         <v>2</v>
       </c>
@@ -17685,7 +17685,7 @@
       <c r="P48" s="1"/>
     </row>
     <row r="49" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="84"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="42">
         <v>4</v>
       </c>
@@ -17711,7 +17711,7 @@
       <c r="P49" s="1"/>
     </row>
     <row r="50" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="84"/>
+      <c r="A50" s="78"/>
       <c r="B50" s="42">
         <v>6</v>
       </c>
@@ -17737,7 +17737,7 @@
       <c r="P50" s="1"/>
     </row>
     <row r="51" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="84"/>
+      <c r="A51" s="78"/>
       <c r="B51" s="42">
         <v>8</v>
       </c>
@@ -17762,7 +17762,7 @@
       <c r="O51" s="1"/>
     </row>
     <row r="52" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="84"/>
+      <c r="A52" s="78"/>
       <c r="B52" s="42">
         <v>10</v>
       </c>
@@ -17787,7 +17787,7 @@
       <c r="O52" s="1"/>
     </row>
     <row r="53" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="84"/>
+      <c r="A53" s="78"/>
       <c r="B53" s="42">
         <v>12</v>
       </c>
@@ -17812,7 +17812,7 @@
       <c r="O53" s="1"/>
     </row>
     <row r="54" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="84"/>
+      <c r="A54" s="78"/>
       <c r="B54" s="42">
         <v>16</v>
       </c>
@@ -17837,55 +17837,55 @@
       <c r="O54" s="1"/>
     </row>
     <row r="55" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="84"/>
+      <c r="A55" s="78"/>
       <c r="B55" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C55" s="82" t="s">
+      <c r="C55" s="76" t="s">
         <v>102</v>
       </c>
-      <c r="D55" s="82"/>
-      <c r="E55" s="82"/>
-      <c r="F55" s="82"/>
-      <c r="G55" s="82"/>
-      <c r="H55" s="82"/>
-      <c r="I55" s="82"/>
-      <c r="J55" s="82"/>
-      <c r="K55" s="82"/>
-      <c r="L55" s="82"/>
-      <c r="M55" s="82"/>
-      <c r="N55" s="82"/>
+      <c r="D55" s="76"/>
+      <c r="E55" s="76"/>
+      <c r="F55" s="76"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="76"/>
+      <c r="I55" s="76"/>
+      <c r="J55" s="76"/>
+      <c r="K55" s="76"/>
+      <c r="L55" s="76"/>
+      <c r="M55" s="76"/>
+      <c r="N55" s="76"/>
     </row>
     <row r="56" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="85" t="s">
+      <c r="A56" s="79" t="s">
         <v>103</v>
       </c>
-      <c r="B56" s="86"/>
-      <c r="C56" s="86"/>
-      <c r="D56" s="86"/>
-      <c r="E56" s="86"/>
-      <c r="F56" s="86"/>
-      <c r="G56" s="86"/>
-      <c r="H56" s="86"/>
-      <c r="I56" s="86"/>
-      <c r="J56" s="86"/>
-      <c r="K56" s="86"/>
-      <c r="L56" s="87"/>
-      <c r="M56" s="72" t="s">
+      <c r="B56" s="80"/>
+      <c r="C56" s="80"/>
+      <c r="D56" s="80"/>
+      <c r="E56" s="80"/>
+      <c r="F56" s="80"/>
+      <c r="G56" s="80"/>
+      <c r="H56" s="80"/>
+      <c r="I56" s="80"/>
+      <c r="J56" s="80"/>
+      <c r="K56" s="80"/>
+      <c r="L56" s="81"/>
+      <c r="M56" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="N56" s="72"/>
+      <c r="N56" s="63"/>
       <c r="O56" s="30"/>
     </row>
     <row r="57" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="75" t="s">
+      <c r="A57" s="74" t="s">
         <v>85</v>
       </c>
-      <c r="B57" s="88" t="s">
+      <c r="B57" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="C57" s="88"/>
-      <c r="D57" s="88"/>
+      <c r="C57" s="82"/>
+      <c r="D57" s="82"/>
       <c r="E57" s="31"/>
       <c r="F57" s="31"/>
       <c r="G57" s="31"/>
@@ -17899,7 +17899,7 @@
       <c r="O57" s="30"/>
     </row>
     <row r="58" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="75"/>
+      <c r="A58" s="74"/>
       <c r="B58" s="42" t="s">
         <v>77</v>
       </c>
@@ -17922,7 +17922,7 @@
       <c r="O58" s="30"/>
     </row>
     <row r="59" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="75"/>
+      <c r="A59" s="74"/>
       <c r="B59" s="15">
         <v>1</v>
       </c>
@@ -17945,7 +17945,7 @@
       <c r="O59" s="30"/>
     </row>
     <row r="60" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="75"/>
+      <c r="A60" s="74"/>
       <c r="B60" s="15">
         <v>2</v>
       </c>
@@ -17968,7 +17968,7 @@
       <c r="O60" s="30"/>
     </row>
     <row r="61" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="75"/>
+      <c r="A61" s="74"/>
       <c r="B61" s="15">
         <v>4</v>
       </c>
@@ -17991,7 +17991,7 @@
       <c r="O61" s="30"/>
     </row>
     <row r="62" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="75"/>
+      <c r="A62" s="74"/>
       <c r="B62" s="15">
         <v>6</v>
       </c>
@@ -18014,7 +18014,7 @@
       <c r="O62" s="30"/>
     </row>
     <row r="63" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="75"/>
+      <c r="A63" s="74"/>
       <c r="B63" s="15">
         <v>8</v>
       </c>
@@ -18037,7 +18037,7 @@
       <c r="O63" s="30"/>
     </row>
     <row r="64" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="75"/>
+      <c r="A64" s="74"/>
       <c r="B64" s="15">
         <v>10</v>
       </c>
@@ -18060,7 +18060,7 @@
       <c r="O64" s="30"/>
     </row>
     <row r="65" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="75"/>
+      <c r="A65" s="74"/>
       <c r="B65" s="15">
         <v>12</v>
       </c>
@@ -18083,7 +18083,7 @@
       <c r="O65" s="30"/>
     </row>
     <row r="66" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="75"/>
+      <c r="A66" s="74"/>
       <c r="B66" s="15">
         <v>16</v>
       </c>
@@ -18106,12 +18106,12 @@
       <c r="O66" s="30"/>
     </row>
     <row r="67" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="75"/>
-      <c r="B67" s="88" t="s">
+      <c r="A67" s="74"/>
+      <c r="B67" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="C67" s="88"/>
-      <c r="D67" s="88"/>
+      <c r="C67" s="82"/>
+      <c r="D67" s="82"/>
       <c r="E67" s="31"/>
       <c r="F67" s="31"/>
       <c r="G67" s="31"/>
@@ -18125,7 +18125,7 @@
       <c r="O67" s="30"/>
     </row>
     <row r="68" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="75"/>
+      <c r="A68" s="74"/>
       <c r="B68" s="42" t="s">
         <v>77</v>
       </c>
@@ -18148,7 +18148,7 @@
       <c r="O68" s="30"/>
     </row>
     <row r="69" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="75"/>
+      <c r="A69" s="74"/>
       <c r="B69" s="42">
         <v>1</v>
       </c>
@@ -18173,7 +18173,7 @@
       <c r="O69" s="30"/>
     </row>
     <row r="70" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="75"/>
+      <c r="A70" s="74"/>
       <c r="B70" s="42">
         <v>2</v>
       </c>
@@ -18198,7 +18198,7 @@
       <c r="O70" s="30"/>
     </row>
     <row r="71" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="75"/>
+      <c r="A71" s="74"/>
       <c r="B71" s="42">
         <v>4</v>
       </c>
@@ -18223,7 +18223,7 @@
       <c r="O71" s="30"/>
     </row>
     <row r="72" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="75"/>
+      <c r="A72" s="74"/>
       <c r="B72" s="42">
         <v>6</v>
       </c>
@@ -18248,7 +18248,7 @@
       <c r="O72" s="30"/>
     </row>
     <row r="73" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="75"/>
+      <c r="A73" s="74"/>
       <c r="B73" s="42">
         <v>8</v>
       </c>
@@ -18273,7 +18273,7 @@
       <c r="O73" s="30"/>
     </row>
     <row r="74" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="75"/>
+      <c r="A74" s="74"/>
       <c r="B74" s="42">
         <v>10</v>
       </c>
@@ -18298,7 +18298,7 @@
       <c r="O74" s="30"/>
     </row>
     <row r="75" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="75"/>
+      <c r="A75" s="74"/>
       <c r="B75" s="42">
         <v>12</v>
       </c>
@@ -18323,7 +18323,7 @@
       <c r="O75" s="30"/>
     </row>
     <row r="76" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="75"/>
+      <c r="A76" s="74"/>
       <c r="B76" s="42">
         <v>16</v>
       </c>
@@ -18348,12 +18348,12 @@
       <c r="O76" s="30"/>
     </row>
     <row r="77" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="75"/>
-      <c r="B77" s="88" t="s">
+      <c r="A77" s="74"/>
+      <c r="B77" s="82" t="s">
         <v>97</v>
       </c>
-      <c r="C77" s="88"/>
-      <c r="D77" s="88"/>
+      <c r="C77" s="82"/>
+      <c r="D77" s="82"/>
       <c r="E77" s="43"/>
       <c r="F77" s="43"/>
       <c r="G77" s="43"/>
@@ -18367,7 +18367,7 @@
       <c r="O77" s="30"/>
     </row>
     <row r="78" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="75"/>
+      <c r="A78" s="74"/>
       <c r="B78" s="42" t="s">
         <v>77</v>
       </c>
@@ -18390,7 +18390,7 @@
       <c r="O78" s="30"/>
     </row>
     <row r="79" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="75"/>
+      <c r="A79" s="74"/>
       <c r="B79" s="42">
         <v>1</v>
       </c>
@@ -18415,7 +18415,7 @@
       <c r="O79" s="30"/>
     </row>
     <row r="80" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="75"/>
+      <c r="A80" s="74"/>
       <c r="B80" s="42">
         <v>2</v>
       </c>
@@ -18440,7 +18440,7 @@
       <c r="O80" s="30"/>
     </row>
     <row r="81" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="75"/>
+      <c r="A81" s="74"/>
       <c r="B81" s="42">
         <v>4</v>
       </c>
@@ -18465,7 +18465,7 @@
       <c r="O81" s="30"/>
     </row>
     <row r="82" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="75"/>
+      <c r="A82" s="74"/>
       <c r="B82" s="42">
         <v>6</v>
       </c>
@@ -18490,7 +18490,7 @@
       <c r="O82" s="30"/>
     </row>
     <row r="83" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="75"/>
+      <c r="A83" s="74"/>
       <c r="B83" s="42">
         <v>8</v>
       </c>
@@ -18515,7 +18515,7 @@
       <c r="O83" s="30"/>
     </row>
     <row r="84" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="75"/>
+      <c r="A84" s="74"/>
       <c r="B84" s="42">
         <v>10</v>
       </c>
@@ -18540,7 +18540,7 @@
       <c r="O84" s="30"/>
     </row>
     <row r="85" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="75"/>
+      <c r="A85" s="74"/>
       <c r="B85" s="42">
         <v>12</v>
       </c>
@@ -18565,7 +18565,7 @@
       <c r="O85" s="30"/>
     </row>
     <row r="86" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="75"/>
+      <c r="A86" s="74"/>
       <c r="B86" s="42">
         <v>16</v>
       </c>
@@ -18590,24 +18590,24 @@
       <c r="O86" s="30"/>
     </row>
     <row r="87" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="75"/>
+      <c r="A87" s="74"/>
       <c r="B87" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="73" t="s">
+      <c r="C87" s="75" t="s">
         <v>106</v>
       </c>
-      <c r="D87" s="73"/>
-      <c r="E87" s="73"/>
-      <c r="F87" s="73"/>
-      <c r="G87" s="73"/>
-      <c r="H87" s="73"/>
-      <c r="I87" s="73"/>
-      <c r="J87" s="73"/>
-      <c r="K87" s="73"/>
-      <c r="L87" s="73"/>
-      <c r="M87" s="73"/>
-      <c r="N87" s="73"/>
+      <c r="D87" s="75"/>
+      <c r="E87" s="75"/>
+      <c r="F87" s="75"/>
+      <c r="G87" s="75"/>
+      <c r="H87" s="75"/>
+      <c r="I87" s="75"/>
+      <c r="J87" s="75"/>
+      <c r="K87" s="75"/>
+      <c r="L87" s="75"/>
+      <c r="M87" s="75"/>
+      <c r="N87" s="75"/>
     </row>
     <row r="88" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="50"/>
@@ -21867,21 +21867,32 @@
     <row r="193" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="47"/>
       <c r="B193" s="30"/>
-      <c r="C193" s="89"/>
-      <c r="D193" s="89"/>
-      <c r="E193" s="89"/>
-      <c r="F193" s="89"/>
-      <c r="G193" s="89"/>
-      <c r="H193" s="89"/>
-      <c r="I193" s="89"/>
-      <c r="J193" s="89"/>
-      <c r="K193" s="89"/>
-      <c r="L193" s="89"/>
-      <c r="M193" s="89"/>
-      <c r="N193" s="89"/>
+      <c r="C193" s="73"/>
+      <c r="D193" s="73"/>
+      <c r="E193" s="73"/>
+      <c r="F193" s="73"/>
+      <c r="G193" s="73"/>
+      <c r="H193" s="73"/>
+      <c r="I193" s="73"/>
+      <c r="J193" s="73"/>
+      <c r="K193" s="73"/>
+      <c r="L193" s="73"/>
+      <c r="M193" s="73"/>
+      <c r="N193" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C12:N12"/>
+    <mergeCell ref="A2:A12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:N23"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="C193:N193"/>
     <mergeCell ref="A57:A87"/>
     <mergeCell ref="C87:N87"/>
@@ -21895,17 +21906,6 @@
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B25:D25"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C12:N12"/>
-    <mergeCell ref="A2:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:N23"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B2:D2"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>

--- a/DecompositionLU/docs/old_versions_statistics.xlsx
+++ b/DecompositionLU/docs/old_versions_statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3B3464-4063-4D09-A0A0-01E212975C0A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BECA629-CC58-4395-817A-223D54190969}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -801,7 +801,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -908,6 +907,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -15506,10 +15506,10 @@
       </c>
       <c r="H5" s="67"/>
       <c r="S5" s="5"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14"/>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -15523,11 +15523,11 @@
       <c r="E6" s="64"/>
       <c r="G6" s="67"/>
       <c r="H6" s="67"/>
-      <c r="S6" s="14"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="14"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
@@ -15547,11 +15547,11 @@
       </c>
       <c r="G7" s="67"/>
       <c r="H7" s="67"/>
-      <c r="S7" s="14"/>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14"/>
-      <c r="V7" s="14"/>
-      <c r="W7" s="14"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="65" t="s">
@@ -15563,11 +15563,11 @@
       <c r="E8" s="65"/>
       <c r="G8" s="67"/>
       <c r="H8" s="67"/>
-      <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
-      <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -15585,11 +15585,11 @@
       <c r="E9" s="10">
         <v>1746</v>
       </c>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="14"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="13"/>
+      <c r="V9" s="13"/>
+      <c r="W9" s="13"/>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
@@ -15794,7 +15794,7 @@
       <c r="E24" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G24" s="18"/>
+      <c r="G24" s="17"/>
       <c r="H24" s="66"/>
       <c r="I24" s="66"/>
     </row>
@@ -15806,9 +15806,9 @@
       <c r="C25" s="65"/>
       <c r="D25" s="65"/>
       <c r="E25" s="65"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
@@ -15826,9 +15826,9 @@
       <c r="E26" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G26" s="20"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="22"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="21"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
@@ -15846,9 +15846,9 @@
       <c r="E27" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="G27" s="20"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="18"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="17"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
@@ -15866,9 +15866,9 @@
       <c r="E28" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="G28" s="23"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C29" s="1" t="s">
@@ -15880,14 +15880,14 @@
       <c r="E29" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G29" s="20"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="18"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="17"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G30" s="23"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="60" t="s">
@@ -15901,9 +15901,9 @@
       <c r="E31" s="63" t="s">
         <v>91</v>
       </c>
-      <c r="G31" s="20"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="18"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="17"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -15915,9 +15915,9 @@
       <c r="C32" s="64"/>
       <c r="D32" s="64"/>
       <c r="E32" s="64"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
@@ -15935,9 +15935,9 @@
       <c r="E33" s="8">
         <v>10000</v>
       </c>
-      <c r="G33" s="20"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="18"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="17"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="65" t="s">
@@ -15947,9 +15947,9 @@
       <c r="C34" s="65"/>
       <c r="D34" s="65"/>
       <c r="E34" s="65"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
@@ -15967,9 +15967,9 @@
       <c r="E35" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G35" s="23"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
@@ -15987,9 +15987,9 @@
       <c r="E36" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="G36" s="23"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
@@ -16007,9 +16007,9 @@
       <c r="E37" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="G37" s="20"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="18"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="17"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="65" t="s">
@@ -16019,9 +16019,9 @@
       <c r="C38" s="65"/>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
@@ -16039,9 +16039,9 @@
       <c r="E39" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="G39" s="23"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="18"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
@@ -16059,9 +16059,9 @@
       <c r="E40" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="G40" s="23"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="18"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
@@ -16079,9 +16079,9 @@
       <c r="E41" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="G41" s="20"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="18"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="17"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B42" s="68" t="s">
@@ -16119,10 +16119,10 @@
       <c r="A46" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="28">
+      <c r="B46" s="27">
         <v>1000</v>
       </c>
-      <c r="C46" s="28">
+      <c r="C46" s="27">
         <v>3000</v>
       </c>
       <c r="D46" s="8">
@@ -16309,10 +16309,10 @@
       <c r="A59" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B59" s="45">
+      <c r="B59" s="44">
         <v>1000</v>
       </c>
-      <c r="C59" s="45">
+      <c r="C59" s="44">
         <v>3000</v>
       </c>
       <c r="D59" s="8">
@@ -16349,19 +16349,19 @@
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="48" t="s">
+      <c r="A62" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="B62" s="49">
+      <c r="B62" s="48">
         <v>58</v>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="48">
         <v>667</v>
       </c>
-      <c r="D62" s="49">
+      <c r="D62" s="48">
         <v>5417</v>
       </c>
-      <c r="E62" s="49">
+      <c r="E62" s="48">
         <v>14294</v>
       </c>
     </row>
@@ -16495,13 +16495,15 @@
   <dimension ref="A1:AC193"/>
   <sheetFormatPr defaultRowHeight="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="28" style="26" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" style="26" customWidth="1"/>
-    <col min="4" max="5" width="21.42578125" style="26" customWidth="1"/>
-    <col min="6" max="20" width="14.28515625" style="26" customWidth="1"/>
-    <col min="21" max="29" width="9.7109375" style="26" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="26"/>
+    <col min="1" max="1" width="15.28515625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="28" style="25" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" style="25" customWidth="1"/>
+    <col min="4" max="5" width="21.42578125" style="25" customWidth="1"/>
+    <col min="6" max="16" width="14.28515625" style="25" customWidth="1"/>
+    <col min="17" max="17" width="23.140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="14.28515625" style="25" customWidth="1"/>
+    <col min="21" max="29" width="9.7109375" style="25" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -16523,18 +16525,18 @@
         <v>90</v>
       </c>
       <c r="N1" s="63"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
     </row>
     <row r="2" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="74" t="s">
@@ -16545,274 +16547,274 @@
       </c>
       <c r="C2" s="84"/>
       <c r="D2" s="85"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
     </row>
     <row r="3" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="74"/>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="30"/>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="33"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="29"/>
+      <c r="X3" s="29"/>
+      <c r="Y3" s="29"/>
+      <c r="Z3" s="29"/>
     </row>
     <row r="4" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="74"/>
-      <c r="B4" s="15">
+      <c r="B4" s="14">
         <v>1</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="23">
         <v>40525</v>
       </c>
-      <c r="D4" s="40">
+      <c r="D4" s="39">
         <v>8737</v>
       </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="30"/>
-      <c r="Y4" s="30"/>
-      <c r="Z4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="29"/>
     </row>
     <row r="5" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="74"/>
-      <c r="B5" s="15">
+      <c r="B5" s="14">
         <v>2</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="23">
         <v>40933</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="39">
         <v>8116</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="31"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="30"/>
-      <c r="R5" s="30"/>
-      <c r="S5" s="30"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="30"/>
-      <c r="Y5" s="30"/>
-      <c r="Z5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29"/>
     </row>
     <row r="6" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="74"/>
-      <c r="B6" s="15">
+      <c r="B6" s="14">
         <v>4</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="23">
         <v>34657</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="39">
         <v>7387</v>
       </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="38"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="33"/>
+      <c r="O6" s="37"/>
     </row>
     <row r="7" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="74"/>
-      <c r="B7" s="15">
+      <c r="B7" s="14">
         <v>6</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="23">
         <v>38071</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="39">
         <v>7472</v>
       </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="38"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="37"/>
     </row>
     <row r="8" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="74"/>
-      <c r="B8" s="15">
+      <c r="B8" s="14">
         <v>8</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="23">
         <v>37594</v>
       </c>
-      <c r="D8" s="40">
+      <c r="D8" s="39">
         <v>7389</v>
       </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="38"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="37"/>
     </row>
     <row r="9" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="74"/>
-      <c r="B9" s="15">
+      <c r="B9" s="14">
         <v>10</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="23">
         <v>36931</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="39">
         <v>8155</v>
       </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="38"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="37"/>
     </row>
     <row r="10" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="74"/>
-      <c r="B10" s="15">
+      <c r="B10" s="14">
         <v>12</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="23">
         <v>40896</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="39">
         <v>8411</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="38"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="37"/>
     </row>
     <row r="11" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="74"/>
-      <c r="B11" s="15">
+      <c r="B11" s="14">
         <v>16</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="23">
         <v>39364</v>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="39">
         <v>7844</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="27"/>
-      <c r="Q11" s="27"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="37"/>
+      <c r="P11" s="26"/>
+      <c r="S11" s="59"/>
     </row>
     <row r="12" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="74"/>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="32" t="s">
         <v>86</v>
       </c>
       <c r="C12" s="75" t="s">
@@ -16829,9 +16831,8 @@
       <c r="L12" s="75"/>
       <c r="M12" s="75"/>
       <c r="N12" s="86"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
+      <c r="O12" s="38"/>
+      <c r="P12" s="22"/>
     </row>
     <row r="13" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="74" t="s">
@@ -16842,215 +16843,209 @@
       </c>
       <c r="C13" s="84"/>
       <c r="D13" s="85"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="38"/>
+      <c r="P13" s="22"/>
     </row>
     <row r="14" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="74"/>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="39"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="22"/>
     </row>
     <row r="15" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="74"/>
-      <c r="B15" s="15">
+      <c r="B15" s="14">
         <v>1</v>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="39">
         <v>21978</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="39">
         <v>4557</v>
       </c>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="38"/>
-      <c r="P15" s="27"/>
-      <c r="Q15" s="27"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="37"/>
+      <c r="P15" s="26"/>
     </row>
     <row r="16" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="74"/>
-      <c r="B16" s="15">
+      <c r="B16" s="14">
         <v>2</v>
       </c>
-      <c r="C16" s="40">
+      <c r="C16" s="39">
         <v>18990</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="39">
         <v>3948</v>
       </c>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="39"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-    </row>
-    <row r="17" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="22"/>
+    </row>
+    <row r="17" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="74"/>
-      <c r="B17" s="15">
+      <c r="B17" s="14">
         <v>4</v>
       </c>
-      <c r="C17" s="40">
+      <c r="C17" s="39">
         <v>18915</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="39">
         <v>3448</v>
       </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="39"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-    </row>
-    <row r="18" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="38"/>
+      <c r="P17" s="22"/>
+    </row>
+    <row r="18" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="74"/>
-      <c r="B18" s="15">
+      <c r="B18" s="14">
         <v>6</v>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="39">
         <v>19263</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="39">
         <v>3554</v>
       </c>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="31"/>
-      <c r="M18" s="31"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="39"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-    </row>
-    <row r="19" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="22"/>
+    </row>
+    <row r="19" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="74"/>
-      <c r="B19" s="15">
+      <c r="B19" s="14">
         <v>8</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="23">
         <v>19123</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="39">
         <v>3538</v>
       </c>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="38"/>
-    </row>
-    <row r="20" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="37"/>
+    </row>
+    <row r="20" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="74"/>
-      <c r="B20" s="15">
+      <c r="B20" s="14">
         <v>10</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="23">
         <v>19536</v>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="39">
         <v>3696</v>
       </c>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="38"/>
-    </row>
-    <row r="21" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="37"/>
+    </row>
+    <row r="21" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="74"/>
-      <c r="B21" s="15">
+      <c r="B21" s="14">
         <v>12</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="23">
         <v>20535</v>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="39">
         <v>4272</v>
       </c>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="31"/>
-      <c r="N21" s="34"/>
-      <c r="O21" s="38"/>
-    </row>
-    <row r="22" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="37"/>
+    </row>
+    <row r="22" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="74"/>
       <c r="B22" s="87" t="s">
         <v>86</v>
@@ -17069,9 +17064,9 @@
       <c r="L22" s="88"/>
       <c r="M22" s="88"/>
       <c r="N22" s="89"/>
-      <c r="O22" s="38"/>
-    </row>
-    <row r="23" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O22" s="37"/>
+    </row>
+    <row r="23" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="74"/>
       <c r="B23" s="87"/>
       <c r="C23" s="88"/>
@@ -17086,9 +17081,9 @@
       <c r="L23" s="88"/>
       <c r="M23" s="88"/>
       <c r="N23" s="89"/>
-      <c r="O23" s="38"/>
-    </row>
-    <row r="24" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O23" s="37"/>
+    </row>
+    <row r="24" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="72" t="s">
         <v>89</v>
       </c>
@@ -17107,9 +17102,9 @@
         <v>90</v>
       </c>
       <c r="N24" s="63"/>
-      <c r="O24" s="38"/>
-    </row>
-    <row r="25" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O24" s="37"/>
+    </row>
+    <row r="25" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="77" t="s">
         <v>85</v>
       </c>
@@ -17118,224 +17113,224 @@
       </c>
       <c r="C25" s="84"/>
       <c r="D25" s="85"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31"/>
-      <c r="O25" s="27"/>
-    </row>
-    <row r="26" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="26"/>
+    </row>
+    <row r="26" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="78"/>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C26" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="25" t="s">
+      <c r="D26" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="27"/>
-    </row>
-    <row r="27" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="26"/>
+    </row>
+    <row r="27" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="78"/>
-      <c r="B27" s="15">
+      <c r="B27" s="14">
         <v>1</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="23">
         <v>16385</v>
       </c>
-      <c r="D27" s="40">
+      <c r="D27" s="39">
         <v>3616</v>
       </c>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="31"/>
-      <c r="N27" s="31"/>
-      <c r="O27" s="27"/>
-    </row>
-    <row r="28" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="26"/>
+    </row>
+    <row r="28" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="78"/>
-      <c r="B28" s="15">
+      <c r="B28" s="14">
         <v>2</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="23">
         <v>8982</v>
       </c>
-      <c r="D28" s="40">
+      <c r="D28" s="39">
         <v>2066</v>
       </c>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="27"/>
-    </row>
-    <row r="29" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="26"/>
+    </row>
+    <row r="29" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="78"/>
-      <c r="B29" s="15">
+      <c r="B29" s="14">
         <v>4</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="23">
         <v>5710</v>
       </c>
-      <c r="D29" s="40">
+      <c r="D29" s="39">
         <v>1430</v>
       </c>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="27"/>
-    </row>
-    <row r="30" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="26"/>
+    </row>
+    <row r="30" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="78"/>
-      <c r="B30" s="15">
+      <c r="B30" s="14">
         <v>6</v>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="23">
         <v>4847</v>
       </c>
-      <c r="D30" s="40">
+      <c r="D30" s="39">
         <v>1212</v>
       </c>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="31"/>
-      <c r="N30" s="31"/>
-      <c r="O30" s="27"/>
-    </row>
-    <row r="31" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="26"/>
+    </row>
+    <row r="31" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="78"/>
-      <c r="B31" s="15">
+      <c r="B31" s="14">
         <v>8</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="23">
         <v>4224</v>
       </c>
-      <c r="D31" s="40">
+      <c r="D31" s="39">
         <v>1190</v>
       </c>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="31"/>
-      <c r="M31" s="31"/>
-      <c r="N31" s="31"/>
-      <c r="O31" s="27"/>
-    </row>
-    <row r="32" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="26"/>
+    </row>
+    <row r="32" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="78"/>
-      <c r="B32" s="15">
+      <c r="B32" s="14">
         <v>10</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="23">
         <v>4304</v>
       </c>
-      <c r="D32" s="40">
+      <c r="D32" s="39">
         <v>1280</v>
       </c>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="27"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="26"/>
     </row>
     <row r="33" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="78"/>
-      <c r="B33" s="15">
+      <c r="B33" s="14">
         <v>12</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="23">
         <v>4260</v>
       </c>
-      <c r="D33" s="40">
+      <c r="D33" s="39">
         <v>1360</v>
       </c>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="27"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="26"/>
     </row>
     <row r="34" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="78"/>
-      <c r="B34" s="15">
+      <c r="B34" s="14">
         <v>16</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="23">
         <v>4287</v>
       </c>
-      <c r="D34" s="40">
+      <c r="D34" s="39">
         <v>1368</v>
       </c>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="27"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="30"/>
+      <c r="O34" s="26"/>
     </row>
     <row r="35" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="78"/>
@@ -17344,247 +17339,247 @@
       </c>
       <c r="C35" s="84"/>
       <c r="D35" s="85"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="27"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="26"/>
     </row>
     <row r="36" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="78"/>
-      <c r="B36" s="42" t="s">
+      <c r="B36" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="C36" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="D36" s="25" t="s">
+      <c r="D36" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
     </row>
     <row r="37" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="78"/>
-      <c r="B37" s="42">
+      <c r="B37" s="41">
         <v>1</v>
       </c>
-      <c r="C37" s="40">
+      <c r="C37" s="39">
         <f>C27/C27</f>
         <v>1</v>
       </c>
-      <c r="D37" s="40">
+      <c r="D37" s="39">
         <f>D27/D27</f>
         <v>1</v>
       </c>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="16"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
     </row>
     <row r="38" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="78"/>
-      <c r="B38" s="42">
+      <c r="B38" s="41">
         <v>2</v>
       </c>
-      <c r="C38" s="40">
+      <c r="C38" s="39">
         <f>C27/C28</f>
         <v>1.8242039634825207</v>
       </c>
-      <c r="D38" s="40">
+      <c r="D38" s="39">
         <f>D27/D28</f>
         <v>1.750242013552759</v>
       </c>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
     </row>
     <row r="39" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="78"/>
-      <c r="B39" s="42">
+      <c r="B39" s="41">
         <v>4</v>
       </c>
-      <c r="C39" s="40">
+      <c r="C39" s="39">
         <f>C27/C29</f>
         <v>2.8695271453590192</v>
       </c>
-      <c r="D39" s="40">
+      <c r="D39" s="39">
         <f>D27/D29</f>
         <v>2.5286713286713285</v>
       </c>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="43"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
     </row>
     <row r="40" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="78"/>
-      <c r="B40" s="42">
+      <c r="B40" s="41">
         <v>6</v>
       </c>
-      <c r="C40" s="40">
+      <c r="C40" s="39">
         <f>C27/C30</f>
         <v>3.3804415102125027</v>
       </c>
-      <c r="D40" s="40">
+      <c r="D40" s="39">
         <f>D27/D30</f>
         <v>2.9834983498349836</v>
       </c>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="16"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
     </row>
     <row r="41" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="78"/>
-      <c r="B41" s="42">
+      <c r="B41" s="41">
         <v>8</v>
       </c>
-      <c r="C41" s="40">
+      <c r="C41" s="39">
         <f>C27/C31</f>
         <v>3.8790246212121211</v>
       </c>
-      <c r="D41" s="40">
+      <c r="D41" s="39">
         <f>D27/D31</f>
         <v>3.0386554621848738</v>
       </c>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="16"/>
-      <c r="J41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="16"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="15"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
     </row>
     <row r="42" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="78"/>
-      <c r="B42" s="42">
+      <c r="B42" s="41">
         <v>10</v>
       </c>
-      <c r="C42" s="40">
+      <c r="C42" s="39">
         <f>C27/C32</f>
         <v>3.8069237918215615</v>
       </c>
-      <c r="D42" s="40">
+      <c r="D42" s="39">
         <f>D27/D32</f>
         <v>2.8250000000000002</v>
       </c>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="16"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
+      <c r="M42" s="15"/>
+      <c r="N42" s="15"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
     </row>
     <row r="43" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="78"/>
-      <c r="B43" s="42">
+      <c r="B43" s="41">
         <v>12</v>
       </c>
-      <c r="C43" s="40">
+      <c r="C43" s="39">
         <f>C27/C33</f>
         <v>3.846244131455399</v>
       </c>
-      <c r="D43" s="40">
+      <c r="D43" s="39">
         <f>D27/D33</f>
         <v>2.6588235294117646</v>
       </c>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="16"/>
-      <c r="I43" s="16"/>
-      <c r="J43" s="16"/>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="16"/>
+      <c r="E43" s="42"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="42"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
+      <c r="L43" s="15"/>
+      <c r="M43" s="15"/>
+      <c r="N43" s="15"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
     </row>
     <row r="44" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="78"/>
-      <c r="B44" s="42">
+      <c r="B44" s="41">
         <v>16</v>
       </c>
-      <c r="C44" s="40">
+      <c r="C44" s="39">
         <f>C27/C34</f>
         <v>3.8220200606484722</v>
       </c>
-      <c r="D44" s="40">
+      <c r="D44" s="39">
         <f>D27/D34</f>
         <v>2.6432748538011697</v>
       </c>
-      <c r="E44" s="43"/>
-      <c r="F44" s="43"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="16"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="15"/>
+      <c r="N44" s="15"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
     </row>
@@ -17595,250 +17590,250 @@
       </c>
       <c r="C45" s="84"/>
       <c r="D45" s="85"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="16"/>
-      <c r="J45" s="16"/>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="16"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
+      <c r="M45" s="15"/>
+      <c r="N45" s="15"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
     </row>
     <row r="46" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="78"/>
-      <c r="B46" s="42" t="s">
+      <c r="B46" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C46" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="D46" s="25" t="s">
+      <c r="D46" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="16"/>
-      <c r="I46" s="16"/>
-      <c r="J46" s="16"/>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="16"/>
+      <c r="E46" s="42"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="42"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="15"/>
+      <c r="M46" s="15"/>
+      <c r="N46" s="15"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
     </row>
     <row r="47" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="78"/>
-      <c r="B47" s="42">
+      <c r="B47" s="41">
         <v>1</v>
       </c>
-      <c r="C47" s="40">
+      <c r="C47" s="39">
         <f t="shared" ref="C47:C54" si="0">C37/B37</f>
         <v>1</v>
       </c>
-      <c r="D47" s="40">
+      <c r="D47" s="39">
         <f t="shared" ref="D47:D54" si="1">D37/B37</f>
         <v>1</v>
       </c>
-      <c r="E47" s="43"/>
-      <c r="F47" s="43"/>
-      <c r="G47" s="43"/>
-      <c r="H47" s="16"/>
-      <c r="I47" s="16"/>
-      <c r="J47" s="16"/>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="16"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="15"/>
+      <c r="N47" s="15"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
     </row>
     <row r="48" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="78"/>
-      <c r="B48" s="42">
+      <c r="B48" s="41">
         <v>2</v>
       </c>
-      <c r="C48" s="40">
+      <c r="C48" s="39">
         <f t="shared" si="0"/>
         <v>0.91210198174126034</v>
       </c>
-      <c r="D48" s="40">
+      <c r="D48" s="39">
         <f t="shared" si="1"/>
         <v>0.8751210067763795</v>
       </c>
-      <c r="E48" s="43"/>
-      <c r="F48" s="43"/>
-      <c r="G48" s="43"/>
-      <c r="H48" s="16"/>
-      <c r="I48" s="16"/>
-      <c r="J48" s="16"/>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="16"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="42"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="15"/>
+      <c r="N48" s="15"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
     </row>
     <row r="49" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="78"/>
-      <c r="B49" s="42">
+      <c r="B49" s="41">
         <v>4</v>
       </c>
-      <c r="C49" s="40">
+      <c r="C49" s="39">
         <f t="shared" si="0"/>
         <v>0.7173817863397548</v>
       </c>
-      <c r="D49" s="40">
+      <c r="D49" s="39">
         <f t="shared" si="1"/>
         <v>0.63216783216783212</v>
       </c>
-      <c r="E49" s="43"/>
-      <c r="F49" s="43"/>
-      <c r="G49" s="43"/>
-      <c r="H49" s="16"/>
-      <c r="I49" s="16"/>
-      <c r="J49" s="16"/>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="16"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="15"/>
+      <c r="M49" s="15"/>
+      <c r="N49" s="15"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
     </row>
     <row r="50" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="78"/>
-      <c r="B50" s="42">
+      <c r="B50" s="41">
         <v>6</v>
       </c>
-      <c r="C50" s="40">
+      <c r="C50" s="39">
         <f t="shared" si="0"/>
         <v>0.56340691836875045</v>
       </c>
-      <c r="D50" s="40">
+      <c r="D50" s="39">
         <f t="shared" si="1"/>
         <v>0.49724972497249725</v>
       </c>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="16"/>
-      <c r="I50" s="16"/>
-      <c r="J50" s="16"/>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="16"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
+      <c r="K50" s="15"/>
+      <c r="L50" s="15"/>
+      <c r="M50" s="15"/>
+      <c r="N50" s="15"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
     </row>
     <row r="51" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="78"/>
-      <c r="B51" s="42">
+      <c r="B51" s="41">
         <v>8</v>
       </c>
-      <c r="C51" s="40">
+      <c r="C51" s="39">
         <f t="shared" si="0"/>
         <v>0.48487807765151514</v>
       </c>
-      <c r="D51" s="40">
+      <c r="D51" s="39">
         <f t="shared" si="1"/>
         <v>0.37983193277310923</v>
       </c>
-      <c r="E51" s="43"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="43"/>
-      <c r="H51" s="16"/>
-      <c r="I51" s="16"/>
-      <c r="J51" s="16"/>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="16"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="42"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15"/>
+      <c r="L51" s="15"/>
+      <c r="M51" s="15"/>
+      <c r="N51" s="15"/>
       <c r="O51" s="1"/>
     </row>
     <row r="52" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="78"/>
-      <c r="B52" s="42">
+      <c r="B52" s="41">
         <v>10</v>
       </c>
-      <c r="C52" s="40">
+      <c r="C52" s="39">
         <f t="shared" si="0"/>
         <v>0.38069237918215615</v>
       </c>
-      <c r="D52" s="40">
+      <c r="D52" s="39">
         <f t="shared" si="1"/>
         <v>0.28250000000000003</v>
       </c>
-      <c r="E52" s="43"/>
-      <c r="F52" s="43"/>
-      <c r="G52" s="43"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="16"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="16"/>
+      <c r="E52" s="42"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="42"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="15"/>
+      <c r="M52" s="15"/>
+      <c r="N52" s="15"/>
       <c r="O52" s="1"/>
     </row>
     <row r="53" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="78"/>
-      <c r="B53" s="42">
+      <c r="B53" s="41">
         <v>12</v>
       </c>
-      <c r="C53" s="40">
+      <c r="C53" s="39">
         <f t="shared" si="0"/>
         <v>0.3205203442879499</v>
       </c>
-      <c r="D53" s="40">
+      <c r="D53" s="39">
         <f t="shared" si="1"/>
         <v>0.22156862745098038</v>
       </c>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
-      <c r="M53" s="31"/>
-      <c r="N53" s="31"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="30"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="30"/>
+      <c r="M53" s="30"/>
+      <c r="N53" s="30"/>
       <c r="O53" s="1"/>
     </row>
     <row r="54" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="78"/>
-      <c r="B54" s="42">
+      <c r="B54" s="41">
         <v>16</v>
       </c>
-      <c r="C54" s="40">
+      <c r="C54" s="39">
         <f t="shared" si="0"/>
         <v>0.23887625379052951</v>
       </c>
-      <c r="D54" s="40">
+      <c r="D54" s="39">
         <f t="shared" si="1"/>
         <v>0.1652046783625731</v>
       </c>
-      <c r="E54" s="31"/>
-      <c r="F54" s="31"/>
-      <c r="G54" s="31"/>
-      <c r="H54" s="31"/>
-      <c r="I54" s="31"/>
-      <c r="J54" s="31"/>
-      <c r="K54" s="31"/>
-      <c r="L54" s="31"/>
-      <c r="M54" s="31"/>
-      <c r="N54" s="31"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="30"/>
+      <c r="N54" s="30"/>
       <c r="O54" s="1"/>
     </row>
     <row r="55" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="78"/>
-      <c r="B55" s="46" t="s">
+      <c r="B55" s="45" t="s">
         <v>86</v>
       </c>
       <c r="C55" s="76" t="s">
@@ -17875,7 +17870,7 @@
         <v>90</v>
       </c>
       <c r="N56" s="63"/>
-      <c r="O56" s="30"/>
+      <c r="O56" s="29"/>
     </row>
     <row r="57" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="74" t="s">
@@ -17886,224 +17881,224 @@
       </c>
       <c r="C57" s="82"/>
       <c r="D57" s="82"/>
-      <c r="E57" s="31"/>
-      <c r="F57" s="31"/>
-      <c r="G57" s="31"/>
-      <c r="H57" s="31"/>
-      <c r="I57" s="31"/>
-      <c r="J57" s="31"/>
-      <c r="K57" s="31"/>
-      <c r="L57" s="31"/>
-      <c r="M57" s="31"/>
-      <c r="N57" s="31"/>
-      <c r="O57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="30"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="30"/>
+      <c r="M57" s="30"/>
+      <c r="N57" s="30"/>
+      <c r="O57" s="29"/>
     </row>
     <row r="58" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="74"/>
-      <c r="B58" s="42" t="s">
+      <c r="B58" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="C58" s="25" t="s">
+      <c r="C58" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="D58" s="25" t="s">
+      <c r="D58" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E58" s="31"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="31"/>
-      <c r="H58" s="31"/>
-      <c r="I58" s="31"/>
-      <c r="J58" s="31"/>
-      <c r="K58" s="31"/>
-      <c r="L58" s="31"/>
-      <c r="M58" s="31"/>
-      <c r="N58" s="31"/>
-      <c r="O58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="29"/>
     </row>
     <row r="59" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="74"/>
-      <c r="B59" s="15">
+      <c r="B59" s="14">
         <v>1</v>
       </c>
-      <c r="C59" s="24">
+      <c r="C59" s="23">
         <v>5044</v>
       </c>
-      <c r="D59" s="40">
+      <c r="D59" s="39">
         <v>1126</v>
       </c>
-      <c r="E59" s="31"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="31"/>
-      <c r="H59" s="31"/>
-      <c r="I59" s="31"/>
-      <c r="J59" s="31"/>
-      <c r="K59" s="31"/>
-      <c r="L59" s="31"/>
-      <c r="M59" s="31"/>
-      <c r="N59" s="31"/>
-      <c r="O59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="30"/>
+      <c r="J59" s="30"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="30"/>
+      <c r="M59" s="30"/>
+      <c r="N59" s="30"/>
+      <c r="O59" s="29"/>
     </row>
     <row r="60" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="74"/>
-      <c r="B60" s="15">
+      <c r="B60" s="14">
         <v>2</v>
       </c>
-      <c r="C60" s="24">
+      <c r="C60" s="23">
         <v>3946</v>
       </c>
-      <c r="D60" s="40">
+      <c r="D60" s="39">
         <v>853</v>
       </c>
-      <c r="E60" s="31"/>
-      <c r="F60" s="31"/>
-      <c r="G60" s="31"/>
-      <c r="H60" s="31"/>
-      <c r="I60" s="31"/>
-      <c r="J60" s="31"/>
-      <c r="K60" s="31"/>
-      <c r="L60" s="31"/>
-      <c r="M60" s="31"/>
-      <c r="N60" s="31"/>
-      <c r="O60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
+      <c r="J60" s="30"/>
+      <c r="K60" s="30"/>
+      <c r="L60" s="30"/>
+      <c r="M60" s="30"/>
+      <c r="N60" s="30"/>
+      <c r="O60" s="29"/>
     </row>
     <row r="61" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="74"/>
-      <c r="B61" s="15">
+      <c r="B61" s="14">
         <v>4</v>
       </c>
-      <c r="C61" s="24">
+      <c r="C61" s="23">
         <v>2667</v>
       </c>
-      <c r="D61" s="40">
+      <c r="D61" s="39">
         <v>702</v>
       </c>
-      <c r="E61" s="31"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="31"/>
-      <c r="H61" s="31"/>
-      <c r="I61" s="31"/>
-      <c r="J61" s="31"/>
-      <c r="K61" s="31"/>
-      <c r="L61" s="31"/>
-      <c r="M61" s="31"/>
-      <c r="N61" s="31"/>
-      <c r="O61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="29"/>
     </row>
     <row r="62" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="74"/>
-      <c r="B62" s="15">
+      <c r="B62" s="14">
         <v>6</v>
       </c>
-      <c r="C62" s="24">
+      <c r="C62" s="23">
         <v>2931</v>
       </c>
-      <c r="D62" s="40">
+      <c r="D62" s="39">
         <v>832</v>
       </c>
-      <c r="E62" s="31"/>
-      <c r="F62" s="31"/>
-      <c r="G62" s="31"/>
-      <c r="H62" s="31"/>
-      <c r="I62" s="31"/>
-      <c r="J62" s="31"/>
-      <c r="K62" s="31"/>
-      <c r="L62" s="31"/>
-      <c r="M62" s="31"/>
-      <c r="N62" s="31"/>
-      <c r="O62" s="30"/>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="30"/>
+      <c r="H62" s="30"/>
+      <c r="I62" s="30"/>
+      <c r="J62" s="30"/>
+      <c r="K62" s="30"/>
+      <c r="L62" s="30"/>
+      <c r="M62" s="30"/>
+      <c r="N62" s="30"/>
+      <c r="O62" s="29"/>
     </row>
     <row r="63" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="74"/>
-      <c r="B63" s="15">
+      <c r="B63" s="14">
         <v>8</v>
       </c>
-      <c r="C63" s="24">
+      <c r="C63" s="23">
         <v>2774</v>
       </c>
-      <c r="D63" s="40">
+      <c r="D63" s="39">
         <v>816</v>
       </c>
-      <c r="E63" s="31"/>
-      <c r="F63" s="31"/>
-      <c r="G63" s="31"/>
-      <c r="H63" s="31"/>
-      <c r="I63" s="31"/>
-      <c r="J63" s="31"/>
-      <c r="K63" s="31"/>
-      <c r="L63" s="31"/>
-      <c r="M63" s="31"/>
-      <c r="N63" s="31"/>
-      <c r="O63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="30"/>
+      <c r="I63" s="30"/>
+      <c r="J63" s="30"/>
+      <c r="K63" s="30"/>
+      <c r="L63" s="30"/>
+      <c r="M63" s="30"/>
+      <c r="N63" s="30"/>
+      <c r="O63" s="29"/>
     </row>
     <row r="64" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="74"/>
-      <c r="B64" s="15">
+      <c r="B64" s="14">
         <v>10</v>
       </c>
-      <c r="C64" s="24">
+      <c r="C64" s="23">
         <v>2866</v>
       </c>
-      <c r="D64" s="40">
+      <c r="D64" s="39">
         <v>844</v>
       </c>
-      <c r="E64" s="31"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="31"/>
-      <c r="H64" s="31"/>
-      <c r="I64" s="31"/>
-      <c r="J64" s="31"/>
-      <c r="K64" s="31"/>
-      <c r="L64" s="31"/>
-      <c r="M64" s="31"/>
-      <c r="N64" s="31"/>
-      <c r="O64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="29"/>
     </row>
     <row r="65" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="74"/>
-      <c r="B65" s="15">
+      <c r="B65" s="14">
         <v>12</v>
       </c>
-      <c r="C65" s="24">
+      <c r="C65" s="23">
         <v>2773</v>
       </c>
-      <c r="D65" s="40">
+      <c r="D65" s="39">
         <v>882</v>
       </c>
-      <c r="E65" s="31"/>
-      <c r="F65" s="31"/>
-      <c r="G65" s="31"/>
-      <c r="H65" s="31"/>
-      <c r="I65" s="31"/>
-      <c r="J65" s="31"/>
-      <c r="K65" s="31"/>
-      <c r="L65" s="31"/>
-      <c r="M65" s="31"/>
-      <c r="N65" s="31"/>
-      <c r="O65" s="30"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="30"/>
+      <c r="G65" s="30"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="30"/>
+      <c r="K65" s="30"/>
+      <c r="L65" s="30"/>
+      <c r="M65" s="30"/>
+      <c r="N65" s="30"/>
+      <c r="O65" s="29"/>
     </row>
     <row r="66" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="74"/>
-      <c r="B66" s="15">
+      <c r="B66" s="14">
         <v>16</v>
       </c>
-      <c r="C66" s="24">
+      <c r="C66" s="23">
         <v>2706</v>
       </c>
-      <c r="D66" s="40">
+      <c r="D66" s="39">
         <v>911</v>
       </c>
-      <c r="E66" s="31"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="31"/>
-      <c r="H66" s="31"/>
-      <c r="I66" s="31"/>
-      <c r="J66" s="31"/>
-      <c r="K66" s="31"/>
-      <c r="L66" s="31"/>
-      <c r="M66" s="31"/>
-      <c r="N66" s="31"/>
-      <c r="O66" s="30"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="30"/>
+      <c r="H66" s="30"/>
+      <c r="I66" s="30"/>
+      <c r="J66" s="30"/>
+      <c r="K66" s="30"/>
+      <c r="L66" s="30"/>
+      <c r="M66" s="30"/>
+      <c r="N66" s="30"/>
+      <c r="O66" s="29"/>
     </row>
     <row r="67" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="74"/>
@@ -18112,240 +18107,240 @@
       </c>
       <c r="C67" s="82"/>
       <c r="D67" s="82"/>
-      <c r="E67" s="31"/>
-      <c r="F67" s="31"/>
-      <c r="G67" s="31"/>
-      <c r="H67" s="31"/>
-      <c r="I67" s="31"/>
-      <c r="J67" s="31"/>
-      <c r="K67" s="31"/>
-      <c r="L67" s="31"/>
-      <c r="M67" s="31"/>
-      <c r="N67" s="31"/>
-      <c r="O67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="29"/>
     </row>
     <row r="68" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="74"/>
-      <c r="B68" s="42" t="s">
+      <c r="B68" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="C68" s="25" t="s">
+      <c r="C68" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="D68" s="25" t="s">
+      <c r="D68" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E68" s="43"/>
-      <c r="F68" s="43"/>
-      <c r="G68" s="43"/>
-      <c r="H68" s="16"/>
-      <c r="I68" s="16"/>
-      <c r="J68" s="16"/>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="16"/>
-      <c r="O68" s="30"/>
+      <c r="E68" s="42"/>
+      <c r="F68" s="42"/>
+      <c r="G68" s="42"/>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
+      <c r="L68" s="15"/>
+      <c r="M68" s="15"/>
+      <c r="N68" s="15"/>
+      <c r="O68" s="29"/>
     </row>
     <row r="69" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="74"/>
-      <c r="B69" s="42">
+      <c r="B69" s="41">
         <v>1</v>
       </c>
-      <c r="C69" s="40">
+      <c r="C69" s="39">
         <f>C59/C59</f>
         <v>1</v>
       </c>
-      <c r="D69" s="40">
+      <c r="D69" s="39">
         <f>D59/D59</f>
         <v>1</v>
       </c>
-      <c r="E69" s="43"/>
-      <c r="F69" s="43"/>
-      <c r="G69" s="43"/>
-      <c r="H69" s="16"/>
-      <c r="I69" s="16"/>
-      <c r="J69" s="16"/>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="16"/>
-      <c r="O69" s="30"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+      <c r="G69" s="42"/>
+      <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
+      <c r="J69" s="15"/>
+      <c r="K69" s="15"/>
+      <c r="L69" s="15"/>
+      <c r="M69" s="15"/>
+      <c r="N69" s="15"/>
+      <c r="O69" s="29"/>
     </row>
     <row r="70" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="74"/>
-      <c r="B70" s="42">
+      <c r="B70" s="41">
         <v>2</v>
       </c>
-      <c r="C70" s="40">
+      <c r="C70" s="39">
         <f>C59/C60</f>
         <v>1.2782564622402433</v>
       </c>
-      <c r="D70" s="40">
+      <c r="D70" s="39">
         <f>D59/D60</f>
         <v>1.3200468933177023</v>
       </c>
-      <c r="E70" s="43"/>
-      <c r="F70" s="43"/>
-      <c r="G70" s="43"/>
-      <c r="H70" s="16"/>
-      <c r="I70" s="16"/>
-      <c r="J70" s="16"/>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="16"/>
-      <c r="O70" s="30"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="42"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
+      <c r="L70" s="15"/>
+      <c r="M70" s="15"/>
+      <c r="N70" s="15"/>
+      <c r="O70" s="29"/>
     </row>
     <row r="71" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="74"/>
-      <c r="B71" s="42">
+      <c r="B71" s="41">
         <v>4</v>
       </c>
-      <c r="C71" s="40">
+      <c r="C71" s="39">
         <f>C59/C61</f>
         <v>1.8912635920509937</v>
       </c>
-      <c r="D71" s="40">
+      <c r="D71" s="39">
         <f>D59/D61</f>
         <v>1.603988603988604</v>
       </c>
-      <c r="E71" s="43"/>
-      <c r="F71" s="43"/>
-      <c r="G71" s="43"/>
-      <c r="H71" s="16"/>
-      <c r="I71" s="16"/>
-      <c r="J71" s="16"/>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="16"/>
-      <c r="O71" s="30"/>
+      <c r="E71" s="42"/>
+      <c r="F71" s="42"/>
+      <c r="G71" s="42"/>
+      <c r="H71" s="15"/>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15"/>
+      <c r="L71" s="15"/>
+      <c r="M71" s="15"/>
+      <c r="N71" s="15"/>
+      <c r="O71" s="29"/>
     </row>
     <row r="72" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="74"/>
-      <c r="B72" s="42">
+      <c r="B72" s="41">
         <v>6</v>
       </c>
-      <c r="C72" s="40">
+      <c r="C72" s="39">
         <f>C59/C62</f>
         <v>1.7209143636983963</v>
       </c>
-      <c r="D72" s="40">
+      <c r="D72" s="39">
         <f>D59/D62</f>
         <v>1.3533653846153846</v>
       </c>
-      <c r="E72" s="43"/>
-      <c r="F72" s="43"/>
-      <c r="G72" s="43"/>
-      <c r="H72" s="16"/>
-      <c r="I72" s="16"/>
-      <c r="J72" s="16"/>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="16"/>
-      <c r="O72" s="30"/>
+      <c r="E72" s="42"/>
+      <c r="F72" s="42"/>
+      <c r="G72" s="42"/>
+      <c r="H72" s="15"/>
+      <c r="I72" s="15"/>
+      <c r="J72" s="15"/>
+      <c r="K72" s="15"/>
+      <c r="L72" s="15"/>
+      <c r="M72" s="15"/>
+      <c r="N72" s="15"/>
+      <c r="O72" s="29"/>
     </row>
     <row r="73" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="74"/>
-      <c r="B73" s="42">
+      <c r="B73" s="41">
         <v>8</v>
       </c>
-      <c r="C73" s="40">
+      <c r="C73" s="39">
         <f>C59/C63</f>
         <v>1.8183129055515501</v>
       </c>
-      <c r="D73" s="40">
+      <c r="D73" s="39">
         <f>D59/D63</f>
         <v>1.3799019607843137</v>
       </c>
-      <c r="E73" s="43"/>
-      <c r="F73" s="43"/>
-      <c r="G73" s="43"/>
-      <c r="H73" s="16"/>
-      <c r="I73" s="16"/>
-      <c r="J73" s="16"/>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="16"/>
-      <c r="O73" s="30"/>
+      <c r="E73" s="42"/>
+      <c r="F73" s="42"/>
+      <c r="G73" s="42"/>
+      <c r="H73" s="15"/>
+      <c r="I73" s="15"/>
+      <c r="J73" s="15"/>
+      <c r="K73" s="15"/>
+      <c r="L73" s="15"/>
+      <c r="M73" s="15"/>
+      <c r="N73" s="15"/>
+      <c r="O73" s="29"/>
     </row>
     <row r="74" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="74"/>
-      <c r="B74" s="42">
+      <c r="B74" s="41">
         <v>10</v>
       </c>
-      <c r="C74" s="40">
+      <c r="C74" s="39">
         <f>C59/C64</f>
         <v>1.759944173063503</v>
       </c>
-      <c r="D74" s="40">
+      <c r="D74" s="39">
         <f>D59/D64</f>
         <v>1.3341232227488151</v>
       </c>
-      <c r="E74" s="43"/>
-      <c r="F74" s="43"/>
-      <c r="G74" s="43"/>
-      <c r="H74" s="16"/>
-      <c r="I74" s="16"/>
-      <c r="J74" s="16"/>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="16"/>
-      <c r="O74" s="30"/>
+      <c r="E74" s="42"/>
+      <c r="F74" s="42"/>
+      <c r="G74" s="42"/>
+      <c r="H74" s="15"/>
+      <c r="I74" s="15"/>
+      <c r="J74" s="15"/>
+      <c r="K74" s="15"/>
+      <c r="L74" s="15"/>
+      <c r="M74" s="15"/>
+      <c r="N74" s="15"/>
+      <c r="O74" s="29"/>
     </row>
     <row r="75" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="74"/>
-      <c r="B75" s="42">
+      <c r="B75" s="41">
         <v>12</v>
       </c>
-      <c r="C75" s="40">
+      <c r="C75" s="39">
         <f>C59/C65</f>
         <v>1.8189686260367832</v>
       </c>
-      <c r="D75" s="40">
+      <c r="D75" s="39">
         <f>D59/D65</f>
         <v>1.2766439909297052</v>
       </c>
-      <c r="E75" s="43"/>
-      <c r="F75" s="43"/>
-      <c r="G75" s="43"/>
-      <c r="H75" s="16"/>
-      <c r="I75" s="16"/>
-      <c r="J75" s="16"/>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="16"/>
-      <c r="O75" s="30"/>
+      <c r="E75" s="42"/>
+      <c r="F75" s="42"/>
+      <c r="G75" s="42"/>
+      <c r="H75" s="15"/>
+      <c r="I75" s="15"/>
+      <c r="J75" s="15"/>
+      <c r="K75" s="15"/>
+      <c r="L75" s="15"/>
+      <c r="M75" s="15"/>
+      <c r="N75" s="15"/>
+      <c r="O75" s="29"/>
     </row>
     <row r="76" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="74"/>
-      <c r="B76" s="42">
+      <c r="B76" s="41">
         <v>16</v>
       </c>
-      <c r="C76" s="40">
+      <c r="C76" s="39">
         <f>C59/C66</f>
         <v>1.8640059127864006</v>
       </c>
-      <c r="D76" s="40">
+      <c r="D76" s="39">
         <f>D59/D66</f>
         <v>1.2360043907793634</v>
       </c>
-      <c r="E76" s="43"/>
-      <c r="F76" s="43"/>
-      <c r="G76" s="43"/>
-      <c r="H76" s="16"/>
-      <c r="I76" s="16"/>
-      <c r="J76" s="16"/>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="16"/>
-      <c r="O76" s="30"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="42"/>
+      <c r="G76" s="42"/>
+      <c r="H76" s="15"/>
+      <c r="I76" s="15"/>
+      <c r="J76" s="15"/>
+      <c r="K76" s="15"/>
+      <c r="L76" s="15"/>
+      <c r="M76" s="15"/>
+      <c r="N76" s="15"/>
+      <c r="O76" s="29"/>
     </row>
     <row r="77" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="74"/>
@@ -18354,244 +18349,244 @@
       </c>
       <c r="C77" s="82"/>
       <c r="D77" s="82"/>
-      <c r="E77" s="43"/>
-      <c r="F77" s="43"/>
-      <c r="G77" s="43"/>
-      <c r="H77" s="16"/>
-      <c r="I77" s="16"/>
-      <c r="J77" s="16"/>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="16"/>
-      <c r="O77" s="30"/>
+      <c r="E77" s="42"/>
+      <c r="F77" s="42"/>
+      <c r="G77" s="42"/>
+      <c r="H77" s="15"/>
+      <c r="I77" s="15"/>
+      <c r="J77" s="15"/>
+      <c r="K77" s="15"/>
+      <c r="L77" s="15"/>
+      <c r="M77" s="15"/>
+      <c r="N77" s="15"/>
+      <c r="O77" s="29"/>
     </row>
     <row r="78" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="74"/>
-      <c r="B78" s="42" t="s">
+      <c r="B78" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="25" t="s">
+      <c r="C78" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="D78" s="25" t="s">
+      <c r="D78" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E78" s="43"/>
-      <c r="F78" s="43"/>
-      <c r="G78" s="43"/>
-      <c r="H78" s="16"/>
-      <c r="I78" s="16"/>
-      <c r="J78" s="16"/>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
-      <c r="N78" s="16"/>
-      <c r="O78" s="30"/>
+      <c r="E78" s="42"/>
+      <c r="F78" s="42"/>
+      <c r="G78" s="42"/>
+      <c r="H78" s="15"/>
+      <c r="I78" s="15"/>
+      <c r="J78" s="15"/>
+      <c r="K78" s="15"/>
+      <c r="L78" s="15"/>
+      <c r="M78" s="15"/>
+      <c r="N78" s="15"/>
+      <c r="O78" s="29"/>
     </row>
     <row r="79" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="74"/>
-      <c r="B79" s="42">
+      <c r="B79" s="41">
         <v>1</v>
       </c>
-      <c r="C79" s="40">
+      <c r="C79" s="39">
         <f t="shared" ref="C79:C86" si="2">C69/B69</f>
         <v>1</v>
       </c>
-      <c r="D79" s="40">
+      <c r="D79" s="39">
         <f t="shared" ref="D79:D86" si="3">D69/B69</f>
         <v>1</v>
       </c>
-      <c r="E79" s="43"/>
-      <c r="F79" s="43"/>
-      <c r="G79" s="43"/>
-      <c r="H79" s="16"/>
-      <c r="I79" s="16"/>
-      <c r="J79" s="16"/>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
-      <c r="N79" s="16"/>
-      <c r="O79" s="30"/>
+      <c r="E79" s="42"/>
+      <c r="F79" s="42"/>
+      <c r="G79" s="42"/>
+      <c r="H79" s="15"/>
+      <c r="I79" s="15"/>
+      <c r="J79" s="15"/>
+      <c r="K79" s="15"/>
+      <c r="L79" s="15"/>
+      <c r="M79" s="15"/>
+      <c r="N79" s="15"/>
+      <c r="O79" s="29"/>
     </row>
     <row r="80" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="74"/>
-      <c r="B80" s="42">
+      <c r="B80" s="41">
         <v>2</v>
       </c>
-      <c r="C80" s="40">
+      <c r="C80" s="39">
         <f t="shared" si="2"/>
         <v>0.63912823112012163</v>
       </c>
-      <c r="D80" s="40">
+      <c r="D80" s="39">
         <f t="shared" si="3"/>
         <v>0.66002344665885115</v>
       </c>
-      <c r="E80" s="43"/>
-      <c r="F80" s="43"/>
-      <c r="G80" s="43"/>
-      <c r="H80" s="16"/>
-      <c r="I80" s="16"/>
-      <c r="J80" s="16"/>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
-      <c r="N80" s="16"/>
-      <c r="O80" s="30"/>
+      <c r="E80" s="42"/>
+      <c r="F80" s="42"/>
+      <c r="G80" s="42"/>
+      <c r="H80" s="15"/>
+      <c r="I80" s="15"/>
+      <c r="J80" s="15"/>
+      <c r="K80" s="15"/>
+      <c r="L80" s="15"/>
+      <c r="M80" s="15"/>
+      <c r="N80" s="15"/>
+      <c r="O80" s="29"/>
     </row>
     <row r="81" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="74"/>
-      <c r="B81" s="42">
+      <c r="B81" s="41">
         <v>4</v>
       </c>
-      <c r="C81" s="40">
+      <c r="C81" s="39">
         <f t="shared" si="2"/>
         <v>0.47281589801274843</v>
       </c>
-      <c r="D81" s="40">
+      <c r="D81" s="39">
         <f t="shared" si="3"/>
         <v>0.400997150997151</v>
       </c>
-      <c r="E81" s="43"/>
-      <c r="F81" s="43"/>
-      <c r="G81" s="43"/>
-      <c r="H81" s="16"/>
-      <c r="I81" s="16"/>
-      <c r="J81" s="16"/>
-      <c r="K81" s="16"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="16"/>
-      <c r="N81" s="16"/>
-      <c r="O81" s="30"/>
+      <c r="E81" s="42"/>
+      <c r="F81" s="42"/>
+      <c r="G81" s="42"/>
+      <c r="H81" s="15"/>
+      <c r="I81" s="15"/>
+      <c r="J81" s="15"/>
+      <c r="K81" s="15"/>
+      <c r="L81" s="15"/>
+      <c r="M81" s="15"/>
+      <c r="N81" s="15"/>
+      <c r="O81" s="29"/>
     </row>
     <row r="82" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="74"/>
-      <c r="B82" s="42">
+      <c r="B82" s="41">
         <v>6</v>
       </c>
-      <c r="C82" s="40">
+      <c r="C82" s="39">
         <f t="shared" si="2"/>
         <v>0.28681906061639939</v>
       </c>
-      <c r="D82" s="40">
+      <c r="D82" s="39">
         <f t="shared" si="3"/>
         <v>0.22556089743589744</v>
       </c>
-      <c r="E82" s="43"/>
-      <c r="F82" s="43"/>
-      <c r="G82" s="43"/>
-      <c r="H82" s="16"/>
-      <c r="I82" s="16"/>
-      <c r="J82" s="16"/>
-      <c r="K82" s="16"/>
-      <c r="L82" s="16"/>
-      <c r="M82" s="16"/>
-      <c r="N82" s="16"/>
-      <c r="O82" s="30"/>
+      <c r="E82" s="42"/>
+      <c r="F82" s="42"/>
+      <c r="G82" s="42"/>
+      <c r="H82" s="15"/>
+      <c r="I82" s="15"/>
+      <c r="J82" s="15"/>
+      <c r="K82" s="15"/>
+      <c r="L82" s="15"/>
+      <c r="M82" s="15"/>
+      <c r="N82" s="15"/>
+      <c r="O82" s="29"/>
     </row>
     <row r="83" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="74"/>
-      <c r="B83" s="42">
+      <c r="B83" s="41">
         <v>8</v>
       </c>
-      <c r="C83" s="40">
+      <c r="C83" s="39">
         <f t="shared" si="2"/>
         <v>0.22728911319394376</v>
       </c>
-      <c r="D83" s="40">
+      <c r="D83" s="39">
         <f t="shared" si="3"/>
         <v>0.17248774509803921</v>
       </c>
-      <c r="E83" s="43"/>
-      <c r="F83" s="43"/>
-      <c r="G83" s="43"/>
-      <c r="H83" s="16"/>
-      <c r="I83" s="16"/>
-      <c r="J83" s="16"/>
-      <c r="K83" s="16"/>
-      <c r="L83" s="16"/>
-      <c r="M83" s="16"/>
-      <c r="N83" s="16"/>
-      <c r="O83" s="30"/>
+      <c r="E83" s="42"/>
+      <c r="F83" s="42"/>
+      <c r="G83" s="42"/>
+      <c r="H83" s="15"/>
+      <c r="I83" s="15"/>
+      <c r="J83" s="15"/>
+      <c r="K83" s="15"/>
+      <c r="L83" s="15"/>
+      <c r="M83" s="15"/>
+      <c r="N83" s="15"/>
+      <c r="O83" s="29"/>
     </row>
     <row r="84" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="74"/>
-      <c r="B84" s="42">
+      <c r="B84" s="41">
         <v>10</v>
       </c>
-      <c r="C84" s="40">
+      <c r="C84" s="39">
         <f t="shared" si="2"/>
         <v>0.17599441730635029</v>
       </c>
-      <c r="D84" s="40">
+      <c r="D84" s="39">
         <f t="shared" si="3"/>
         <v>0.13341232227488151</v>
       </c>
-      <c r="E84" s="43"/>
-      <c r="F84" s="43"/>
-      <c r="G84" s="43"/>
-      <c r="H84" s="16"/>
-      <c r="I84" s="16"/>
-      <c r="J84" s="16"/>
-      <c r="K84" s="16"/>
-      <c r="L84" s="16"/>
-      <c r="M84" s="16"/>
-      <c r="N84" s="16"/>
-      <c r="O84" s="30"/>
+      <c r="E84" s="42"/>
+      <c r="F84" s="42"/>
+      <c r="G84" s="42"/>
+      <c r="H84" s="15"/>
+      <c r="I84" s="15"/>
+      <c r="J84" s="15"/>
+      <c r="K84" s="15"/>
+      <c r="L84" s="15"/>
+      <c r="M84" s="15"/>
+      <c r="N84" s="15"/>
+      <c r="O84" s="29"/>
     </row>
     <row r="85" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="74"/>
-      <c r="B85" s="42">
+      <c r="B85" s="41">
         <v>12</v>
       </c>
-      <c r="C85" s="40">
+      <c r="C85" s="39">
         <f t="shared" si="2"/>
         <v>0.15158071883639859</v>
       </c>
-      <c r="D85" s="40">
+      <c r="D85" s="39">
         <f t="shared" si="3"/>
         <v>0.10638699924414209</v>
       </c>
-      <c r="E85" s="31"/>
-      <c r="F85" s="31"/>
-      <c r="G85" s="31"/>
-      <c r="H85" s="31"/>
-      <c r="I85" s="31"/>
-      <c r="J85" s="31"/>
-      <c r="K85" s="31"/>
-      <c r="L85" s="31"/>
-      <c r="M85" s="31"/>
-      <c r="N85" s="31"/>
-      <c r="O85" s="30"/>
+      <c r="E85" s="30"/>
+      <c r="F85" s="30"/>
+      <c r="G85" s="30"/>
+      <c r="H85" s="30"/>
+      <c r="I85" s="30"/>
+      <c r="J85" s="30"/>
+      <c r="K85" s="30"/>
+      <c r="L85" s="30"/>
+      <c r="M85" s="30"/>
+      <c r="N85" s="30"/>
+      <c r="O85" s="29"/>
     </row>
     <row r="86" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="74"/>
-      <c r="B86" s="42">
+      <c r="B86" s="41">
         <v>16</v>
       </c>
-      <c r="C86" s="40">
+      <c r="C86" s="39">
         <f t="shared" si="2"/>
         <v>0.11650036954915004</v>
       </c>
-      <c r="D86" s="40">
+      <c r="D86" s="39">
         <f t="shared" si="3"/>
         <v>7.7250274423710213E-2</v>
       </c>
-      <c r="E86" s="31"/>
-      <c r="F86" s="31"/>
-      <c r="G86" s="31"/>
-      <c r="H86" s="31"/>
-      <c r="I86" s="31"/>
-      <c r="J86" s="31"/>
-      <c r="K86" s="31"/>
-      <c r="L86" s="31"/>
-      <c r="M86" s="31"/>
-      <c r="N86" s="31"/>
-      <c r="O86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="30"/>
+      <c r="H86" s="30"/>
+      <c r="I86" s="30"/>
+      <c r="J86" s="30"/>
+      <c r="K86" s="30"/>
+      <c r="L86" s="30"/>
+      <c r="M86" s="30"/>
+      <c r="N86" s="30"/>
+      <c r="O86" s="29"/>
     </row>
     <row r="87" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="74"/>
-      <c r="B87" s="33" t="s">
+      <c r="B87" s="32" t="s">
         <v>86</v>
       </c>
       <c r="C87" s="75" t="s">
@@ -18610,3263 +18605,3263 @@
       <c r="N87" s="75"/>
     </row>
     <row r="88" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="50"/>
-      <c r="B88" s="50"/>
-      <c r="C88" s="50"/>
-      <c r="D88" s="50"/>
-      <c r="E88" s="50"/>
-      <c r="F88" s="50"/>
-      <c r="G88" s="50"/>
-      <c r="H88" s="50"/>
-      <c r="I88" s="50"/>
-      <c r="J88" s="50"/>
-      <c r="K88" s="50"/>
-      <c r="L88" s="50"/>
-      <c r="M88" s="50"/>
-      <c r="N88" s="50"/>
-      <c r="O88" s="51"/>
-      <c r="P88" s="51"/>
-      <c r="Q88" s="51"/>
-      <c r="R88" s="51"/>
-      <c r="S88" s="51"/>
-      <c r="T88" s="51"/>
-      <c r="U88" s="52"/>
-      <c r="V88" s="52"/>
-      <c r="W88" s="52"/>
-      <c r="X88" s="52"/>
-      <c r="Y88" s="52"/>
-      <c r="Z88" s="52"/>
-      <c r="AA88" s="52"/>
-      <c r="AB88" s="52"/>
-      <c r="AC88" s="52"/>
+      <c r="A88" s="49"/>
+      <c r="B88" s="49"/>
+      <c r="C88" s="49"/>
+      <c r="D88" s="49"/>
+      <c r="E88" s="49"/>
+      <c r="F88" s="49"/>
+      <c r="G88" s="49"/>
+      <c r="H88" s="49"/>
+      <c r="I88" s="49"/>
+      <c r="J88" s="49"/>
+      <c r="K88" s="49"/>
+      <c r="L88" s="49"/>
+      <c r="M88" s="49"/>
+      <c r="N88" s="49"/>
+      <c r="O88" s="50"/>
+      <c r="P88" s="50"/>
+      <c r="Q88" s="50"/>
+      <c r="R88" s="50"/>
+      <c r="S88" s="50"/>
+      <c r="T88" s="50"/>
+      <c r="U88" s="51"/>
+      <c r="V88" s="51"/>
+      <c r="W88" s="51"/>
+      <c r="X88" s="51"/>
+      <c r="Y88" s="51"/>
+      <c r="Z88" s="51"/>
+      <c r="AA88" s="51"/>
+      <c r="AB88" s="51"/>
+      <c r="AC88" s="51"/>
     </row>
     <row r="89" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="53"/>
-      <c r="B89" s="54"/>
-      <c r="C89" s="54"/>
-      <c r="D89" s="54"/>
-      <c r="E89" s="54"/>
-      <c r="F89" s="52"/>
-      <c r="G89" s="52"/>
-      <c r="H89" s="52"/>
-      <c r="I89" s="52"/>
-      <c r="J89" s="52"/>
-      <c r="K89" s="52"/>
-      <c r="L89" s="52"/>
-      <c r="M89" s="52"/>
-      <c r="N89" s="52"/>
-      <c r="O89" s="52"/>
-      <c r="P89" s="52"/>
-      <c r="Q89" s="52"/>
-      <c r="R89" s="52"/>
-      <c r="S89" s="52"/>
-      <c r="T89" s="52"/>
-      <c r="U89" s="52"/>
-      <c r="V89" s="52"/>
-      <c r="W89" s="52"/>
-      <c r="X89" s="52"/>
-      <c r="Y89" s="52"/>
-      <c r="Z89" s="52"/>
-      <c r="AA89" s="52"/>
-      <c r="AB89" s="52"/>
-      <c r="AC89" s="52"/>
+      <c r="A89" s="52"/>
+      <c r="B89" s="53"/>
+      <c r="C89" s="53"/>
+      <c r="D89" s="53"/>
+      <c r="E89" s="53"/>
+      <c r="F89" s="51"/>
+      <c r="G89" s="51"/>
+      <c r="H89" s="51"/>
+      <c r="I89" s="51"/>
+      <c r="J89" s="51"/>
+      <c r="K89" s="51"/>
+      <c r="L89" s="51"/>
+      <c r="M89" s="51"/>
+      <c r="N89" s="51"/>
+      <c r="O89" s="51"/>
+      <c r="P89" s="51"/>
+      <c r="Q89" s="51"/>
+      <c r="R89" s="51"/>
+      <c r="S89" s="51"/>
+      <c r="T89" s="51"/>
+      <c r="U89" s="51"/>
+      <c r="V89" s="51"/>
+      <c r="W89" s="51"/>
+      <c r="X89" s="51"/>
+      <c r="Y89" s="51"/>
+      <c r="Z89" s="51"/>
+      <c r="AA89" s="51"/>
+      <c r="AB89" s="51"/>
+      <c r="AC89" s="51"/>
     </row>
     <row r="90" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="53"/>
-      <c r="B90" s="54"/>
-      <c r="C90" s="55"/>
-      <c r="D90" s="55"/>
-      <c r="E90" s="55"/>
-      <c r="F90" s="52"/>
-      <c r="G90" s="52"/>
-      <c r="H90" s="52"/>
-      <c r="I90" s="52"/>
-      <c r="J90" s="52"/>
-      <c r="K90" s="52"/>
-      <c r="L90" s="52"/>
-      <c r="M90" s="52"/>
-      <c r="N90" s="52"/>
-      <c r="O90" s="52"/>
-      <c r="P90" s="52"/>
-      <c r="Q90" s="52"/>
-      <c r="R90" s="52"/>
-      <c r="S90" s="52"/>
-      <c r="T90" s="52"/>
-      <c r="U90" s="52"/>
-      <c r="V90" s="52"/>
-      <c r="W90" s="52"/>
-      <c r="X90" s="52"/>
-      <c r="Y90" s="52"/>
-      <c r="Z90" s="52"/>
-      <c r="AA90" s="52"/>
-      <c r="AB90" s="52"/>
-      <c r="AC90" s="52"/>
+      <c r="A90" s="52"/>
+      <c r="B90" s="53"/>
+      <c r="C90" s="54"/>
+      <c r="D90" s="54"/>
+      <c r="E90" s="54"/>
+      <c r="F90" s="51"/>
+      <c r="G90" s="51"/>
+      <c r="H90" s="51"/>
+      <c r="I90" s="51"/>
+      <c r="J90" s="51"/>
+      <c r="K90" s="51"/>
+      <c r="L90" s="51"/>
+      <c r="M90" s="51"/>
+      <c r="N90" s="51"/>
+      <c r="O90" s="51"/>
+      <c r="P90" s="51"/>
+      <c r="Q90" s="51"/>
+      <c r="R90" s="51"/>
+      <c r="S90" s="51"/>
+      <c r="T90" s="51"/>
+      <c r="U90" s="51"/>
+      <c r="V90" s="51"/>
+      <c r="W90" s="51"/>
+      <c r="X90" s="51"/>
+      <c r="Y90" s="51"/>
+      <c r="Z90" s="51"/>
+      <c r="AA90" s="51"/>
+      <c r="AB90" s="51"/>
+      <c r="AC90" s="51"/>
     </row>
     <row r="91" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="53"/>
-      <c r="B91" s="55"/>
-      <c r="C91" s="56"/>
-      <c r="D91" s="57"/>
-      <c r="E91" s="57"/>
-      <c r="F91" s="52"/>
-      <c r="G91" s="52"/>
-      <c r="H91" s="52"/>
-      <c r="I91" s="52"/>
-      <c r="J91" s="52"/>
-      <c r="K91" s="52"/>
-      <c r="L91" s="52"/>
-      <c r="M91" s="52"/>
-      <c r="N91" s="52"/>
-      <c r="O91" s="52"/>
-      <c r="P91" s="52"/>
-      <c r="Q91" s="52"/>
-      <c r="R91" s="52"/>
-      <c r="S91" s="52"/>
-      <c r="T91" s="52"/>
-      <c r="U91" s="52"/>
-      <c r="V91" s="52"/>
-      <c r="W91" s="52"/>
-      <c r="X91" s="52"/>
-      <c r="Y91" s="52"/>
-      <c r="Z91" s="52"/>
-      <c r="AA91" s="52"/>
-      <c r="AB91" s="52"/>
-      <c r="AC91" s="52"/>
+      <c r="A91" s="52"/>
+      <c r="B91" s="54"/>
+      <c r="C91" s="55"/>
+      <c r="D91" s="56"/>
+      <c r="E91" s="56"/>
+      <c r="F91" s="51"/>
+      <c r="G91" s="51"/>
+      <c r="H91" s="51"/>
+      <c r="I91" s="51"/>
+      <c r="J91" s="51"/>
+      <c r="K91" s="51"/>
+      <c r="L91" s="51"/>
+      <c r="M91" s="51"/>
+      <c r="N91" s="51"/>
+      <c r="O91" s="51"/>
+      <c r="P91" s="51"/>
+      <c r="Q91" s="51"/>
+      <c r="R91" s="51"/>
+      <c r="S91" s="51"/>
+      <c r="T91" s="51"/>
+      <c r="U91" s="51"/>
+      <c r="V91" s="51"/>
+      <c r="W91" s="51"/>
+      <c r="X91" s="51"/>
+      <c r="Y91" s="51"/>
+      <c r="Z91" s="51"/>
+      <c r="AA91" s="51"/>
+      <c r="AB91" s="51"/>
+      <c r="AC91" s="51"/>
     </row>
     <row r="92" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="53"/>
-      <c r="B92" s="55"/>
-      <c r="C92" s="56"/>
-      <c r="D92" s="57"/>
-      <c r="E92" s="57"/>
-      <c r="F92" s="52"/>
-      <c r="G92" s="52"/>
-      <c r="H92" s="52"/>
-      <c r="I92" s="52"/>
-      <c r="J92" s="52"/>
-      <c r="K92" s="52"/>
-      <c r="L92" s="52"/>
-      <c r="M92" s="52"/>
-      <c r="N92" s="52"/>
-      <c r="O92" s="52"/>
-      <c r="P92" s="52"/>
-      <c r="Q92" s="52"/>
-      <c r="R92" s="52"/>
-      <c r="S92" s="52"/>
-      <c r="T92" s="52"/>
-      <c r="U92" s="52"/>
-      <c r="V92" s="52"/>
-      <c r="W92" s="52"/>
-      <c r="X92" s="52"/>
-      <c r="Y92" s="52"/>
-      <c r="Z92" s="52"/>
-      <c r="AA92" s="52"/>
-      <c r="AB92" s="52"/>
-      <c r="AC92" s="52"/>
+      <c r="A92" s="52"/>
+      <c r="B92" s="54"/>
+      <c r="C92" s="55"/>
+      <c r="D92" s="56"/>
+      <c r="E92" s="56"/>
+      <c r="F92" s="51"/>
+      <c r="G92" s="51"/>
+      <c r="H92" s="51"/>
+      <c r="I92" s="51"/>
+      <c r="J92" s="51"/>
+      <c r="K92" s="51"/>
+      <c r="L92" s="51"/>
+      <c r="M92" s="51"/>
+      <c r="N92" s="51"/>
+      <c r="O92" s="51"/>
+      <c r="P92" s="51"/>
+      <c r="Q92" s="51"/>
+      <c r="R92" s="51"/>
+      <c r="S92" s="51"/>
+      <c r="T92" s="51"/>
+      <c r="U92" s="51"/>
+      <c r="V92" s="51"/>
+      <c r="W92" s="51"/>
+      <c r="X92" s="51"/>
+      <c r="Y92" s="51"/>
+      <c r="Z92" s="51"/>
+      <c r="AA92" s="51"/>
+      <c r="AB92" s="51"/>
+      <c r="AC92" s="51"/>
     </row>
     <row r="93" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="53"/>
-      <c r="B93" s="55"/>
-      <c r="C93" s="56"/>
-      <c r="D93" s="57"/>
-      <c r="E93" s="57"/>
-      <c r="F93" s="52"/>
-      <c r="G93" s="52"/>
-      <c r="H93" s="52"/>
-      <c r="I93" s="52"/>
-      <c r="J93" s="52"/>
-      <c r="K93" s="52"/>
-      <c r="L93" s="52"/>
-      <c r="M93" s="52"/>
-      <c r="N93" s="52"/>
-      <c r="O93" s="52"/>
-      <c r="P93" s="52"/>
-      <c r="Q93" s="52"/>
-      <c r="R93" s="52"/>
-      <c r="S93" s="52"/>
-      <c r="T93" s="52"/>
-      <c r="U93" s="52"/>
-      <c r="V93" s="52"/>
-      <c r="W93" s="52"/>
-      <c r="X93" s="52"/>
-      <c r="Y93" s="52"/>
-      <c r="Z93" s="52"/>
-      <c r="AA93" s="52"/>
-      <c r="AB93" s="52"/>
-      <c r="AC93" s="52"/>
+      <c r="A93" s="52"/>
+      <c r="B93" s="54"/>
+      <c r="C93" s="55"/>
+      <c r="D93" s="56"/>
+      <c r="E93" s="56"/>
+      <c r="F93" s="51"/>
+      <c r="G93" s="51"/>
+      <c r="H93" s="51"/>
+      <c r="I93" s="51"/>
+      <c r="J93" s="51"/>
+      <c r="K93" s="51"/>
+      <c r="L93" s="51"/>
+      <c r="M93" s="51"/>
+      <c r="N93" s="51"/>
+      <c r="O93" s="51"/>
+      <c r="P93" s="51"/>
+      <c r="Q93" s="51"/>
+      <c r="R93" s="51"/>
+      <c r="S93" s="51"/>
+      <c r="T93" s="51"/>
+      <c r="U93" s="51"/>
+      <c r="V93" s="51"/>
+      <c r="W93" s="51"/>
+      <c r="X93" s="51"/>
+      <c r="Y93" s="51"/>
+      <c r="Z93" s="51"/>
+      <c r="AA93" s="51"/>
+      <c r="AB93" s="51"/>
+      <c r="AC93" s="51"/>
     </row>
     <row r="94" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="53"/>
-      <c r="B94" s="55"/>
-      <c r="C94" s="56"/>
-      <c r="D94" s="57"/>
-      <c r="E94" s="57"/>
-      <c r="F94" s="52"/>
-      <c r="G94" s="52"/>
-      <c r="H94" s="52"/>
-      <c r="I94" s="52"/>
-      <c r="J94" s="52"/>
-      <c r="K94" s="52"/>
-      <c r="L94" s="52"/>
-      <c r="M94" s="52"/>
-      <c r="N94" s="52"/>
-      <c r="O94" s="52"/>
-      <c r="P94" s="52"/>
-      <c r="Q94" s="52"/>
-      <c r="R94" s="52"/>
-      <c r="S94" s="52"/>
-      <c r="T94" s="52"/>
-      <c r="U94" s="52"/>
-      <c r="V94" s="52"/>
-      <c r="W94" s="52"/>
-      <c r="X94" s="52"/>
-      <c r="Y94" s="52"/>
-      <c r="Z94" s="52"/>
-      <c r="AA94" s="52"/>
-      <c r="AB94" s="52"/>
-      <c r="AC94" s="52"/>
+      <c r="A94" s="52"/>
+      <c r="B94" s="54"/>
+      <c r="C94" s="55"/>
+      <c r="D94" s="56"/>
+      <c r="E94" s="56"/>
+      <c r="F94" s="51"/>
+      <c r="G94" s="51"/>
+      <c r="H94" s="51"/>
+      <c r="I94" s="51"/>
+      <c r="J94" s="51"/>
+      <c r="K94" s="51"/>
+      <c r="L94" s="51"/>
+      <c r="M94" s="51"/>
+      <c r="N94" s="51"/>
+      <c r="O94" s="51"/>
+      <c r="P94" s="51"/>
+      <c r="Q94" s="51"/>
+      <c r="R94" s="51"/>
+      <c r="S94" s="51"/>
+      <c r="T94" s="51"/>
+      <c r="U94" s="51"/>
+      <c r="V94" s="51"/>
+      <c r="W94" s="51"/>
+      <c r="X94" s="51"/>
+      <c r="Y94" s="51"/>
+      <c r="Z94" s="51"/>
+      <c r="AA94" s="51"/>
+      <c r="AB94" s="51"/>
+      <c r="AC94" s="51"/>
     </row>
     <row r="95" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="53"/>
-      <c r="B95" s="55"/>
-      <c r="C95" s="56"/>
-      <c r="D95" s="57"/>
-      <c r="E95" s="57"/>
-      <c r="F95" s="52"/>
-      <c r="G95" s="52"/>
-      <c r="H95" s="52"/>
-      <c r="I95" s="52"/>
-      <c r="J95" s="52"/>
-      <c r="K95" s="52"/>
-      <c r="L95" s="52"/>
-      <c r="M95" s="52"/>
-      <c r="N95" s="52"/>
-      <c r="O95" s="52"/>
-      <c r="P95" s="52"/>
-      <c r="Q95" s="52"/>
-      <c r="R95" s="52"/>
-      <c r="S95" s="52"/>
-      <c r="T95" s="52"/>
-      <c r="U95" s="52"/>
-      <c r="V95" s="52"/>
-      <c r="W95" s="52"/>
-      <c r="X95" s="52"/>
-      <c r="Y95" s="52"/>
-      <c r="Z95" s="52"/>
-      <c r="AA95" s="52"/>
-      <c r="AB95" s="52"/>
-      <c r="AC95" s="52"/>
+      <c r="A95" s="52"/>
+      <c r="B95" s="54"/>
+      <c r="C95" s="55"/>
+      <c r="D95" s="56"/>
+      <c r="E95" s="56"/>
+      <c r="F95" s="51"/>
+      <c r="G95" s="51"/>
+      <c r="H95" s="51"/>
+      <c r="I95" s="51"/>
+      <c r="J95" s="51"/>
+      <c r="K95" s="51"/>
+      <c r="L95" s="51"/>
+      <c r="M95" s="51"/>
+      <c r="N95" s="51"/>
+      <c r="O95" s="51"/>
+      <c r="P95" s="51"/>
+      <c r="Q95" s="51"/>
+      <c r="R95" s="51"/>
+      <c r="S95" s="51"/>
+      <c r="T95" s="51"/>
+      <c r="U95" s="51"/>
+      <c r="V95" s="51"/>
+      <c r="W95" s="51"/>
+      <c r="X95" s="51"/>
+      <c r="Y95" s="51"/>
+      <c r="Z95" s="51"/>
+      <c r="AA95" s="51"/>
+      <c r="AB95" s="51"/>
+      <c r="AC95" s="51"/>
     </row>
     <row r="96" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="53"/>
-      <c r="B96" s="55"/>
-      <c r="C96" s="56"/>
-      <c r="D96" s="57"/>
-      <c r="E96" s="57"/>
-      <c r="F96" s="52"/>
-      <c r="G96" s="52"/>
-      <c r="H96" s="52"/>
-      <c r="I96" s="52"/>
-      <c r="J96" s="52"/>
-      <c r="K96" s="52"/>
-      <c r="L96" s="52"/>
-      <c r="M96" s="52"/>
-      <c r="N96" s="52"/>
-      <c r="O96" s="52"/>
-      <c r="P96" s="52"/>
-      <c r="Q96" s="52"/>
-      <c r="R96" s="52"/>
-      <c r="S96" s="52"/>
-      <c r="T96" s="52"/>
-      <c r="U96" s="52"/>
-      <c r="V96" s="52"/>
-      <c r="W96" s="52"/>
-      <c r="X96" s="52"/>
-      <c r="Y96" s="52"/>
-      <c r="Z96" s="52"/>
-      <c r="AA96" s="52"/>
-      <c r="AB96" s="52"/>
-      <c r="AC96" s="52"/>
+      <c r="A96" s="52"/>
+      <c r="B96" s="54"/>
+      <c r="C96" s="55"/>
+      <c r="D96" s="56"/>
+      <c r="E96" s="56"/>
+      <c r="F96" s="51"/>
+      <c r="G96" s="51"/>
+      <c r="H96" s="51"/>
+      <c r="I96" s="51"/>
+      <c r="J96" s="51"/>
+      <c r="K96" s="51"/>
+      <c r="L96" s="51"/>
+      <c r="M96" s="51"/>
+      <c r="N96" s="51"/>
+      <c r="O96" s="51"/>
+      <c r="P96" s="51"/>
+      <c r="Q96" s="51"/>
+      <c r="R96" s="51"/>
+      <c r="S96" s="51"/>
+      <c r="T96" s="51"/>
+      <c r="U96" s="51"/>
+      <c r="V96" s="51"/>
+      <c r="W96" s="51"/>
+      <c r="X96" s="51"/>
+      <c r="Y96" s="51"/>
+      <c r="Z96" s="51"/>
+      <c r="AA96" s="51"/>
+      <c r="AB96" s="51"/>
+      <c r="AC96" s="51"/>
     </row>
     <row r="97" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="53"/>
-      <c r="B97" s="55"/>
-      <c r="C97" s="56"/>
-      <c r="D97" s="57"/>
-      <c r="E97" s="57"/>
-      <c r="F97" s="52"/>
-      <c r="G97" s="52"/>
-      <c r="H97" s="52"/>
-      <c r="I97" s="52"/>
-      <c r="J97" s="52"/>
-      <c r="K97" s="52"/>
-      <c r="L97" s="52"/>
-      <c r="M97" s="52"/>
-      <c r="N97" s="52"/>
-      <c r="O97" s="52"/>
-      <c r="P97" s="52"/>
-      <c r="Q97" s="52"/>
-      <c r="R97" s="52"/>
-      <c r="S97" s="52"/>
-      <c r="T97" s="52"/>
-      <c r="U97" s="52"/>
-      <c r="V97" s="52"/>
-      <c r="W97" s="52"/>
-      <c r="X97" s="52"/>
-      <c r="Y97" s="52"/>
-      <c r="Z97" s="52"/>
-      <c r="AA97" s="52"/>
-      <c r="AB97" s="52"/>
-      <c r="AC97" s="52"/>
+      <c r="A97" s="52"/>
+      <c r="B97" s="54"/>
+      <c r="C97" s="55"/>
+      <c r="D97" s="56"/>
+      <c r="E97" s="56"/>
+      <c r="F97" s="51"/>
+      <c r="G97" s="51"/>
+      <c r="H97" s="51"/>
+      <c r="I97" s="51"/>
+      <c r="J97" s="51"/>
+      <c r="K97" s="51"/>
+      <c r="L97" s="51"/>
+      <c r="M97" s="51"/>
+      <c r="N97" s="51"/>
+      <c r="O97" s="51"/>
+      <c r="P97" s="51"/>
+      <c r="Q97" s="51"/>
+      <c r="R97" s="51"/>
+      <c r="S97" s="51"/>
+      <c r="T97" s="51"/>
+      <c r="U97" s="51"/>
+      <c r="V97" s="51"/>
+      <c r="W97" s="51"/>
+      <c r="X97" s="51"/>
+      <c r="Y97" s="51"/>
+      <c r="Z97" s="51"/>
+      <c r="AA97" s="51"/>
+      <c r="AB97" s="51"/>
+      <c r="AC97" s="51"/>
     </row>
     <row r="98" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="53"/>
-      <c r="B98" s="55"/>
-      <c r="C98" s="56"/>
-      <c r="D98" s="57"/>
-      <c r="E98" s="57"/>
-      <c r="F98" s="52"/>
-      <c r="G98" s="52"/>
-      <c r="H98" s="52"/>
-      <c r="I98" s="52"/>
-      <c r="J98" s="52"/>
-      <c r="K98" s="52"/>
-      <c r="L98" s="52"/>
-      <c r="M98" s="52"/>
-      <c r="N98" s="52"/>
-      <c r="O98" s="52"/>
-      <c r="P98" s="52"/>
-      <c r="Q98" s="52"/>
-      <c r="R98" s="52"/>
-      <c r="S98" s="52"/>
-      <c r="T98" s="52"/>
-      <c r="U98" s="52"/>
-      <c r="V98" s="52"/>
-      <c r="W98" s="52"/>
-      <c r="X98" s="52"/>
-      <c r="Y98" s="52"/>
-      <c r="Z98" s="52"/>
-      <c r="AA98" s="52"/>
-      <c r="AB98" s="52"/>
-      <c r="AC98" s="52"/>
+      <c r="A98" s="52"/>
+      <c r="B98" s="54"/>
+      <c r="C98" s="55"/>
+      <c r="D98" s="56"/>
+      <c r="E98" s="56"/>
+      <c r="F98" s="51"/>
+      <c r="G98" s="51"/>
+      <c r="H98" s="51"/>
+      <c r="I98" s="51"/>
+      <c r="J98" s="51"/>
+      <c r="K98" s="51"/>
+      <c r="L98" s="51"/>
+      <c r="M98" s="51"/>
+      <c r="N98" s="51"/>
+      <c r="O98" s="51"/>
+      <c r="P98" s="51"/>
+      <c r="Q98" s="51"/>
+      <c r="R98" s="51"/>
+      <c r="S98" s="51"/>
+      <c r="T98" s="51"/>
+      <c r="U98" s="51"/>
+      <c r="V98" s="51"/>
+      <c r="W98" s="51"/>
+      <c r="X98" s="51"/>
+      <c r="Y98" s="51"/>
+      <c r="Z98" s="51"/>
+      <c r="AA98" s="51"/>
+      <c r="AB98" s="51"/>
+      <c r="AC98" s="51"/>
     </row>
     <row r="99" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="53"/>
-      <c r="B99" s="54"/>
-      <c r="C99" s="54"/>
-      <c r="D99" s="54"/>
-      <c r="E99" s="54"/>
-      <c r="F99" s="52"/>
-      <c r="G99" s="52"/>
-      <c r="H99" s="52"/>
-      <c r="I99" s="52"/>
-      <c r="J99" s="52"/>
-      <c r="K99" s="52"/>
-      <c r="L99" s="52"/>
-      <c r="M99" s="52"/>
-      <c r="N99" s="52"/>
-      <c r="O99" s="52"/>
-      <c r="P99" s="52"/>
-      <c r="Q99" s="52"/>
-      <c r="R99" s="52"/>
-      <c r="S99" s="52"/>
-      <c r="T99" s="52"/>
-      <c r="U99" s="52"/>
-      <c r="V99" s="52"/>
-      <c r="W99" s="52"/>
-      <c r="X99" s="52"/>
-      <c r="Y99" s="52"/>
-      <c r="Z99" s="52"/>
-      <c r="AA99" s="52"/>
-      <c r="AB99" s="52"/>
-      <c r="AC99" s="52"/>
+      <c r="A99" s="52"/>
+      <c r="B99" s="53"/>
+      <c r="C99" s="53"/>
+      <c r="D99" s="53"/>
+      <c r="E99" s="53"/>
+      <c r="F99" s="51"/>
+      <c r="G99" s="51"/>
+      <c r="H99" s="51"/>
+      <c r="I99" s="51"/>
+      <c r="J99" s="51"/>
+      <c r="K99" s="51"/>
+      <c r="L99" s="51"/>
+      <c r="M99" s="51"/>
+      <c r="N99" s="51"/>
+      <c r="O99" s="51"/>
+      <c r="P99" s="51"/>
+      <c r="Q99" s="51"/>
+      <c r="R99" s="51"/>
+      <c r="S99" s="51"/>
+      <c r="T99" s="51"/>
+      <c r="U99" s="51"/>
+      <c r="V99" s="51"/>
+      <c r="W99" s="51"/>
+      <c r="X99" s="51"/>
+      <c r="Y99" s="51"/>
+      <c r="Z99" s="51"/>
+      <c r="AA99" s="51"/>
+      <c r="AB99" s="51"/>
+      <c r="AC99" s="51"/>
     </row>
     <row r="100" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="53"/>
-      <c r="B100" s="54"/>
-      <c r="C100" s="55"/>
-      <c r="D100" s="55"/>
-      <c r="E100" s="55"/>
-      <c r="F100" s="58"/>
-      <c r="G100" s="58"/>
-      <c r="H100" s="58"/>
-      <c r="I100" s="58"/>
-      <c r="J100" s="58"/>
-      <c r="K100" s="58"/>
-      <c r="L100" s="58"/>
-      <c r="M100" s="58"/>
-      <c r="N100" s="58"/>
-      <c r="O100" s="58"/>
-      <c r="P100" s="58"/>
-      <c r="Q100" s="58"/>
-      <c r="R100" s="58"/>
-      <c r="S100" s="58"/>
-      <c r="T100" s="58"/>
-      <c r="U100" s="52"/>
-      <c r="V100" s="52"/>
-      <c r="W100" s="52"/>
-      <c r="X100" s="52"/>
-      <c r="Y100" s="52"/>
-      <c r="Z100" s="52"/>
-      <c r="AA100" s="52"/>
-      <c r="AB100" s="52"/>
-      <c r="AC100" s="52"/>
+      <c r="A100" s="52"/>
+      <c r="B100" s="53"/>
+      <c r="C100" s="54"/>
+      <c r="D100" s="54"/>
+      <c r="E100" s="54"/>
+      <c r="F100" s="57"/>
+      <c r="G100" s="57"/>
+      <c r="H100" s="57"/>
+      <c r="I100" s="57"/>
+      <c r="J100" s="57"/>
+      <c r="K100" s="57"/>
+      <c r="L100" s="57"/>
+      <c r="M100" s="57"/>
+      <c r="N100" s="57"/>
+      <c r="O100" s="57"/>
+      <c r="P100" s="57"/>
+      <c r="Q100" s="57"/>
+      <c r="R100" s="57"/>
+      <c r="S100" s="57"/>
+      <c r="T100" s="57"/>
+      <c r="U100" s="51"/>
+      <c r="V100" s="51"/>
+      <c r="W100" s="51"/>
+      <c r="X100" s="51"/>
+      <c r="Y100" s="51"/>
+      <c r="Z100" s="51"/>
+      <c r="AA100" s="51"/>
+      <c r="AB100" s="51"/>
+      <c r="AC100" s="51"/>
     </row>
     <row r="101" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="53"/>
-      <c r="B101" s="54"/>
-      <c r="C101" s="56"/>
-      <c r="D101" s="56"/>
-      <c r="E101" s="56"/>
-      <c r="F101" s="58"/>
-      <c r="G101" s="58"/>
-      <c r="H101" s="58"/>
-      <c r="I101" s="58"/>
-      <c r="J101" s="58"/>
-      <c r="K101" s="58"/>
-      <c r="L101" s="58"/>
-      <c r="M101" s="58"/>
-      <c r="N101" s="58"/>
-      <c r="O101" s="58"/>
-      <c r="P101" s="58"/>
-      <c r="Q101" s="58"/>
-      <c r="R101" s="58"/>
-      <c r="S101" s="58"/>
-      <c r="T101" s="58"/>
-      <c r="U101" s="52"/>
-      <c r="V101" s="52"/>
-      <c r="W101" s="52"/>
-      <c r="X101" s="52"/>
-      <c r="Y101" s="52"/>
-      <c r="Z101" s="52"/>
-      <c r="AA101" s="52"/>
-      <c r="AB101" s="52"/>
-      <c r="AC101" s="52"/>
+      <c r="A101" s="52"/>
+      <c r="B101" s="53"/>
+      <c r="C101" s="55"/>
+      <c r="D101" s="55"/>
+      <c r="E101" s="55"/>
+      <c r="F101" s="57"/>
+      <c r="G101" s="57"/>
+      <c r="H101" s="57"/>
+      <c r="I101" s="57"/>
+      <c r="J101" s="57"/>
+      <c r="K101" s="57"/>
+      <c r="L101" s="57"/>
+      <c r="M101" s="57"/>
+      <c r="N101" s="57"/>
+      <c r="O101" s="57"/>
+      <c r="P101" s="57"/>
+      <c r="Q101" s="57"/>
+      <c r="R101" s="57"/>
+      <c r="S101" s="57"/>
+      <c r="T101" s="57"/>
+      <c r="U101" s="51"/>
+      <c r="V101" s="51"/>
+      <c r="W101" s="51"/>
+      <c r="X101" s="51"/>
+      <c r="Y101" s="51"/>
+      <c r="Z101" s="51"/>
+      <c r="AA101" s="51"/>
+      <c r="AB101" s="51"/>
+      <c r="AC101" s="51"/>
     </row>
     <row r="102" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="53"/>
-      <c r="B102" s="54"/>
-      <c r="C102" s="56"/>
-      <c r="D102" s="56"/>
-      <c r="E102" s="56"/>
-      <c r="F102" s="58"/>
-      <c r="G102" s="58"/>
-      <c r="H102" s="58"/>
-      <c r="I102" s="58"/>
-      <c r="J102" s="58"/>
-      <c r="K102" s="58"/>
-      <c r="L102" s="58"/>
-      <c r="M102" s="58"/>
-      <c r="N102" s="58"/>
-      <c r="O102" s="58"/>
-      <c r="P102" s="58"/>
-      <c r="Q102" s="58"/>
-      <c r="R102" s="58"/>
-      <c r="S102" s="58"/>
-      <c r="T102" s="58"/>
-      <c r="U102" s="52"/>
-      <c r="V102" s="52"/>
-      <c r="W102" s="52"/>
-      <c r="X102" s="52"/>
-      <c r="Y102" s="52"/>
-      <c r="Z102" s="52"/>
-      <c r="AA102" s="52"/>
-      <c r="AB102" s="52"/>
-      <c r="AC102" s="52"/>
+      <c r="A102" s="52"/>
+      <c r="B102" s="53"/>
+      <c r="C102" s="55"/>
+      <c r="D102" s="55"/>
+      <c r="E102" s="55"/>
+      <c r="F102" s="57"/>
+      <c r="G102" s="57"/>
+      <c r="H102" s="57"/>
+      <c r="I102" s="57"/>
+      <c r="J102" s="57"/>
+      <c r="K102" s="57"/>
+      <c r="L102" s="57"/>
+      <c r="M102" s="57"/>
+      <c r="N102" s="57"/>
+      <c r="O102" s="57"/>
+      <c r="P102" s="57"/>
+      <c r="Q102" s="57"/>
+      <c r="R102" s="57"/>
+      <c r="S102" s="57"/>
+      <c r="T102" s="57"/>
+      <c r="U102" s="51"/>
+      <c r="V102" s="51"/>
+      <c r="W102" s="51"/>
+      <c r="X102" s="51"/>
+      <c r="Y102" s="51"/>
+      <c r="Z102" s="51"/>
+      <c r="AA102" s="51"/>
+      <c r="AB102" s="51"/>
+      <c r="AC102" s="51"/>
     </row>
     <row r="103" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="53"/>
-      <c r="B103" s="54"/>
-      <c r="C103" s="56"/>
-      <c r="D103" s="56"/>
-      <c r="E103" s="56"/>
-      <c r="F103" s="58"/>
-      <c r="G103" s="58"/>
-      <c r="H103" s="58"/>
-      <c r="I103" s="58"/>
-      <c r="J103" s="58"/>
-      <c r="K103" s="58"/>
-      <c r="L103" s="58"/>
-      <c r="M103" s="58"/>
-      <c r="N103" s="58"/>
-      <c r="O103" s="58"/>
-      <c r="P103" s="58"/>
-      <c r="Q103" s="58"/>
-      <c r="R103" s="58"/>
-      <c r="S103" s="58"/>
-      <c r="T103" s="58"/>
-      <c r="U103" s="52"/>
-      <c r="V103" s="52"/>
-      <c r="W103" s="52"/>
-      <c r="X103" s="52"/>
-      <c r="Y103" s="52"/>
-      <c r="Z103" s="52"/>
-      <c r="AA103" s="52"/>
-      <c r="AB103" s="52"/>
-      <c r="AC103" s="52"/>
+      <c r="A103" s="52"/>
+      <c r="B103" s="53"/>
+      <c r="C103" s="55"/>
+      <c r="D103" s="55"/>
+      <c r="E103" s="55"/>
+      <c r="F103" s="57"/>
+      <c r="G103" s="57"/>
+      <c r="H103" s="57"/>
+      <c r="I103" s="57"/>
+      <c r="J103" s="57"/>
+      <c r="K103" s="57"/>
+      <c r="L103" s="57"/>
+      <c r="M103" s="57"/>
+      <c r="N103" s="57"/>
+      <c r="O103" s="57"/>
+      <c r="P103" s="57"/>
+      <c r="Q103" s="57"/>
+      <c r="R103" s="57"/>
+      <c r="S103" s="57"/>
+      <c r="T103" s="57"/>
+      <c r="U103" s="51"/>
+      <c r="V103" s="51"/>
+      <c r="W103" s="51"/>
+      <c r="X103" s="51"/>
+      <c r="Y103" s="51"/>
+      <c r="Z103" s="51"/>
+      <c r="AA103" s="51"/>
+      <c r="AB103" s="51"/>
+      <c r="AC103" s="51"/>
     </row>
     <row r="104" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="53"/>
-      <c r="B104" s="54"/>
-      <c r="C104" s="56"/>
-      <c r="D104" s="56"/>
-      <c r="E104" s="56"/>
-      <c r="F104" s="58"/>
-      <c r="G104" s="58"/>
-      <c r="H104" s="58"/>
-      <c r="I104" s="58"/>
-      <c r="J104" s="58"/>
-      <c r="K104" s="58"/>
-      <c r="L104" s="58"/>
-      <c r="M104" s="58"/>
-      <c r="N104" s="58"/>
-      <c r="O104" s="58"/>
-      <c r="P104" s="58"/>
-      <c r="Q104" s="58"/>
-      <c r="R104" s="58"/>
-      <c r="S104" s="58"/>
-      <c r="T104" s="58"/>
-      <c r="U104" s="52"/>
-      <c r="V104" s="52"/>
-      <c r="W104" s="52"/>
-      <c r="X104" s="52"/>
-      <c r="Y104" s="52"/>
-      <c r="Z104" s="52"/>
-      <c r="AA104" s="52"/>
-      <c r="AB104" s="52"/>
-      <c r="AC104" s="52"/>
+      <c r="A104" s="52"/>
+      <c r="B104" s="53"/>
+      <c r="C104" s="55"/>
+      <c r="D104" s="55"/>
+      <c r="E104" s="55"/>
+      <c r="F104" s="57"/>
+      <c r="G104" s="57"/>
+      <c r="H104" s="57"/>
+      <c r="I104" s="57"/>
+      <c r="J104" s="57"/>
+      <c r="K104" s="57"/>
+      <c r="L104" s="57"/>
+      <c r="M104" s="57"/>
+      <c r="N104" s="57"/>
+      <c r="O104" s="57"/>
+      <c r="P104" s="57"/>
+      <c r="Q104" s="57"/>
+      <c r="R104" s="57"/>
+      <c r="S104" s="57"/>
+      <c r="T104" s="57"/>
+      <c r="U104" s="51"/>
+      <c r="V104" s="51"/>
+      <c r="W104" s="51"/>
+      <c r="X104" s="51"/>
+      <c r="Y104" s="51"/>
+      <c r="Z104" s="51"/>
+      <c r="AA104" s="51"/>
+      <c r="AB104" s="51"/>
+      <c r="AC104" s="51"/>
     </row>
     <row r="105" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="53"/>
-      <c r="B105" s="54"/>
-      <c r="C105" s="56"/>
-      <c r="D105" s="56"/>
-      <c r="E105" s="56"/>
-      <c r="F105" s="58"/>
-      <c r="G105" s="58"/>
-      <c r="H105" s="58"/>
-      <c r="I105" s="58"/>
-      <c r="J105" s="58"/>
-      <c r="K105" s="58"/>
-      <c r="L105" s="58"/>
-      <c r="M105" s="58"/>
-      <c r="N105" s="58"/>
-      <c r="O105" s="58"/>
-      <c r="P105" s="58"/>
-      <c r="Q105" s="58"/>
-      <c r="R105" s="58"/>
-      <c r="S105" s="58"/>
-      <c r="T105" s="58"/>
-      <c r="U105" s="52"/>
-      <c r="V105" s="52"/>
-      <c r="W105" s="52"/>
-      <c r="X105" s="52"/>
-      <c r="Y105" s="52"/>
-      <c r="Z105" s="52"/>
-      <c r="AA105" s="52"/>
-      <c r="AB105" s="52"/>
-      <c r="AC105" s="52"/>
+      <c r="A105" s="52"/>
+      <c r="B105" s="53"/>
+      <c r="C105" s="55"/>
+      <c r="D105" s="55"/>
+      <c r="E105" s="55"/>
+      <c r="F105" s="57"/>
+      <c r="G105" s="57"/>
+      <c r="H105" s="57"/>
+      <c r="I105" s="57"/>
+      <c r="J105" s="57"/>
+      <c r="K105" s="57"/>
+      <c r="L105" s="57"/>
+      <c r="M105" s="57"/>
+      <c r="N105" s="57"/>
+      <c r="O105" s="57"/>
+      <c r="P105" s="57"/>
+      <c r="Q105" s="57"/>
+      <c r="R105" s="57"/>
+      <c r="S105" s="57"/>
+      <c r="T105" s="57"/>
+      <c r="U105" s="51"/>
+      <c r="V105" s="51"/>
+      <c r="W105" s="51"/>
+      <c r="X105" s="51"/>
+      <c r="Y105" s="51"/>
+      <c r="Z105" s="51"/>
+      <c r="AA105" s="51"/>
+      <c r="AB105" s="51"/>
+      <c r="AC105" s="51"/>
     </row>
     <row r="106" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="53"/>
-      <c r="B106" s="54"/>
-      <c r="C106" s="56"/>
-      <c r="D106" s="56"/>
-      <c r="E106" s="56"/>
-      <c r="F106" s="58"/>
-      <c r="G106" s="58"/>
-      <c r="H106" s="58"/>
-      <c r="I106" s="58"/>
-      <c r="J106" s="58"/>
-      <c r="K106" s="58"/>
-      <c r="L106" s="58"/>
-      <c r="M106" s="58"/>
-      <c r="N106" s="58"/>
-      <c r="O106" s="58"/>
-      <c r="P106" s="58"/>
-      <c r="Q106" s="58"/>
-      <c r="R106" s="58"/>
-      <c r="S106" s="58"/>
-      <c r="T106" s="58"/>
-      <c r="U106" s="52"/>
-      <c r="V106" s="52"/>
-      <c r="W106" s="52"/>
-      <c r="X106" s="52"/>
-      <c r="Y106" s="52"/>
-      <c r="Z106" s="52"/>
-      <c r="AA106" s="52"/>
-      <c r="AB106" s="52"/>
-      <c r="AC106" s="52"/>
+      <c r="A106" s="52"/>
+      <c r="B106" s="53"/>
+      <c r="C106" s="55"/>
+      <c r="D106" s="55"/>
+      <c r="E106" s="55"/>
+      <c r="F106" s="57"/>
+      <c r="G106" s="57"/>
+      <c r="H106" s="57"/>
+      <c r="I106" s="57"/>
+      <c r="J106" s="57"/>
+      <c r="K106" s="57"/>
+      <c r="L106" s="57"/>
+      <c r="M106" s="57"/>
+      <c r="N106" s="57"/>
+      <c r="O106" s="57"/>
+      <c r="P106" s="57"/>
+      <c r="Q106" s="57"/>
+      <c r="R106" s="57"/>
+      <c r="S106" s="57"/>
+      <c r="T106" s="57"/>
+      <c r="U106" s="51"/>
+      <c r="V106" s="51"/>
+      <c r="W106" s="51"/>
+      <c r="X106" s="51"/>
+      <c r="Y106" s="51"/>
+      <c r="Z106" s="51"/>
+      <c r="AA106" s="51"/>
+      <c r="AB106" s="51"/>
+      <c r="AC106" s="51"/>
     </row>
     <row r="107" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="53"/>
-      <c r="B107" s="54"/>
-      <c r="C107" s="56"/>
-      <c r="D107" s="56"/>
-      <c r="E107" s="56"/>
-      <c r="F107" s="58"/>
-      <c r="G107" s="58"/>
-      <c r="H107" s="58"/>
-      <c r="I107" s="58"/>
-      <c r="J107" s="58"/>
-      <c r="K107" s="58"/>
-      <c r="L107" s="58"/>
-      <c r="M107" s="58"/>
-      <c r="N107" s="58"/>
-      <c r="O107" s="58"/>
-      <c r="P107" s="58"/>
-      <c r="Q107" s="58"/>
-      <c r="R107" s="58"/>
-      <c r="S107" s="58"/>
-      <c r="T107" s="58"/>
-      <c r="U107" s="52"/>
-      <c r="V107" s="52"/>
-      <c r="W107" s="52"/>
-      <c r="X107" s="52"/>
-      <c r="Y107" s="52"/>
-      <c r="Z107" s="52"/>
-      <c r="AA107" s="52"/>
-      <c r="AB107" s="52"/>
-      <c r="AC107" s="52"/>
+      <c r="A107" s="52"/>
+      <c r="B107" s="53"/>
+      <c r="C107" s="55"/>
+      <c r="D107" s="55"/>
+      <c r="E107" s="55"/>
+      <c r="F107" s="57"/>
+      <c r="G107" s="57"/>
+      <c r="H107" s="57"/>
+      <c r="I107" s="57"/>
+      <c r="J107" s="57"/>
+      <c r="K107" s="57"/>
+      <c r="L107" s="57"/>
+      <c r="M107" s="57"/>
+      <c r="N107" s="57"/>
+      <c r="O107" s="57"/>
+      <c r="P107" s="57"/>
+      <c r="Q107" s="57"/>
+      <c r="R107" s="57"/>
+      <c r="S107" s="57"/>
+      <c r="T107" s="57"/>
+      <c r="U107" s="51"/>
+      <c r="V107" s="51"/>
+      <c r="W107" s="51"/>
+      <c r="X107" s="51"/>
+      <c r="Y107" s="51"/>
+      <c r="Z107" s="51"/>
+      <c r="AA107" s="51"/>
+      <c r="AB107" s="51"/>
+      <c r="AC107" s="51"/>
     </row>
     <row r="108" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="53"/>
-      <c r="B108" s="54"/>
-      <c r="C108" s="56"/>
-      <c r="D108" s="56"/>
-      <c r="E108" s="56"/>
-      <c r="F108" s="58"/>
-      <c r="G108" s="58"/>
-      <c r="H108" s="58"/>
-      <c r="I108" s="58"/>
-      <c r="J108" s="58"/>
-      <c r="K108" s="58"/>
-      <c r="L108" s="58"/>
-      <c r="M108" s="58"/>
-      <c r="N108" s="58"/>
-      <c r="O108" s="58"/>
-      <c r="P108" s="58"/>
-      <c r="Q108" s="58"/>
-      <c r="R108" s="58"/>
-      <c r="S108" s="58"/>
-      <c r="T108" s="58"/>
-      <c r="U108" s="52"/>
-      <c r="V108" s="52"/>
-      <c r="W108" s="52"/>
-      <c r="X108" s="52"/>
-      <c r="Y108" s="52"/>
-      <c r="Z108" s="52"/>
-      <c r="AA108" s="52"/>
-      <c r="AB108" s="52"/>
-      <c r="AC108" s="52"/>
+      <c r="A108" s="52"/>
+      <c r="B108" s="53"/>
+      <c r="C108" s="55"/>
+      <c r="D108" s="55"/>
+      <c r="E108" s="55"/>
+      <c r="F108" s="57"/>
+      <c r="G108" s="57"/>
+      <c r="H108" s="57"/>
+      <c r="I108" s="57"/>
+      <c r="J108" s="57"/>
+      <c r="K108" s="57"/>
+      <c r="L108" s="57"/>
+      <c r="M108" s="57"/>
+      <c r="N108" s="57"/>
+      <c r="O108" s="57"/>
+      <c r="P108" s="57"/>
+      <c r="Q108" s="57"/>
+      <c r="R108" s="57"/>
+      <c r="S108" s="57"/>
+      <c r="T108" s="57"/>
+      <c r="U108" s="51"/>
+      <c r="V108" s="51"/>
+      <c r="W108" s="51"/>
+      <c r="X108" s="51"/>
+      <c r="Y108" s="51"/>
+      <c r="Z108" s="51"/>
+      <c r="AA108" s="51"/>
+      <c r="AB108" s="51"/>
+      <c r="AC108" s="51"/>
     </row>
     <row r="109" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="53"/>
-      <c r="B109" s="54"/>
-      <c r="C109" s="54"/>
-      <c r="D109" s="54"/>
-      <c r="E109" s="54"/>
-      <c r="F109" s="58"/>
-      <c r="G109" s="58"/>
-      <c r="H109" s="58"/>
-      <c r="I109" s="58"/>
-      <c r="J109" s="58"/>
-      <c r="K109" s="58"/>
-      <c r="L109" s="58"/>
-      <c r="M109" s="58"/>
-      <c r="N109" s="58"/>
-      <c r="O109" s="58"/>
-      <c r="P109" s="58"/>
-      <c r="Q109" s="58"/>
-      <c r="R109" s="58"/>
-      <c r="S109" s="58"/>
-      <c r="T109" s="58"/>
-      <c r="U109" s="52"/>
-      <c r="V109" s="52"/>
-      <c r="W109" s="52"/>
-      <c r="X109" s="52"/>
-      <c r="Y109" s="52"/>
-      <c r="Z109" s="52"/>
-      <c r="AA109" s="52"/>
-      <c r="AB109" s="52"/>
-      <c r="AC109" s="52"/>
+      <c r="A109" s="52"/>
+      <c r="B109" s="53"/>
+      <c r="C109" s="53"/>
+      <c r="D109" s="53"/>
+      <c r="E109" s="53"/>
+      <c r="F109" s="57"/>
+      <c r="G109" s="57"/>
+      <c r="H109" s="57"/>
+      <c r="I109" s="57"/>
+      <c r="J109" s="57"/>
+      <c r="K109" s="57"/>
+      <c r="L109" s="57"/>
+      <c r="M109" s="57"/>
+      <c r="N109" s="57"/>
+      <c r="O109" s="57"/>
+      <c r="P109" s="57"/>
+      <c r="Q109" s="57"/>
+      <c r="R109" s="57"/>
+      <c r="S109" s="57"/>
+      <c r="T109" s="57"/>
+      <c r="U109" s="51"/>
+      <c r="V109" s="51"/>
+      <c r="W109" s="51"/>
+      <c r="X109" s="51"/>
+      <c r="Y109" s="51"/>
+      <c r="Z109" s="51"/>
+      <c r="AA109" s="51"/>
+      <c r="AB109" s="51"/>
+      <c r="AC109" s="51"/>
     </row>
     <row r="110" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="53"/>
-      <c r="B110" s="54"/>
-      <c r="C110" s="55"/>
-      <c r="D110" s="55"/>
-      <c r="E110" s="55"/>
-      <c r="F110" s="58"/>
-      <c r="G110" s="58"/>
-      <c r="H110" s="58"/>
-      <c r="I110" s="58"/>
-      <c r="J110" s="58"/>
-      <c r="K110" s="58"/>
-      <c r="L110" s="58"/>
-      <c r="M110" s="58"/>
-      <c r="N110" s="58"/>
-      <c r="O110" s="58"/>
-      <c r="P110" s="58"/>
-      <c r="Q110" s="58"/>
-      <c r="R110" s="58"/>
-      <c r="S110" s="58"/>
-      <c r="T110" s="58"/>
-      <c r="U110" s="52"/>
-      <c r="V110" s="52"/>
-      <c r="W110" s="52"/>
-      <c r="X110" s="52"/>
-      <c r="Y110" s="52"/>
-      <c r="Z110" s="52"/>
-      <c r="AA110" s="52"/>
-      <c r="AB110" s="52"/>
-      <c r="AC110" s="52"/>
+      <c r="A110" s="52"/>
+      <c r="B110" s="53"/>
+      <c r="C110" s="54"/>
+      <c r="D110" s="54"/>
+      <c r="E110" s="54"/>
+      <c r="F110" s="57"/>
+      <c r="G110" s="57"/>
+      <c r="H110" s="57"/>
+      <c r="I110" s="57"/>
+      <c r="J110" s="57"/>
+      <c r="K110" s="57"/>
+      <c r="L110" s="57"/>
+      <c r="M110" s="57"/>
+      <c r="N110" s="57"/>
+      <c r="O110" s="57"/>
+      <c r="P110" s="57"/>
+      <c r="Q110" s="57"/>
+      <c r="R110" s="57"/>
+      <c r="S110" s="57"/>
+      <c r="T110" s="57"/>
+      <c r="U110" s="51"/>
+      <c r="V110" s="51"/>
+      <c r="W110" s="51"/>
+      <c r="X110" s="51"/>
+      <c r="Y110" s="51"/>
+      <c r="Z110" s="51"/>
+      <c r="AA110" s="51"/>
+      <c r="AB110" s="51"/>
+      <c r="AC110" s="51"/>
     </row>
     <row r="111" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="53"/>
-      <c r="B111" s="54"/>
-      <c r="C111" s="56"/>
-      <c r="D111" s="56"/>
-      <c r="E111" s="56"/>
-      <c r="F111" s="58"/>
-      <c r="G111" s="58"/>
-      <c r="H111" s="58"/>
-      <c r="I111" s="58"/>
-      <c r="J111" s="58"/>
-      <c r="K111" s="58"/>
-      <c r="L111" s="58"/>
-      <c r="M111" s="58"/>
-      <c r="N111" s="58"/>
-      <c r="O111" s="58"/>
-      <c r="P111" s="58"/>
-      <c r="Q111" s="58"/>
-      <c r="R111" s="58"/>
-      <c r="S111" s="58"/>
-      <c r="T111" s="58"/>
-      <c r="U111" s="52"/>
-      <c r="V111" s="52"/>
-      <c r="W111" s="52"/>
-      <c r="X111" s="52"/>
-      <c r="Y111" s="52"/>
-      <c r="Z111" s="52"/>
-      <c r="AA111" s="52"/>
-      <c r="AB111" s="52"/>
-      <c r="AC111" s="52"/>
+      <c r="A111" s="52"/>
+      <c r="B111" s="53"/>
+      <c r="C111" s="55"/>
+      <c r="D111" s="55"/>
+      <c r="E111" s="55"/>
+      <c r="F111" s="57"/>
+      <c r="G111" s="57"/>
+      <c r="H111" s="57"/>
+      <c r="I111" s="57"/>
+      <c r="J111" s="57"/>
+      <c r="K111" s="57"/>
+      <c r="L111" s="57"/>
+      <c r="M111" s="57"/>
+      <c r="N111" s="57"/>
+      <c r="O111" s="57"/>
+      <c r="P111" s="57"/>
+      <c r="Q111" s="57"/>
+      <c r="R111" s="57"/>
+      <c r="S111" s="57"/>
+      <c r="T111" s="57"/>
+      <c r="U111" s="51"/>
+      <c r="V111" s="51"/>
+      <c r="W111" s="51"/>
+      <c r="X111" s="51"/>
+      <c r="Y111" s="51"/>
+      <c r="Z111" s="51"/>
+      <c r="AA111" s="51"/>
+      <c r="AB111" s="51"/>
+      <c r="AC111" s="51"/>
     </row>
     <row r="112" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="53"/>
-      <c r="B112" s="54"/>
-      <c r="C112" s="56"/>
-      <c r="D112" s="56"/>
-      <c r="E112" s="56"/>
-      <c r="F112" s="58"/>
-      <c r="G112" s="58"/>
-      <c r="H112" s="58"/>
-      <c r="I112" s="58"/>
-      <c r="J112" s="58"/>
-      <c r="K112" s="58"/>
-      <c r="L112" s="58"/>
-      <c r="M112" s="58"/>
-      <c r="N112" s="58"/>
-      <c r="O112" s="58"/>
-      <c r="P112" s="58"/>
-      <c r="Q112" s="58"/>
-      <c r="R112" s="58"/>
-      <c r="S112" s="58"/>
-      <c r="T112" s="58"/>
-      <c r="U112" s="52"/>
-      <c r="V112" s="52"/>
-      <c r="W112" s="52"/>
-      <c r="X112" s="52"/>
-      <c r="Y112" s="52"/>
-      <c r="Z112" s="52"/>
-      <c r="AA112" s="52"/>
-      <c r="AB112" s="52"/>
-      <c r="AC112" s="52"/>
+      <c r="A112" s="52"/>
+      <c r="B112" s="53"/>
+      <c r="C112" s="55"/>
+      <c r="D112" s="55"/>
+      <c r="E112" s="55"/>
+      <c r="F112" s="57"/>
+      <c r="G112" s="57"/>
+      <c r="H112" s="57"/>
+      <c r="I112" s="57"/>
+      <c r="J112" s="57"/>
+      <c r="K112" s="57"/>
+      <c r="L112" s="57"/>
+      <c r="M112" s="57"/>
+      <c r="N112" s="57"/>
+      <c r="O112" s="57"/>
+      <c r="P112" s="57"/>
+      <c r="Q112" s="57"/>
+      <c r="R112" s="57"/>
+      <c r="S112" s="57"/>
+      <c r="T112" s="57"/>
+      <c r="U112" s="51"/>
+      <c r="V112" s="51"/>
+      <c r="W112" s="51"/>
+      <c r="X112" s="51"/>
+      <c r="Y112" s="51"/>
+      <c r="Z112" s="51"/>
+      <c r="AA112" s="51"/>
+      <c r="AB112" s="51"/>
+      <c r="AC112" s="51"/>
     </row>
     <row r="113" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="53"/>
-      <c r="B113" s="54"/>
-      <c r="C113" s="56"/>
-      <c r="D113" s="56"/>
-      <c r="E113" s="56"/>
-      <c r="F113" s="58"/>
-      <c r="G113" s="58"/>
-      <c r="H113" s="58"/>
-      <c r="I113" s="58"/>
-      <c r="J113" s="58"/>
-      <c r="K113" s="58"/>
-      <c r="L113" s="58"/>
-      <c r="M113" s="58"/>
-      <c r="N113" s="58"/>
-      <c r="O113" s="58"/>
-      <c r="P113" s="58"/>
-      <c r="Q113" s="58"/>
-      <c r="R113" s="58"/>
-      <c r="S113" s="58"/>
-      <c r="T113" s="58"/>
-      <c r="U113" s="52"/>
-      <c r="V113" s="52"/>
-      <c r="W113" s="52"/>
-      <c r="X113" s="52"/>
-      <c r="Y113" s="52"/>
-      <c r="Z113" s="52"/>
-      <c r="AA113" s="52"/>
-      <c r="AB113" s="52"/>
-      <c r="AC113" s="52"/>
+      <c r="A113" s="52"/>
+      <c r="B113" s="53"/>
+      <c r="C113" s="55"/>
+      <c r="D113" s="55"/>
+      <c r="E113" s="55"/>
+      <c r="F113" s="57"/>
+      <c r="G113" s="57"/>
+      <c r="H113" s="57"/>
+      <c r="I113" s="57"/>
+      <c r="J113" s="57"/>
+      <c r="K113" s="57"/>
+      <c r="L113" s="57"/>
+      <c r="M113" s="57"/>
+      <c r="N113" s="57"/>
+      <c r="O113" s="57"/>
+      <c r="P113" s="57"/>
+      <c r="Q113" s="57"/>
+      <c r="R113" s="57"/>
+      <c r="S113" s="57"/>
+      <c r="T113" s="57"/>
+      <c r="U113" s="51"/>
+      <c r="V113" s="51"/>
+      <c r="W113" s="51"/>
+      <c r="X113" s="51"/>
+      <c r="Y113" s="51"/>
+      <c r="Z113" s="51"/>
+      <c r="AA113" s="51"/>
+      <c r="AB113" s="51"/>
+      <c r="AC113" s="51"/>
     </row>
     <row r="114" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="53"/>
-      <c r="B114" s="54"/>
-      <c r="C114" s="56"/>
-      <c r="D114" s="56"/>
-      <c r="E114" s="56"/>
-      <c r="F114" s="58"/>
-      <c r="G114" s="58"/>
-      <c r="H114" s="58"/>
-      <c r="I114" s="58"/>
-      <c r="J114" s="58"/>
-      <c r="K114" s="58"/>
-      <c r="L114" s="58"/>
-      <c r="M114" s="58"/>
-      <c r="N114" s="58"/>
-      <c r="O114" s="58"/>
-      <c r="P114" s="58"/>
-      <c r="Q114" s="58"/>
-      <c r="R114" s="58"/>
-      <c r="S114" s="58"/>
-      <c r="T114" s="58"/>
-      <c r="U114" s="52"/>
-      <c r="V114" s="52"/>
-      <c r="W114" s="52"/>
-      <c r="X114" s="52"/>
-      <c r="Y114" s="52"/>
-      <c r="Z114" s="52"/>
-      <c r="AA114" s="52"/>
-      <c r="AB114" s="52"/>
-      <c r="AC114" s="52"/>
+      <c r="A114" s="52"/>
+      <c r="B114" s="53"/>
+      <c r="C114" s="55"/>
+      <c r="D114" s="55"/>
+      <c r="E114" s="55"/>
+      <c r="F114" s="57"/>
+      <c r="G114" s="57"/>
+      <c r="H114" s="57"/>
+      <c r="I114" s="57"/>
+      <c r="J114" s="57"/>
+      <c r="K114" s="57"/>
+      <c r="L114" s="57"/>
+      <c r="M114" s="57"/>
+      <c r="N114" s="57"/>
+      <c r="O114" s="57"/>
+      <c r="P114" s="57"/>
+      <c r="Q114" s="57"/>
+      <c r="R114" s="57"/>
+      <c r="S114" s="57"/>
+      <c r="T114" s="57"/>
+      <c r="U114" s="51"/>
+      <c r="V114" s="51"/>
+      <c r="W114" s="51"/>
+      <c r="X114" s="51"/>
+      <c r="Y114" s="51"/>
+      <c r="Z114" s="51"/>
+      <c r="AA114" s="51"/>
+      <c r="AB114" s="51"/>
+      <c r="AC114" s="51"/>
     </row>
     <row r="115" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="53"/>
-      <c r="B115" s="54"/>
-      <c r="C115" s="56"/>
-      <c r="D115" s="56"/>
-      <c r="E115" s="56"/>
-      <c r="F115" s="58"/>
-      <c r="G115" s="58"/>
-      <c r="H115" s="58"/>
-      <c r="I115" s="58"/>
-      <c r="J115" s="58"/>
-      <c r="K115" s="58"/>
-      <c r="L115" s="58"/>
-      <c r="M115" s="58"/>
-      <c r="N115" s="58"/>
-      <c r="O115" s="58"/>
-      <c r="P115" s="58"/>
-      <c r="Q115" s="58"/>
-      <c r="R115" s="58"/>
-      <c r="S115" s="58"/>
-      <c r="T115" s="58"/>
-      <c r="U115" s="52"/>
-      <c r="V115" s="52"/>
-      <c r="W115" s="52"/>
-      <c r="X115" s="52"/>
-      <c r="Y115" s="52"/>
-      <c r="Z115" s="52"/>
-      <c r="AA115" s="52"/>
-      <c r="AB115" s="52"/>
-      <c r="AC115" s="52"/>
+      <c r="A115" s="52"/>
+      <c r="B115" s="53"/>
+      <c r="C115" s="55"/>
+      <c r="D115" s="55"/>
+      <c r="E115" s="55"/>
+      <c r="F115" s="57"/>
+      <c r="G115" s="57"/>
+      <c r="H115" s="57"/>
+      <c r="I115" s="57"/>
+      <c r="J115" s="57"/>
+      <c r="K115" s="57"/>
+      <c r="L115" s="57"/>
+      <c r="M115" s="57"/>
+      <c r="N115" s="57"/>
+      <c r="O115" s="57"/>
+      <c r="P115" s="57"/>
+      <c r="Q115" s="57"/>
+      <c r="R115" s="57"/>
+      <c r="S115" s="57"/>
+      <c r="T115" s="57"/>
+      <c r="U115" s="51"/>
+      <c r="V115" s="51"/>
+      <c r="W115" s="51"/>
+      <c r="X115" s="51"/>
+      <c r="Y115" s="51"/>
+      <c r="Z115" s="51"/>
+      <c r="AA115" s="51"/>
+      <c r="AB115" s="51"/>
+      <c r="AC115" s="51"/>
     </row>
     <row r="116" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="53"/>
-      <c r="B116" s="54"/>
-      <c r="C116" s="56"/>
-      <c r="D116" s="56"/>
-      <c r="E116" s="56"/>
-      <c r="F116" s="58"/>
-      <c r="G116" s="58"/>
-      <c r="H116" s="58"/>
-      <c r="I116" s="58"/>
-      <c r="J116" s="58"/>
-      <c r="K116" s="58"/>
-      <c r="L116" s="58"/>
-      <c r="M116" s="58"/>
-      <c r="N116" s="58"/>
-      <c r="O116" s="58"/>
-      <c r="P116" s="58"/>
-      <c r="Q116" s="58"/>
-      <c r="R116" s="58"/>
-      <c r="S116" s="58"/>
-      <c r="T116" s="58"/>
-      <c r="U116" s="52"/>
-      <c r="V116" s="52"/>
-      <c r="W116" s="52"/>
-      <c r="X116" s="52"/>
-      <c r="Y116" s="52"/>
-      <c r="Z116" s="52"/>
-      <c r="AA116" s="52"/>
-      <c r="AB116" s="52"/>
-      <c r="AC116" s="52"/>
+      <c r="A116" s="52"/>
+      <c r="B116" s="53"/>
+      <c r="C116" s="55"/>
+      <c r="D116" s="55"/>
+      <c r="E116" s="55"/>
+      <c r="F116" s="57"/>
+      <c r="G116" s="57"/>
+      <c r="H116" s="57"/>
+      <c r="I116" s="57"/>
+      <c r="J116" s="57"/>
+      <c r="K116" s="57"/>
+      <c r="L116" s="57"/>
+      <c r="M116" s="57"/>
+      <c r="N116" s="57"/>
+      <c r="O116" s="57"/>
+      <c r="P116" s="57"/>
+      <c r="Q116" s="57"/>
+      <c r="R116" s="57"/>
+      <c r="S116" s="57"/>
+      <c r="T116" s="57"/>
+      <c r="U116" s="51"/>
+      <c r="V116" s="51"/>
+      <c r="W116" s="51"/>
+      <c r="X116" s="51"/>
+      <c r="Y116" s="51"/>
+      <c r="Z116" s="51"/>
+      <c r="AA116" s="51"/>
+      <c r="AB116" s="51"/>
+      <c r="AC116" s="51"/>
     </row>
     <row r="117" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="53"/>
-      <c r="B117" s="54"/>
-      <c r="C117" s="56"/>
-      <c r="D117" s="56"/>
-      <c r="E117" s="56"/>
-      <c r="F117" s="52"/>
-      <c r="G117" s="52"/>
-      <c r="H117" s="52"/>
-      <c r="I117" s="52"/>
-      <c r="J117" s="52"/>
-      <c r="K117" s="52"/>
-      <c r="L117" s="52"/>
-      <c r="M117" s="52"/>
-      <c r="N117" s="52"/>
-      <c r="O117" s="52"/>
-      <c r="P117" s="52"/>
-      <c r="Q117" s="52"/>
-      <c r="R117" s="52"/>
-      <c r="S117" s="52"/>
-      <c r="T117" s="52"/>
-      <c r="U117" s="52"/>
-      <c r="V117" s="52"/>
-      <c r="W117" s="52"/>
-      <c r="X117" s="52"/>
-      <c r="Y117" s="52"/>
-      <c r="Z117" s="52"/>
-      <c r="AA117" s="52"/>
-      <c r="AB117" s="52"/>
-      <c r="AC117" s="52"/>
+      <c r="A117" s="52"/>
+      <c r="B117" s="53"/>
+      <c r="C117" s="55"/>
+      <c r="D117" s="55"/>
+      <c r="E117" s="55"/>
+      <c r="F117" s="51"/>
+      <c r="G117" s="51"/>
+      <c r="H117" s="51"/>
+      <c r="I117" s="51"/>
+      <c r="J117" s="51"/>
+      <c r="K117" s="51"/>
+      <c r="L117" s="51"/>
+      <c r="M117" s="51"/>
+      <c r="N117" s="51"/>
+      <c r="O117" s="51"/>
+      <c r="P117" s="51"/>
+      <c r="Q117" s="51"/>
+      <c r="R117" s="51"/>
+      <c r="S117" s="51"/>
+      <c r="T117" s="51"/>
+      <c r="U117" s="51"/>
+      <c r="V117" s="51"/>
+      <c r="W117" s="51"/>
+      <c r="X117" s="51"/>
+      <c r="Y117" s="51"/>
+      <c r="Z117" s="51"/>
+      <c r="AA117" s="51"/>
+      <c r="AB117" s="51"/>
+      <c r="AC117" s="51"/>
     </row>
     <row r="118" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="53"/>
-      <c r="B118" s="54"/>
-      <c r="C118" s="56"/>
-      <c r="D118" s="56"/>
-      <c r="E118" s="56"/>
-      <c r="F118" s="52"/>
-      <c r="G118" s="52"/>
-      <c r="H118" s="52"/>
-      <c r="I118" s="52"/>
-      <c r="J118" s="52"/>
-      <c r="K118" s="52"/>
-      <c r="L118" s="52"/>
-      <c r="M118" s="52"/>
-      <c r="N118" s="52"/>
-      <c r="O118" s="52"/>
-      <c r="P118" s="52"/>
-      <c r="Q118" s="52"/>
-      <c r="R118" s="52"/>
-      <c r="S118" s="52"/>
-      <c r="T118" s="52"/>
-      <c r="U118" s="52"/>
-      <c r="V118" s="52"/>
-      <c r="W118" s="52"/>
-      <c r="X118" s="52"/>
-      <c r="Y118" s="52"/>
-      <c r="Z118" s="52"/>
-      <c r="AA118" s="52"/>
-      <c r="AB118" s="52"/>
-      <c r="AC118" s="52"/>
+      <c r="A118" s="52"/>
+      <c r="B118" s="53"/>
+      <c r="C118" s="55"/>
+      <c r="D118" s="55"/>
+      <c r="E118" s="55"/>
+      <c r="F118" s="51"/>
+      <c r="G118" s="51"/>
+      <c r="H118" s="51"/>
+      <c r="I118" s="51"/>
+      <c r="J118" s="51"/>
+      <c r="K118" s="51"/>
+      <c r="L118" s="51"/>
+      <c r="M118" s="51"/>
+      <c r="N118" s="51"/>
+      <c r="O118" s="51"/>
+      <c r="P118" s="51"/>
+      <c r="Q118" s="51"/>
+      <c r="R118" s="51"/>
+      <c r="S118" s="51"/>
+      <c r="T118" s="51"/>
+      <c r="U118" s="51"/>
+      <c r="V118" s="51"/>
+      <c r="W118" s="51"/>
+      <c r="X118" s="51"/>
+      <c r="Y118" s="51"/>
+      <c r="Z118" s="51"/>
+      <c r="AA118" s="51"/>
+      <c r="AB118" s="51"/>
+      <c r="AC118" s="51"/>
     </row>
     <row r="119" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="53"/>
-      <c r="B119" s="54"/>
-      <c r="C119" s="58"/>
-      <c r="D119" s="58"/>
-      <c r="E119" s="58"/>
-      <c r="F119" s="58"/>
-      <c r="G119" s="58"/>
-      <c r="H119" s="58"/>
-      <c r="I119" s="58"/>
-      <c r="J119" s="58"/>
-      <c r="K119" s="58"/>
-      <c r="L119" s="58"/>
-      <c r="M119" s="58"/>
-      <c r="N119" s="58"/>
-      <c r="O119" s="58"/>
-      <c r="P119" s="58"/>
-      <c r="Q119" s="58"/>
-      <c r="R119" s="58"/>
-      <c r="S119" s="58"/>
-      <c r="T119" s="58"/>
-      <c r="U119" s="52"/>
-      <c r="V119" s="52"/>
-      <c r="W119" s="52"/>
-      <c r="X119" s="52"/>
-      <c r="Y119" s="52"/>
-      <c r="Z119" s="52"/>
-      <c r="AA119" s="52"/>
-      <c r="AB119" s="52"/>
-      <c r="AC119" s="52"/>
+      <c r="A119" s="52"/>
+      <c r="B119" s="53"/>
+      <c r="C119" s="57"/>
+      <c r="D119" s="57"/>
+      <c r="E119" s="57"/>
+      <c r="F119" s="57"/>
+      <c r="G119" s="57"/>
+      <c r="H119" s="57"/>
+      <c r="I119" s="57"/>
+      <c r="J119" s="57"/>
+      <c r="K119" s="57"/>
+      <c r="L119" s="57"/>
+      <c r="M119" s="57"/>
+      <c r="N119" s="57"/>
+      <c r="O119" s="57"/>
+      <c r="P119" s="57"/>
+      <c r="Q119" s="57"/>
+      <c r="R119" s="57"/>
+      <c r="S119" s="57"/>
+      <c r="T119" s="57"/>
+      <c r="U119" s="51"/>
+      <c r="V119" s="51"/>
+      <c r="W119" s="51"/>
+      <c r="X119" s="51"/>
+      <c r="Y119" s="51"/>
+      <c r="Z119" s="51"/>
+      <c r="AA119" s="51"/>
+      <c r="AB119" s="51"/>
+      <c r="AC119" s="51"/>
     </row>
     <row r="120" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="53"/>
-      <c r="B120" s="54"/>
-      <c r="C120" s="54"/>
-      <c r="D120" s="54"/>
-      <c r="E120" s="54"/>
-      <c r="F120" s="52"/>
-      <c r="G120" s="52"/>
-      <c r="H120" s="52"/>
-      <c r="I120" s="52"/>
-      <c r="J120" s="52"/>
-      <c r="K120" s="52"/>
-      <c r="L120" s="52"/>
-      <c r="M120" s="52"/>
-      <c r="N120" s="52"/>
-      <c r="O120" s="52"/>
-      <c r="P120" s="52"/>
-      <c r="Q120" s="52"/>
-      <c r="R120" s="52"/>
-      <c r="S120" s="52"/>
-      <c r="T120" s="52"/>
-      <c r="U120" s="52"/>
-      <c r="V120" s="52"/>
-      <c r="W120" s="52"/>
-      <c r="X120" s="52"/>
-      <c r="Y120" s="52"/>
-      <c r="Z120" s="52"/>
-      <c r="AA120" s="52"/>
-      <c r="AB120" s="52"/>
-      <c r="AC120" s="52"/>
+      <c r="A120" s="52"/>
+      <c r="B120" s="53"/>
+      <c r="C120" s="53"/>
+      <c r="D120" s="53"/>
+      <c r="E120" s="53"/>
+      <c r="F120" s="51"/>
+      <c r="G120" s="51"/>
+      <c r="H120" s="51"/>
+      <c r="I120" s="51"/>
+      <c r="J120" s="51"/>
+      <c r="K120" s="51"/>
+      <c r="L120" s="51"/>
+      <c r="M120" s="51"/>
+      <c r="N120" s="51"/>
+      <c r="O120" s="51"/>
+      <c r="P120" s="51"/>
+      <c r="Q120" s="51"/>
+      <c r="R120" s="51"/>
+      <c r="S120" s="51"/>
+      <c r="T120" s="51"/>
+      <c r="U120" s="51"/>
+      <c r="V120" s="51"/>
+      <c r="W120" s="51"/>
+      <c r="X120" s="51"/>
+      <c r="Y120" s="51"/>
+      <c r="Z120" s="51"/>
+      <c r="AA120" s="51"/>
+      <c r="AB120" s="51"/>
+      <c r="AC120" s="51"/>
     </row>
     <row r="121" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="53"/>
-      <c r="B121" s="54"/>
-      <c r="C121" s="55"/>
-      <c r="D121" s="55"/>
-      <c r="E121" s="55"/>
-      <c r="F121" s="52"/>
-      <c r="G121" s="52"/>
-      <c r="H121" s="52"/>
-      <c r="I121" s="52"/>
-      <c r="J121" s="52"/>
-      <c r="K121" s="52"/>
-      <c r="L121" s="52"/>
-      <c r="M121" s="52"/>
-      <c r="N121" s="52"/>
-      <c r="O121" s="52"/>
-      <c r="P121" s="52"/>
-      <c r="Q121" s="52"/>
-      <c r="R121" s="52"/>
-      <c r="S121" s="52"/>
-      <c r="T121" s="52"/>
-      <c r="U121" s="52"/>
-      <c r="V121" s="52"/>
-      <c r="W121" s="52"/>
-      <c r="X121" s="52"/>
-      <c r="Y121" s="52"/>
-      <c r="Z121" s="52"/>
-      <c r="AA121" s="52"/>
-      <c r="AB121" s="52"/>
-      <c r="AC121" s="52"/>
+      <c r="A121" s="52"/>
+      <c r="B121" s="53"/>
+      <c r="C121" s="54"/>
+      <c r="D121" s="54"/>
+      <c r="E121" s="54"/>
+      <c r="F121" s="51"/>
+      <c r="G121" s="51"/>
+      <c r="H121" s="51"/>
+      <c r="I121" s="51"/>
+      <c r="J121" s="51"/>
+      <c r="K121" s="51"/>
+      <c r="L121" s="51"/>
+      <c r="M121" s="51"/>
+      <c r="N121" s="51"/>
+      <c r="O121" s="51"/>
+      <c r="P121" s="51"/>
+      <c r="Q121" s="51"/>
+      <c r="R121" s="51"/>
+      <c r="S121" s="51"/>
+      <c r="T121" s="51"/>
+      <c r="U121" s="51"/>
+      <c r="V121" s="51"/>
+      <c r="W121" s="51"/>
+      <c r="X121" s="51"/>
+      <c r="Y121" s="51"/>
+      <c r="Z121" s="51"/>
+      <c r="AA121" s="51"/>
+      <c r="AB121" s="51"/>
+      <c r="AC121" s="51"/>
     </row>
     <row r="122" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="53"/>
-      <c r="B122" s="55"/>
-      <c r="C122" s="57"/>
-      <c r="D122" s="57"/>
-      <c r="E122" s="57"/>
-      <c r="F122" s="52"/>
-      <c r="G122" s="52"/>
-      <c r="H122" s="52"/>
-      <c r="I122" s="52"/>
-      <c r="J122" s="52"/>
-      <c r="K122" s="52"/>
-      <c r="L122" s="52"/>
-      <c r="M122" s="52"/>
-      <c r="N122" s="52"/>
-      <c r="O122" s="52"/>
-      <c r="P122" s="52"/>
-      <c r="Q122" s="52"/>
-      <c r="R122" s="52"/>
-      <c r="S122" s="52"/>
-      <c r="T122" s="52"/>
-      <c r="U122" s="52"/>
-      <c r="V122" s="52"/>
-      <c r="W122" s="52"/>
-      <c r="X122" s="52"/>
-      <c r="Y122" s="52"/>
-      <c r="Z122" s="52"/>
-      <c r="AA122" s="52"/>
-      <c r="AB122" s="52"/>
-      <c r="AC122" s="52"/>
+      <c r="A122" s="52"/>
+      <c r="B122" s="54"/>
+      <c r="C122" s="56"/>
+      <c r="D122" s="56"/>
+      <c r="E122" s="56"/>
+      <c r="F122" s="51"/>
+      <c r="G122" s="51"/>
+      <c r="H122" s="51"/>
+      <c r="I122" s="51"/>
+      <c r="J122" s="51"/>
+      <c r="K122" s="51"/>
+      <c r="L122" s="51"/>
+      <c r="M122" s="51"/>
+      <c r="N122" s="51"/>
+      <c r="O122" s="51"/>
+      <c r="P122" s="51"/>
+      <c r="Q122" s="51"/>
+      <c r="R122" s="51"/>
+      <c r="S122" s="51"/>
+      <c r="T122" s="51"/>
+      <c r="U122" s="51"/>
+      <c r="V122" s="51"/>
+      <c r="W122" s="51"/>
+      <c r="X122" s="51"/>
+      <c r="Y122" s="51"/>
+      <c r="Z122" s="51"/>
+      <c r="AA122" s="51"/>
+      <c r="AB122" s="51"/>
+      <c r="AC122" s="51"/>
     </row>
     <row r="123" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="53"/>
-      <c r="B123" s="55"/>
-      <c r="C123" s="57"/>
-      <c r="D123" s="57"/>
-      <c r="E123" s="57"/>
-      <c r="F123" s="52"/>
-      <c r="G123" s="52"/>
-      <c r="H123" s="52"/>
-      <c r="I123" s="52"/>
-      <c r="J123" s="52"/>
-      <c r="K123" s="52"/>
-      <c r="L123" s="52"/>
-      <c r="M123" s="52"/>
-      <c r="N123" s="52"/>
-      <c r="O123" s="52"/>
-      <c r="P123" s="52"/>
-      <c r="Q123" s="52"/>
-      <c r="R123" s="52"/>
-      <c r="S123" s="52"/>
-      <c r="T123" s="52"/>
-      <c r="U123" s="52"/>
-      <c r="V123" s="52"/>
-      <c r="W123" s="52"/>
-      <c r="X123" s="52"/>
-      <c r="Y123" s="52"/>
-      <c r="Z123" s="52"/>
-      <c r="AA123" s="52"/>
-      <c r="AB123" s="52"/>
-      <c r="AC123" s="52"/>
+      <c r="A123" s="52"/>
+      <c r="B123" s="54"/>
+      <c r="C123" s="56"/>
+      <c r="D123" s="56"/>
+      <c r="E123" s="56"/>
+      <c r="F123" s="51"/>
+      <c r="G123" s="51"/>
+      <c r="H123" s="51"/>
+      <c r="I123" s="51"/>
+      <c r="J123" s="51"/>
+      <c r="K123" s="51"/>
+      <c r="L123" s="51"/>
+      <c r="M123" s="51"/>
+      <c r="N123" s="51"/>
+      <c r="O123" s="51"/>
+      <c r="P123" s="51"/>
+      <c r="Q123" s="51"/>
+      <c r="R123" s="51"/>
+      <c r="S123" s="51"/>
+      <c r="T123" s="51"/>
+      <c r="U123" s="51"/>
+      <c r="V123" s="51"/>
+      <c r="W123" s="51"/>
+      <c r="X123" s="51"/>
+      <c r="Y123" s="51"/>
+      <c r="Z123" s="51"/>
+      <c r="AA123" s="51"/>
+      <c r="AB123" s="51"/>
+      <c r="AC123" s="51"/>
     </row>
     <row r="124" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="53"/>
-      <c r="B124" s="55"/>
-      <c r="C124" s="57"/>
-      <c r="D124" s="57"/>
-      <c r="E124" s="57"/>
-      <c r="F124" s="52"/>
-      <c r="G124" s="52"/>
-      <c r="H124" s="52"/>
-      <c r="I124" s="52"/>
-      <c r="J124" s="52"/>
-      <c r="K124" s="52"/>
-      <c r="L124" s="52"/>
-      <c r="M124" s="52"/>
-      <c r="N124" s="52"/>
-      <c r="O124" s="52"/>
-      <c r="P124" s="52"/>
-      <c r="Q124" s="52"/>
-      <c r="R124" s="52"/>
-      <c r="S124" s="52"/>
-      <c r="T124" s="52"/>
-      <c r="U124" s="52"/>
-      <c r="V124" s="52"/>
-      <c r="W124" s="52"/>
-      <c r="X124" s="52"/>
-      <c r="Y124" s="52"/>
-      <c r="Z124" s="52"/>
-      <c r="AA124" s="52"/>
-      <c r="AB124" s="52"/>
-      <c r="AC124" s="52"/>
+      <c r="A124" s="52"/>
+      <c r="B124" s="54"/>
+      <c r="C124" s="56"/>
+      <c r="D124" s="56"/>
+      <c r="E124" s="56"/>
+      <c r="F124" s="51"/>
+      <c r="G124" s="51"/>
+      <c r="H124" s="51"/>
+      <c r="I124" s="51"/>
+      <c r="J124" s="51"/>
+      <c r="K124" s="51"/>
+      <c r="L124" s="51"/>
+      <c r="M124" s="51"/>
+      <c r="N124" s="51"/>
+      <c r="O124" s="51"/>
+      <c r="P124" s="51"/>
+      <c r="Q124" s="51"/>
+      <c r="R124" s="51"/>
+      <c r="S124" s="51"/>
+      <c r="T124" s="51"/>
+      <c r="U124" s="51"/>
+      <c r="V124" s="51"/>
+      <c r="W124" s="51"/>
+      <c r="X124" s="51"/>
+      <c r="Y124" s="51"/>
+      <c r="Z124" s="51"/>
+      <c r="AA124" s="51"/>
+      <c r="AB124" s="51"/>
+      <c r="AC124" s="51"/>
     </row>
     <row r="125" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="53"/>
-      <c r="B125" s="55"/>
-      <c r="C125" s="57"/>
-      <c r="D125" s="57"/>
-      <c r="E125" s="57"/>
-      <c r="F125" s="52"/>
-      <c r="G125" s="52"/>
-      <c r="H125" s="52"/>
-      <c r="I125" s="52"/>
-      <c r="J125" s="52"/>
-      <c r="K125" s="52"/>
-      <c r="L125" s="52"/>
-      <c r="M125" s="52"/>
-      <c r="N125" s="52"/>
-      <c r="O125" s="52"/>
-      <c r="P125" s="52"/>
-      <c r="Q125" s="52"/>
-      <c r="R125" s="52"/>
-      <c r="S125" s="52"/>
-      <c r="T125" s="52"/>
-      <c r="U125" s="52"/>
-      <c r="V125" s="52"/>
-      <c r="W125" s="52"/>
-      <c r="X125" s="52"/>
-      <c r="Y125" s="52"/>
-      <c r="Z125" s="52"/>
-      <c r="AA125" s="52"/>
-      <c r="AB125" s="52"/>
-      <c r="AC125" s="52"/>
+      <c r="A125" s="52"/>
+      <c r="B125" s="54"/>
+      <c r="C125" s="56"/>
+      <c r="D125" s="56"/>
+      <c r="E125" s="56"/>
+      <c r="F125" s="51"/>
+      <c r="G125" s="51"/>
+      <c r="H125" s="51"/>
+      <c r="I125" s="51"/>
+      <c r="J125" s="51"/>
+      <c r="K125" s="51"/>
+      <c r="L125" s="51"/>
+      <c r="M125" s="51"/>
+      <c r="N125" s="51"/>
+      <c r="O125" s="51"/>
+      <c r="P125" s="51"/>
+      <c r="Q125" s="51"/>
+      <c r="R125" s="51"/>
+      <c r="S125" s="51"/>
+      <c r="T125" s="51"/>
+      <c r="U125" s="51"/>
+      <c r="V125" s="51"/>
+      <c r="W125" s="51"/>
+      <c r="X125" s="51"/>
+      <c r="Y125" s="51"/>
+      <c r="Z125" s="51"/>
+      <c r="AA125" s="51"/>
+      <c r="AB125" s="51"/>
+      <c r="AC125" s="51"/>
     </row>
     <row r="126" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="53"/>
-      <c r="B126" s="55"/>
-      <c r="C126" s="56"/>
-      <c r="D126" s="57"/>
-      <c r="E126" s="57"/>
-      <c r="F126" s="52"/>
-      <c r="G126" s="52"/>
-      <c r="H126" s="52"/>
-      <c r="I126" s="52"/>
-      <c r="J126" s="52"/>
-      <c r="K126" s="52"/>
-      <c r="L126" s="52"/>
-      <c r="M126" s="52"/>
-      <c r="N126" s="52"/>
-      <c r="O126" s="52"/>
-      <c r="P126" s="52"/>
-      <c r="Q126" s="52"/>
-      <c r="R126" s="52"/>
-      <c r="S126" s="52"/>
-      <c r="T126" s="52"/>
-      <c r="U126" s="52"/>
-      <c r="V126" s="52"/>
-      <c r="W126" s="52"/>
-      <c r="X126" s="52"/>
-      <c r="Y126" s="52"/>
-      <c r="Z126" s="52"/>
-      <c r="AA126" s="52"/>
-      <c r="AB126" s="52"/>
-      <c r="AC126" s="52"/>
+      <c r="A126" s="52"/>
+      <c r="B126" s="54"/>
+      <c r="C126" s="55"/>
+      <c r="D126" s="56"/>
+      <c r="E126" s="56"/>
+      <c r="F126" s="51"/>
+      <c r="G126" s="51"/>
+      <c r="H126" s="51"/>
+      <c r="I126" s="51"/>
+      <c r="J126" s="51"/>
+      <c r="K126" s="51"/>
+      <c r="L126" s="51"/>
+      <c r="M126" s="51"/>
+      <c r="N126" s="51"/>
+      <c r="O126" s="51"/>
+      <c r="P126" s="51"/>
+      <c r="Q126" s="51"/>
+      <c r="R126" s="51"/>
+      <c r="S126" s="51"/>
+      <c r="T126" s="51"/>
+      <c r="U126" s="51"/>
+      <c r="V126" s="51"/>
+      <c r="W126" s="51"/>
+      <c r="X126" s="51"/>
+      <c r="Y126" s="51"/>
+      <c r="Z126" s="51"/>
+      <c r="AA126" s="51"/>
+      <c r="AB126" s="51"/>
+      <c r="AC126" s="51"/>
     </row>
     <row r="127" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="53"/>
-      <c r="B127" s="55"/>
-      <c r="C127" s="56"/>
-      <c r="D127" s="57"/>
-      <c r="E127" s="57"/>
-      <c r="F127" s="52"/>
-      <c r="G127" s="52"/>
-      <c r="H127" s="52"/>
-      <c r="I127" s="52"/>
-      <c r="J127" s="52"/>
-      <c r="K127" s="52"/>
-      <c r="L127" s="52"/>
-      <c r="M127" s="52"/>
-      <c r="N127" s="52"/>
-      <c r="O127" s="52"/>
-      <c r="P127" s="52"/>
-      <c r="Q127" s="52"/>
-      <c r="R127" s="52"/>
-      <c r="S127" s="52"/>
-      <c r="T127" s="52"/>
-      <c r="U127" s="52"/>
-      <c r="V127" s="52"/>
-      <c r="W127" s="52"/>
-      <c r="X127" s="52"/>
-      <c r="Y127" s="52"/>
-      <c r="Z127" s="52"/>
-      <c r="AA127" s="52"/>
-      <c r="AB127" s="52"/>
-      <c r="AC127" s="52"/>
+      <c r="A127" s="52"/>
+      <c r="B127" s="54"/>
+      <c r="C127" s="55"/>
+      <c r="D127" s="56"/>
+      <c r="E127" s="56"/>
+      <c r="F127" s="51"/>
+      <c r="G127" s="51"/>
+      <c r="H127" s="51"/>
+      <c r="I127" s="51"/>
+      <c r="J127" s="51"/>
+      <c r="K127" s="51"/>
+      <c r="L127" s="51"/>
+      <c r="M127" s="51"/>
+      <c r="N127" s="51"/>
+      <c r="O127" s="51"/>
+      <c r="P127" s="51"/>
+      <c r="Q127" s="51"/>
+      <c r="R127" s="51"/>
+      <c r="S127" s="51"/>
+      <c r="T127" s="51"/>
+      <c r="U127" s="51"/>
+      <c r="V127" s="51"/>
+      <c r="W127" s="51"/>
+      <c r="X127" s="51"/>
+      <c r="Y127" s="51"/>
+      <c r="Z127" s="51"/>
+      <c r="AA127" s="51"/>
+      <c r="AB127" s="51"/>
+      <c r="AC127" s="51"/>
     </row>
     <row r="128" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="53"/>
-      <c r="B128" s="55"/>
-      <c r="C128" s="56"/>
-      <c r="D128" s="57"/>
-      <c r="E128" s="57"/>
-      <c r="F128" s="52"/>
-      <c r="G128" s="52"/>
-      <c r="H128" s="52"/>
-      <c r="I128" s="52"/>
-      <c r="J128" s="52"/>
-      <c r="K128" s="52"/>
-      <c r="L128" s="52"/>
-      <c r="M128" s="52"/>
-      <c r="N128" s="52"/>
-      <c r="O128" s="52"/>
-      <c r="P128" s="52"/>
-      <c r="Q128" s="52"/>
-      <c r="R128" s="52"/>
-      <c r="S128" s="52"/>
-      <c r="T128" s="52"/>
-      <c r="U128" s="52"/>
-      <c r="V128" s="52"/>
-      <c r="W128" s="52"/>
-      <c r="X128" s="52"/>
-      <c r="Y128" s="52"/>
-      <c r="Z128" s="52"/>
-      <c r="AA128" s="52"/>
-      <c r="AB128" s="52"/>
-      <c r="AC128" s="52"/>
+      <c r="A128" s="52"/>
+      <c r="B128" s="54"/>
+      <c r="C128" s="55"/>
+      <c r="D128" s="56"/>
+      <c r="E128" s="56"/>
+      <c r="F128" s="51"/>
+      <c r="G128" s="51"/>
+      <c r="H128" s="51"/>
+      <c r="I128" s="51"/>
+      <c r="J128" s="51"/>
+      <c r="K128" s="51"/>
+      <c r="L128" s="51"/>
+      <c r="M128" s="51"/>
+      <c r="N128" s="51"/>
+      <c r="O128" s="51"/>
+      <c r="P128" s="51"/>
+      <c r="Q128" s="51"/>
+      <c r="R128" s="51"/>
+      <c r="S128" s="51"/>
+      <c r="T128" s="51"/>
+      <c r="U128" s="51"/>
+      <c r="V128" s="51"/>
+      <c r="W128" s="51"/>
+      <c r="X128" s="51"/>
+      <c r="Y128" s="51"/>
+      <c r="Z128" s="51"/>
+      <c r="AA128" s="51"/>
+      <c r="AB128" s="51"/>
+      <c r="AC128" s="51"/>
     </row>
     <row r="129" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="53"/>
-      <c r="B129" s="55"/>
-      <c r="C129" s="56"/>
-      <c r="D129" s="57"/>
-      <c r="E129" s="57"/>
-      <c r="F129" s="52"/>
-      <c r="G129" s="52"/>
-      <c r="H129" s="52"/>
-      <c r="I129" s="52"/>
-      <c r="J129" s="52"/>
-      <c r="K129" s="52"/>
-      <c r="L129" s="52"/>
-      <c r="M129" s="52"/>
-      <c r="N129" s="52"/>
-      <c r="O129" s="52"/>
-      <c r="P129" s="52"/>
-      <c r="Q129" s="52"/>
-      <c r="R129" s="52"/>
-      <c r="S129" s="52"/>
-      <c r="T129" s="52"/>
-      <c r="U129" s="52"/>
-      <c r="V129" s="52"/>
-      <c r="W129" s="52"/>
-      <c r="X129" s="52"/>
-      <c r="Y129" s="52"/>
-      <c r="Z129" s="52"/>
-      <c r="AA129" s="52"/>
-      <c r="AB129" s="52"/>
-      <c r="AC129" s="52"/>
+      <c r="A129" s="52"/>
+      <c r="B129" s="54"/>
+      <c r="C129" s="55"/>
+      <c r="D129" s="56"/>
+      <c r="E129" s="56"/>
+      <c r="F129" s="51"/>
+      <c r="G129" s="51"/>
+      <c r="H129" s="51"/>
+      <c r="I129" s="51"/>
+      <c r="J129" s="51"/>
+      <c r="K129" s="51"/>
+      <c r="L129" s="51"/>
+      <c r="M129" s="51"/>
+      <c r="N129" s="51"/>
+      <c r="O129" s="51"/>
+      <c r="P129" s="51"/>
+      <c r="Q129" s="51"/>
+      <c r="R129" s="51"/>
+      <c r="S129" s="51"/>
+      <c r="T129" s="51"/>
+      <c r="U129" s="51"/>
+      <c r="V129" s="51"/>
+      <c r="W129" s="51"/>
+      <c r="X129" s="51"/>
+      <c r="Y129" s="51"/>
+      <c r="Z129" s="51"/>
+      <c r="AA129" s="51"/>
+      <c r="AB129" s="51"/>
+      <c r="AC129" s="51"/>
     </row>
     <row r="130" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="53"/>
-      <c r="B130" s="55"/>
-      <c r="C130" s="56"/>
-      <c r="D130" s="57"/>
-      <c r="E130" s="57"/>
-      <c r="F130" s="52"/>
-      <c r="G130" s="52"/>
-      <c r="H130" s="52"/>
-      <c r="I130" s="52"/>
-      <c r="J130" s="52"/>
-      <c r="K130" s="52"/>
-      <c r="L130" s="52"/>
-      <c r="M130" s="52"/>
-      <c r="N130" s="52"/>
-      <c r="O130" s="52"/>
-      <c r="P130" s="52"/>
-      <c r="Q130" s="52"/>
-      <c r="R130" s="52"/>
-      <c r="S130" s="52"/>
-      <c r="T130" s="52"/>
-      <c r="U130" s="52"/>
-      <c r="V130" s="52"/>
-      <c r="W130" s="52"/>
-      <c r="X130" s="52"/>
-      <c r="Y130" s="52"/>
-      <c r="Z130" s="52"/>
-      <c r="AA130" s="52"/>
-      <c r="AB130" s="52"/>
-      <c r="AC130" s="52"/>
+      <c r="A130" s="52"/>
+      <c r="B130" s="54"/>
+      <c r="C130" s="55"/>
+      <c r="D130" s="56"/>
+      <c r="E130" s="56"/>
+      <c r="F130" s="51"/>
+      <c r="G130" s="51"/>
+      <c r="H130" s="51"/>
+      <c r="I130" s="51"/>
+      <c r="J130" s="51"/>
+      <c r="K130" s="51"/>
+      <c r="L130" s="51"/>
+      <c r="M130" s="51"/>
+      <c r="N130" s="51"/>
+      <c r="O130" s="51"/>
+      <c r="P130" s="51"/>
+      <c r="Q130" s="51"/>
+      <c r="R130" s="51"/>
+      <c r="S130" s="51"/>
+      <c r="T130" s="51"/>
+      <c r="U130" s="51"/>
+      <c r="V130" s="51"/>
+      <c r="W130" s="51"/>
+      <c r="X130" s="51"/>
+      <c r="Y130" s="51"/>
+      <c r="Z130" s="51"/>
+      <c r="AA130" s="51"/>
+      <c r="AB130" s="51"/>
+      <c r="AC130" s="51"/>
     </row>
     <row r="131" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="53"/>
-      <c r="B131" s="55"/>
-      <c r="C131" s="56"/>
-      <c r="D131" s="57"/>
-      <c r="E131" s="57"/>
-      <c r="F131" s="52"/>
-      <c r="G131" s="52"/>
-      <c r="H131" s="52"/>
-      <c r="I131" s="52"/>
-      <c r="J131" s="52"/>
-      <c r="K131" s="52"/>
-      <c r="L131" s="52"/>
-      <c r="M131" s="52"/>
-      <c r="N131" s="52"/>
-      <c r="O131" s="52"/>
-      <c r="P131" s="52"/>
-      <c r="Q131" s="52"/>
-      <c r="R131" s="52"/>
-      <c r="S131" s="52"/>
-      <c r="T131" s="52"/>
-      <c r="U131" s="52"/>
-      <c r="V131" s="52"/>
-      <c r="W131" s="52"/>
-      <c r="X131" s="52"/>
-      <c r="Y131" s="52"/>
-      <c r="Z131" s="52"/>
-      <c r="AA131" s="52"/>
-      <c r="AB131" s="52"/>
-      <c r="AC131" s="52"/>
+      <c r="A131" s="52"/>
+      <c r="B131" s="54"/>
+      <c r="C131" s="55"/>
+      <c r="D131" s="56"/>
+      <c r="E131" s="56"/>
+      <c r="F131" s="51"/>
+      <c r="G131" s="51"/>
+      <c r="H131" s="51"/>
+      <c r="I131" s="51"/>
+      <c r="J131" s="51"/>
+      <c r="K131" s="51"/>
+      <c r="L131" s="51"/>
+      <c r="M131" s="51"/>
+      <c r="N131" s="51"/>
+      <c r="O131" s="51"/>
+      <c r="P131" s="51"/>
+      <c r="Q131" s="51"/>
+      <c r="R131" s="51"/>
+      <c r="S131" s="51"/>
+      <c r="T131" s="51"/>
+      <c r="U131" s="51"/>
+      <c r="V131" s="51"/>
+      <c r="W131" s="51"/>
+      <c r="X131" s="51"/>
+      <c r="Y131" s="51"/>
+      <c r="Z131" s="51"/>
+      <c r="AA131" s="51"/>
+      <c r="AB131" s="51"/>
+      <c r="AC131" s="51"/>
     </row>
     <row r="132" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="53"/>
-      <c r="B132" s="55"/>
-      <c r="C132" s="56"/>
-      <c r="D132" s="57"/>
-      <c r="E132" s="57"/>
-      <c r="F132" s="52"/>
-      <c r="G132" s="52"/>
-      <c r="H132" s="52"/>
-      <c r="I132" s="52"/>
-      <c r="J132" s="52"/>
-      <c r="K132" s="52"/>
-      <c r="L132" s="52"/>
-      <c r="M132" s="52"/>
-      <c r="N132" s="52"/>
-      <c r="O132" s="52"/>
-      <c r="P132" s="52"/>
-      <c r="Q132" s="52"/>
-      <c r="R132" s="52"/>
-      <c r="S132" s="52"/>
-      <c r="T132" s="52"/>
-      <c r="U132" s="52"/>
-      <c r="V132" s="52"/>
-      <c r="W132" s="52"/>
-      <c r="X132" s="52"/>
-      <c r="Y132" s="52"/>
-      <c r="Z132" s="52"/>
-      <c r="AA132" s="52"/>
-      <c r="AB132" s="52"/>
-      <c r="AC132" s="52"/>
+      <c r="A132" s="52"/>
+      <c r="B132" s="54"/>
+      <c r="C132" s="55"/>
+      <c r="D132" s="56"/>
+      <c r="E132" s="56"/>
+      <c r="F132" s="51"/>
+      <c r="G132" s="51"/>
+      <c r="H132" s="51"/>
+      <c r="I132" s="51"/>
+      <c r="J132" s="51"/>
+      <c r="K132" s="51"/>
+      <c r="L132" s="51"/>
+      <c r="M132" s="51"/>
+      <c r="N132" s="51"/>
+      <c r="O132" s="51"/>
+      <c r="P132" s="51"/>
+      <c r="Q132" s="51"/>
+      <c r="R132" s="51"/>
+      <c r="S132" s="51"/>
+      <c r="T132" s="51"/>
+      <c r="U132" s="51"/>
+      <c r="V132" s="51"/>
+      <c r="W132" s="51"/>
+      <c r="X132" s="51"/>
+      <c r="Y132" s="51"/>
+      <c r="Z132" s="51"/>
+      <c r="AA132" s="51"/>
+      <c r="AB132" s="51"/>
+      <c r="AC132" s="51"/>
     </row>
     <row r="133" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="53"/>
-      <c r="B133" s="55"/>
-      <c r="C133" s="56"/>
-      <c r="D133" s="57"/>
-      <c r="E133" s="57"/>
-      <c r="F133" s="52"/>
-      <c r="G133" s="52"/>
-      <c r="H133" s="52"/>
-      <c r="I133" s="52"/>
-      <c r="J133" s="52"/>
-      <c r="K133" s="52"/>
-      <c r="L133" s="52"/>
-      <c r="M133" s="52"/>
-      <c r="N133" s="52"/>
-      <c r="O133" s="52"/>
-      <c r="P133" s="52"/>
-      <c r="Q133" s="52"/>
-      <c r="R133" s="52"/>
-      <c r="S133" s="52"/>
-      <c r="T133" s="52"/>
-      <c r="U133" s="52"/>
-      <c r="V133" s="52"/>
-      <c r="W133" s="52"/>
-      <c r="X133" s="52"/>
-      <c r="Y133" s="52"/>
-      <c r="Z133" s="52"/>
-      <c r="AA133" s="52"/>
-      <c r="AB133" s="52"/>
-      <c r="AC133" s="52"/>
+      <c r="A133" s="52"/>
+      <c r="B133" s="54"/>
+      <c r="C133" s="55"/>
+      <c r="D133" s="56"/>
+      <c r="E133" s="56"/>
+      <c r="F133" s="51"/>
+      <c r="G133" s="51"/>
+      <c r="H133" s="51"/>
+      <c r="I133" s="51"/>
+      <c r="J133" s="51"/>
+      <c r="K133" s="51"/>
+      <c r="L133" s="51"/>
+      <c r="M133" s="51"/>
+      <c r="N133" s="51"/>
+      <c r="O133" s="51"/>
+      <c r="P133" s="51"/>
+      <c r="Q133" s="51"/>
+      <c r="R133" s="51"/>
+      <c r="S133" s="51"/>
+      <c r="T133" s="51"/>
+      <c r="U133" s="51"/>
+      <c r="V133" s="51"/>
+      <c r="W133" s="51"/>
+      <c r="X133" s="51"/>
+      <c r="Y133" s="51"/>
+      <c r="Z133" s="51"/>
+      <c r="AA133" s="51"/>
+      <c r="AB133" s="51"/>
+      <c r="AC133" s="51"/>
     </row>
     <row r="134" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="53"/>
-      <c r="B134" s="54"/>
-      <c r="C134" s="54"/>
-      <c r="D134" s="54"/>
-      <c r="E134" s="54"/>
-      <c r="F134" s="52"/>
-      <c r="G134" s="52"/>
-      <c r="H134" s="52"/>
-      <c r="I134" s="52"/>
-      <c r="J134" s="52"/>
-      <c r="K134" s="52"/>
-      <c r="L134" s="52"/>
-      <c r="M134" s="52"/>
-      <c r="N134" s="52"/>
-      <c r="O134" s="52"/>
-      <c r="P134" s="52"/>
-      <c r="Q134" s="52"/>
-      <c r="R134" s="52"/>
-      <c r="S134" s="52"/>
-      <c r="T134" s="52"/>
-      <c r="U134" s="52"/>
-      <c r="V134" s="52"/>
-      <c r="W134" s="52"/>
-      <c r="X134" s="52"/>
-      <c r="Y134" s="52"/>
-      <c r="Z134" s="52"/>
-      <c r="AA134" s="52"/>
-      <c r="AB134" s="52"/>
-      <c r="AC134" s="52"/>
+      <c r="A134" s="52"/>
+      <c r="B134" s="53"/>
+      <c r="C134" s="53"/>
+      <c r="D134" s="53"/>
+      <c r="E134" s="53"/>
+      <c r="F134" s="51"/>
+      <c r="G134" s="51"/>
+      <c r="H134" s="51"/>
+      <c r="I134" s="51"/>
+      <c r="J134" s="51"/>
+      <c r="K134" s="51"/>
+      <c r="L134" s="51"/>
+      <c r="M134" s="51"/>
+      <c r="N134" s="51"/>
+      <c r="O134" s="51"/>
+      <c r="P134" s="51"/>
+      <c r="Q134" s="51"/>
+      <c r="R134" s="51"/>
+      <c r="S134" s="51"/>
+      <c r="T134" s="51"/>
+      <c r="U134" s="51"/>
+      <c r="V134" s="51"/>
+      <c r="W134" s="51"/>
+      <c r="X134" s="51"/>
+      <c r="Y134" s="51"/>
+      <c r="Z134" s="51"/>
+      <c r="AA134" s="51"/>
+      <c r="AB134" s="51"/>
+      <c r="AC134" s="51"/>
     </row>
     <row r="135" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="53"/>
-      <c r="B135" s="54"/>
-      <c r="C135" s="55"/>
-      <c r="D135" s="55"/>
-      <c r="E135" s="55"/>
-      <c r="F135" s="58"/>
-      <c r="G135" s="58"/>
-      <c r="H135" s="58"/>
-      <c r="I135" s="58"/>
-      <c r="J135" s="58"/>
-      <c r="K135" s="58"/>
-      <c r="L135" s="58"/>
-      <c r="M135" s="58"/>
-      <c r="N135" s="58"/>
-      <c r="O135" s="58"/>
-      <c r="P135" s="58"/>
-      <c r="Q135" s="58"/>
-      <c r="R135" s="58"/>
-      <c r="S135" s="58"/>
-      <c r="T135" s="58"/>
-      <c r="U135" s="58"/>
-      <c r="V135" s="58"/>
-      <c r="W135" s="58"/>
-      <c r="X135" s="58"/>
-      <c r="Y135" s="58"/>
-      <c r="Z135" s="58"/>
-      <c r="AA135" s="58"/>
-      <c r="AB135" s="58"/>
-      <c r="AC135" s="58"/>
+      <c r="A135" s="52"/>
+      <c r="B135" s="53"/>
+      <c r="C135" s="54"/>
+      <c r="D135" s="54"/>
+      <c r="E135" s="54"/>
+      <c r="F135" s="57"/>
+      <c r="G135" s="57"/>
+      <c r="H135" s="57"/>
+      <c r="I135" s="57"/>
+      <c r="J135" s="57"/>
+      <c r="K135" s="57"/>
+      <c r="L135" s="57"/>
+      <c r="M135" s="57"/>
+      <c r="N135" s="57"/>
+      <c r="O135" s="57"/>
+      <c r="P135" s="57"/>
+      <c r="Q135" s="57"/>
+      <c r="R135" s="57"/>
+      <c r="S135" s="57"/>
+      <c r="T135" s="57"/>
+      <c r="U135" s="57"/>
+      <c r="V135" s="57"/>
+      <c r="W135" s="57"/>
+      <c r="X135" s="57"/>
+      <c r="Y135" s="57"/>
+      <c r="Z135" s="57"/>
+      <c r="AA135" s="57"/>
+      <c r="AB135" s="57"/>
+      <c r="AC135" s="57"/>
     </row>
     <row r="136" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="53"/>
-      <c r="B136" s="55"/>
-      <c r="C136" s="56"/>
-      <c r="D136" s="56"/>
-      <c r="E136" s="56"/>
-      <c r="F136" s="58"/>
-      <c r="G136" s="58"/>
-      <c r="H136" s="58"/>
-      <c r="I136" s="58"/>
-      <c r="J136" s="58"/>
-      <c r="K136" s="58"/>
-      <c r="L136" s="58"/>
-      <c r="M136" s="58"/>
-      <c r="N136" s="58"/>
-      <c r="O136" s="58"/>
-      <c r="P136" s="58"/>
-      <c r="Q136" s="58"/>
-      <c r="R136" s="58"/>
-      <c r="S136" s="58"/>
-      <c r="T136" s="58"/>
-      <c r="U136" s="58"/>
-      <c r="V136" s="58"/>
-      <c r="W136" s="58"/>
-      <c r="X136" s="58"/>
-      <c r="Y136" s="58"/>
-      <c r="Z136" s="58"/>
-      <c r="AA136" s="58"/>
-      <c r="AB136" s="58"/>
-      <c r="AC136" s="58"/>
+      <c r="A136" s="52"/>
+      <c r="B136" s="54"/>
+      <c r="C136" s="55"/>
+      <c r="D136" s="55"/>
+      <c r="E136" s="55"/>
+      <c r="F136" s="57"/>
+      <c r="G136" s="57"/>
+      <c r="H136" s="57"/>
+      <c r="I136" s="57"/>
+      <c r="J136" s="57"/>
+      <c r="K136" s="57"/>
+      <c r="L136" s="57"/>
+      <c r="M136" s="57"/>
+      <c r="N136" s="57"/>
+      <c r="O136" s="57"/>
+      <c r="P136" s="57"/>
+      <c r="Q136" s="57"/>
+      <c r="R136" s="57"/>
+      <c r="S136" s="57"/>
+      <c r="T136" s="57"/>
+      <c r="U136" s="57"/>
+      <c r="V136" s="57"/>
+      <c r="W136" s="57"/>
+      <c r="X136" s="57"/>
+      <c r="Y136" s="57"/>
+      <c r="Z136" s="57"/>
+      <c r="AA136" s="57"/>
+      <c r="AB136" s="57"/>
+      <c r="AC136" s="57"/>
     </row>
     <row r="137" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="53"/>
-      <c r="B137" s="55"/>
-      <c r="C137" s="56"/>
-      <c r="D137" s="56"/>
-      <c r="E137" s="56"/>
-      <c r="F137" s="58"/>
-      <c r="G137" s="58"/>
-      <c r="H137" s="58"/>
-      <c r="I137" s="58"/>
-      <c r="J137" s="58"/>
-      <c r="K137" s="58"/>
-      <c r="L137" s="58"/>
-      <c r="M137" s="58"/>
-      <c r="N137" s="58"/>
-      <c r="O137" s="58"/>
-      <c r="P137" s="58"/>
-      <c r="Q137" s="58"/>
-      <c r="R137" s="58"/>
-      <c r="S137" s="58"/>
-      <c r="T137" s="58"/>
-      <c r="U137" s="58"/>
-      <c r="V137" s="58"/>
-      <c r="W137" s="58"/>
-      <c r="X137" s="58"/>
-      <c r="Y137" s="58"/>
-      <c r="Z137" s="58"/>
-      <c r="AA137" s="58"/>
-      <c r="AB137" s="58"/>
-      <c r="AC137" s="58"/>
+      <c r="A137" s="52"/>
+      <c r="B137" s="54"/>
+      <c r="C137" s="55"/>
+      <c r="D137" s="55"/>
+      <c r="E137" s="55"/>
+      <c r="F137" s="57"/>
+      <c r="G137" s="57"/>
+      <c r="H137" s="57"/>
+      <c r="I137" s="57"/>
+      <c r="J137" s="57"/>
+      <c r="K137" s="57"/>
+      <c r="L137" s="57"/>
+      <c r="M137" s="57"/>
+      <c r="N137" s="57"/>
+      <c r="O137" s="57"/>
+      <c r="P137" s="57"/>
+      <c r="Q137" s="57"/>
+      <c r="R137" s="57"/>
+      <c r="S137" s="57"/>
+      <c r="T137" s="57"/>
+      <c r="U137" s="57"/>
+      <c r="V137" s="57"/>
+      <c r="W137" s="57"/>
+      <c r="X137" s="57"/>
+      <c r="Y137" s="57"/>
+      <c r="Z137" s="57"/>
+      <c r="AA137" s="57"/>
+      <c r="AB137" s="57"/>
+      <c r="AC137" s="57"/>
     </row>
     <row r="138" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="53"/>
-      <c r="B138" s="55"/>
-      <c r="C138" s="56"/>
-      <c r="D138" s="56"/>
-      <c r="E138" s="56"/>
-      <c r="F138" s="58"/>
-      <c r="G138" s="58"/>
-      <c r="H138" s="58"/>
-      <c r="I138" s="58"/>
-      <c r="J138" s="58"/>
-      <c r="K138" s="58"/>
-      <c r="L138" s="58"/>
-      <c r="M138" s="58"/>
-      <c r="N138" s="58"/>
-      <c r="O138" s="58"/>
-      <c r="P138" s="58"/>
-      <c r="Q138" s="58"/>
-      <c r="R138" s="58"/>
-      <c r="S138" s="58"/>
-      <c r="T138" s="58"/>
-      <c r="U138" s="58"/>
-      <c r="V138" s="58"/>
-      <c r="W138" s="58"/>
-      <c r="X138" s="58"/>
-      <c r="Y138" s="58"/>
-      <c r="Z138" s="58"/>
-      <c r="AA138" s="58"/>
-      <c r="AB138" s="58"/>
-      <c r="AC138" s="58"/>
+      <c r="A138" s="52"/>
+      <c r="B138" s="54"/>
+      <c r="C138" s="55"/>
+      <c r="D138" s="55"/>
+      <c r="E138" s="55"/>
+      <c r="F138" s="57"/>
+      <c r="G138" s="57"/>
+      <c r="H138" s="57"/>
+      <c r="I138" s="57"/>
+      <c r="J138" s="57"/>
+      <c r="K138" s="57"/>
+      <c r="L138" s="57"/>
+      <c r="M138" s="57"/>
+      <c r="N138" s="57"/>
+      <c r="O138" s="57"/>
+      <c r="P138" s="57"/>
+      <c r="Q138" s="57"/>
+      <c r="R138" s="57"/>
+      <c r="S138" s="57"/>
+      <c r="T138" s="57"/>
+      <c r="U138" s="57"/>
+      <c r="V138" s="57"/>
+      <c r="W138" s="57"/>
+      <c r="X138" s="57"/>
+      <c r="Y138" s="57"/>
+      <c r="Z138" s="57"/>
+      <c r="AA138" s="57"/>
+      <c r="AB138" s="57"/>
+      <c r="AC138" s="57"/>
     </row>
     <row r="139" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="53"/>
-      <c r="B139" s="55"/>
-      <c r="C139" s="56"/>
-      <c r="D139" s="56"/>
-      <c r="E139" s="56"/>
-      <c r="F139" s="58"/>
-      <c r="G139" s="58"/>
-      <c r="H139" s="58"/>
-      <c r="I139" s="58"/>
-      <c r="J139" s="58"/>
-      <c r="K139" s="58"/>
-      <c r="L139" s="58"/>
-      <c r="M139" s="58"/>
-      <c r="N139" s="58"/>
-      <c r="O139" s="58"/>
-      <c r="P139" s="58"/>
-      <c r="Q139" s="58"/>
-      <c r="R139" s="58"/>
-      <c r="S139" s="58"/>
-      <c r="T139" s="58"/>
-      <c r="U139" s="58"/>
-      <c r="V139" s="58"/>
-      <c r="W139" s="58"/>
-      <c r="X139" s="58"/>
-      <c r="Y139" s="58"/>
-      <c r="Z139" s="58"/>
-      <c r="AA139" s="58"/>
-      <c r="AB139" s="58"/>
-      <c r="AC139" s="58"/>
+      <c r="A139" s="52"/>
+      <c r="B139" s="54"/>
+      <c r="C139" s="55"/>
+      <c r="D139" s="55"/>
+      <c r="E139" s="55"/>
+      <c r="F139" s="57"/>
+      <c r="G139" s="57"/>
+      <c r="H139" s="57"/>
+      <c r="I139" s="57"/>
+      <c r="J139" s="57"/>
+      <c r="K139" s="57"/>
+      <c r="L139" s="57"/>
+      <c r="M139" s="57"/>
+      <c r="N139" s="57"/>
+      <c r="O139" s="57"/>
+      <c r="P139" s="57"/>
+      <c r="Q139" s="57"/>
+      <c r="R139" s="57"/>
+      <c r="S139" s="57"/>
+      <c r="T139" s="57"/>
+      <c r="U139" s="57"/>
+      <c r="V139" s="57"/>
+      <c r="W139" s="57"/>
+      <c r="X139" s="57"/>
+      <c r="Y139" s="57"/>
+      <c r="Z139" s="57"/>
+      <c r="AA139" s="57"/>
+      <c r="AB139" s="57"/>
+      <c r="AC139" s="57"/>
     </row>
     <row r="140" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="53"/>
-      <c r="B140" s="55"/>
-      <c r="C140" s="56"/>
-      <c r="D140" s="56"/>
-      <c r="E140" s="56"/>
-      <c r="F140" s="58"/>
-      <c r="G140" s="58"/>
-      <c r="H140" s="58"/>
-      <c r="I140" s="58"/>
-      <c r="J140" s="58"/>
-      <c r="K140" s="58"/>
-      <c r="L140" s="58"/>
-      <c r="M140" s="58"/>
-      <c r="N140" s="58"/>
-      <c r="O140" s="58"/>
-      <c r="P140" s="58"/>
-      <c r="Q140" s="58"/>
-      <c r="R140" s="58"/>
-      <c r="S140" s="58"/>
-      <c r="T140" s="58"/>
-      <c r="U140" s="58"/>
-      <c r="V140" s="58"/>
-      <c r="W140" s="58"/>
-      <c r="X140" s="58"/>
-      <c r="Y140" s="58"/>
-      <c r="Z140" s="58"/>
-      <c r="AA140" s="58"/>
-      <c r="AB140" s="58"/>
-      <c r="AC140" s="58"/>
+      <c r="A140" s="52"/>
+      <c r="B140" s="54"/>
+      <c r="C140" s="55"/>
+      <c r="D140" s="55"/>
+      <c r="E140" s="55"/>
+      <c r="F140" s="57"/>
+      <c r="G140" s="57"/>
+      <c r="H140" s="57"/>
+      <c r="I140" s="57"/>
+      <c r="J140" s="57"/>
+      <c r="K140" s="57"/>
+      <c r="L140" s="57"/>
+      <c r="M140" s="57"/>
+      <c r="N140" s="57"/>
+      <c r="O140" s="57"/>
+      <c r="P140" s="57"/>
+      <c r="Q140" s="57"/>
+      <c r="R140" s="57"/>
+      <c r="S140" s="57"/>
+      <c r="T140" s="57"/>
+      <c r="U140" s="57"/>
+      <c r="V140" s="57"/>
+      <c r="W140" s="57"/>
+      <c r="X140" s="57"/>
+      <c r="Y140" s="57"/>
+      <c r="Z140" s="57"/>
+      <c r="AA140" s="57"/>
+      <c r="AB140" s="57"/>
+      <c r="AC140" s="57"/>
     </row>
     <row r="141" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="53"/>
-      <c r="B141" s="55"/>
-      <c r="C141" s="56"/>
-      <c r="D141" s="56"/>
-      <c r="E141" s="56"/>
-      <c r="F141" s="58"/>
-      <c r="G141" s="58"/>
-      <c r="H141" s="58"/>
-      <c r="I141" s="58"/>
-      <c r="J141" s="58"/>
-      <c r="K141" s="58"/>
-      <c r="L141" s="58"/>
-      <c r="M141" s="58"/>
-      <c r="N141" s="58"/>
-      <c r="O141" s="58"/>
-      <c r="P141" s="58"/>
-      <c r="Q141" s="58"/>
-      <c r="R141" s="58"/>
-      <c r="S141" s="58"/>
-      <c r="T141" s="58"/>
-      <c r="U141" s="58"/>
-      <c r="V141" s="58"/>
-      <c r="W141" s="58"/>
-      <c r="X141" s="58"/>
-      <c r="Y141" s="58"/>
-      <c r="Z141" s="58"/>
-      <c r="AA141" s="58"/>
-      <c r="AB141" s="58"/>
-      <c r="AC141" s="58"/>
+      <c r="A141" s="52"/>
+      <c r="B141" s="54"/>
+      <c r="C141" s="55"/>
+      <c r="D141" s="55"/>
+      <c r="E141" s="55"/>
+      <c r="F141" s="57"/>
+      <c r="G141" s="57"/>
+      <c r="H141" s="57"/>
+      <c r="I141" s="57"/>
+      <c r="J141" s="57"/>
+      <c r="K141" s="57"/>
+      <c r="L141" s="57"/>
+      <c r="M141" s="57"/>
+      <c r="N141" s="57"/>
+      <c r="O141" s="57"/>
+      <c r="P141" s="57"/>
+      <c r="Q141" s="57"/>
+      <c r="R141" s="57"/>
+      <c r="S141" s="57"/>
+      <c r="T141" s="57"/>
+      <c r="U141" s="57"/>
+      <c r="V141" s="57"/>
+      <c r="W141" s="57"/>
+      <c r="X141" s="57"/>
+      <c r="Y141" s="57"/>
+      <c r="Z141" s="57"/>
+      <c r="AA141" s="57"/>
+      <c r="AB141" s="57"/>
+      <c r="AC141" s="57"/>
     </row>
     <row r="142" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="53"/>
-      <c r="B142" s="55"/>
-      <c r="C142" s="56"/>
-      <c r="D142" s="56"/>
-      <c r="E142" s="56"/>
-      <c r="F142" s="58"/>
-      <c r="G142" s="58"/>
-      <c r="H142" s="58"/>
-      <c r="I142" s="58"/>
-      <c r="J142" s="58"/>
-      <c r="K142" s="58"/>
-      <c r="L142" s="58"/>
-      <c r="M142" s="58"/>
-      <c r="N142" s="58"/>
-      <c r="O142" s="58"/>
-      <c r="P142" s="58"/>
-      <c r="Q142" s="58"/>
-      <c r="R142" s="58"/>
-      <c r="S142" s="58"/>
-      <c r="T142" s="58"/>
-      <c r="U142" s="58"/>
-      <c r="V142" s="58"/>
-      <c r="W142" s="58"/>
-      <c r="X142" s="58"/>
-      <c r="Y142" s="58"/>
-      <c r="Z142" s="58"/>
-      <c r="AA142" s="58"/>
-      <c r="AB142" s="58"/>
-      <c r="AC142" s="58"/>
+      <c r="A142" s="52"/>
+      <c r="B142" s="54"/>
+      <c r="C142" s="55"/>
+      <c r="D142" s="55"/>
+      <c r="E142" s="55"/>
+      <c r="F142" s="57"/>
+      <c r="G142" s="57"/>
+      <c r="H142" s="57"/>
+      <c r="I142" s="57"/>
+      <c r="J142" s="57"/>
+      <c r="K142" s="57"/>
+      <c r="L142" s="57"/>
+      <c r="M142" s="57"/>
+      <c r="N142" s="57"/>
+      <c r="O142" s="57"/>
+      <c r="P142" s="57"/>
+      <c r="Q142" s="57"/>
+      <c r="R142" s="57"/>
+      <c r="S142" s="57"/>
+      <c r="T142" s="57"/>
+      <c r="U142" s="57"/>
+      <c r="V142" s="57"/>
+      <c r="W142" s="57"/>
+      <c r="X142" s="57"/>
+      <c r="Y142" s="57"/>
+      <c r="Z142" s="57"/>
+      <c r="AA142" s="57"/>
+      <c r="AB142" s="57"/>
+      <c r="AC142" s="57"/>
     </row>
     <row r="143" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="53"/>
-      <c r="B143" s="55"/>
-      <c r="C143" s="56"/>
-      <c r="D143" s="56"/>
-      <c r="E143" s="56"/>
-      <c r="F143" s="58"/>
-      <c r="G143" s="58"/>
-      <c r="H143" s="58"/>
-      <c r="I143" s="58"/>
-      <c r="J143" s="58"/>
-      <c r="K143" s="58"/>
-      <c r="L143" s="58"/>
-      <c r="M143" s="58"/>
-      <c r="N143" s="58"/>
-      <c r="O143" s="58"/>
-      <c r="P143" s="58"/>
-      <c r="Q143" s="58"/>
-      <c r="R143" s="58"/>
-      <c r="S143" s="58"/>
-      <c r="T143" s="58"/>
-      <c r="U143" s="58"/>
-      <c r="V143" s="58"/>
-      <c r="W143" s="58"/>
-      <c r="X143" s="58"/>
-      <c r="Y143" s="58"/>
-      <c r="Z143" s="58"/>
-      <c r="AA143" s="58"/>
-      <c r="AB143" s="58"/>
-      <c r="AC143" s="58"/>
+      <c r="A143" s="52"/>
+      <c r="B143" s="54"/>
+      <c r="C143" s="55"/>
+      <c r="D143" s="55"/>
+      <c r="E143" s="55"/>
+      <c r="F143" s="57"/>
+      <c r="G143" s="57"/>
+      <c r="H143" s="57"/>
+      <c r="I143" s="57"/>
+      <c r="J143" s="57"/>
+      <c r="K143" s="57"/>
+      <c r="L143" s="57"/>
+      <c r="M143" s="57"/>
+      <c r="N143" s="57"/>
+      <c r="O143" s="57"/>
+      <c r="P143" s="57"/>
+      <c r="Q143" s="57"/>
+      <c r="R143" s="57"/>
+      <c r="S143" s="57"/>
+      <c r="T143" s="57"/>
+      <c r="U143" s="57"/>
+      <c r="V143" s="57"/>
+      <c r="W143" s="57"/>
+      <c r="X143" s="57"/>
+      <c r="Y143" s="57"/>
+      <c r="Z143" s="57"/>
+      <c r="AA143" s="57"/>
+      <c r="AB143" s="57"/>
+      <c r="AC143" s="57"/>
     </row>
     <row r="144" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="53"/>
-      <c r="B144" s="55"/>
-      <c r="C144" s="56"/>
-      <c r="D144" s="56"/>
-      <c r="E144" s="56"/>
-      <c r="F144" s="52"/>
-      <c r="G144" s="52"/>
-      <c r="H144" s="52"/>
-      <c r="I144" s="52"/>
-      <c r="J144" s="52"/>
-      <c r="K144" s="52"/>
-      <c r="L144" s="52"/>
-      <c r="M144" s="52"/>
-      <c r="N144" s="52"/>
-      <c r="O144" s="52"/>
-      <c r="P144" s="52"/>
-      <c r="Q144" s="52"/>
-      <c r="R144" s="52"/>
-      <c r="S144" s="52"/>
-      <c r="T144" s="52"/>
-      <c r="U144" s="52"/>
-      <c r="V144" s="52"/>
-      <c r="W144" s="52"/>
-      <c r="X144" s="52"/>
-      <c r="Y144" s="52"/>
-      <c r="Z144" s="52"/>
-      <c r="AA144" s="52"/>
-      <c r="AB144" s="52"/>
-      <c r="AC144" s="52"/>
+      <c r="A144" s="52"/>
+      <c r="B144" s="54"/>
+      <c r="C144" s="55"/>
+      <c r="D144" s="55"/>
+      <c r="E144" s="55"/>
+      <c r="F144" s="51"/>
+      <c r="G144" s="51"/>
+      <c r="H144" s="51"/>
+      <c r="I144" s="51"/>
+      <c r="J144" s="51"/>
+      <c r="K144" s="51"/>
+      <c r="L144" s="51"/>
+      <c r="M144" s="51"/>
+      <c r="N144" s="51"/>
+      <c r="O144" s="51"/>
+      <c r="P144" s="51"/>
+      <c r="Q144" s="51"/>
+      <c r="R144" s="51"/>
+      <c r="S144" s="51"/>
+      <c r="T144" s="51"/>
+      <c r="U144" s="51"/>
+      <c r="V144" s="51"/>
+      <c r="W144" s="51"/>
+      <c r="X144" s="51"/>
+      <c r="Y144" s="51"/>
+      <c r="Z144" s="51"/>
+      <c r="AA144" s="51"/>
+      <c r="AB144" s="51"/>
+      <c r="AC144" s="51"/>
     </row>
     <row r="145" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="53"/>
-      <c r="B145" s="55"/>
-      <c r="C145" s="56"/>
-      <c r="D145" s="56"/>
-      <c r="E145" s="56"/>
-      <c r="F145" s="58"/>
-      <c r="G145" s="58"/>
-      <c r="H145" s="58"/>
-      <c r="I145" s="58"/>
-      <c r="J145" s="58"/>
-      <c r="K145" s="58"/>
-      <c r="L145" s="58"/>
-      <c r="M145" s="58"/>
-      <c r="N145" s="58"/>
-      <c r="O145" s="58"/>
-      <c r="P145" s="58"/>
-      <c r="Q145" s="58"/>
-      <c r="R145" s="58"/>
-      <c r="S145" s="58"/>
-      <c r="T145" s="58"/>
-      <c r="U145" s="58"/>
-      <c r="V145" s="58"/>
-      <c r="W145" s="58"/>
-      <c r="X145" s="58"/>
-      <c r="Y145" s="58"/>
-      <c r="Z145" s="58"/>
-      <c r="AA145" s="58"/>
-      <c r="AB145" s="58"/>
-      <c r="AC145" s="58"/>
+      <c r="A145" s="52"/>
+      <c r="B145" s="54"/>
+      <c r="C145" s="55"/>
+      <c r="D145" s="55"/>
+      <c r="E145" s="55"/>
+      <c r="F145" s="57"/>
+      <c r="G145" s="57"/>
+      <c r="H145" s="57"/>
+      <c r="I145" s="57"/>
+      <c r="J145" s="57"/>
+      <c r="K145" s="57"/>
+      <c r="L145" s="57"/>
+      <c r="M145" s="57"/>
+      <c r="N145" s="57"/>
+      <c r="O145" s="57"/>
+      <c r="P145" s="57"/>
+      <c r="Q145" s="57"/>
+      <c r="R145" s="57"/>
+      <c r="S145" s="57"/>
+      <c r="T145" s="57"/>
+      <c r="U145" s="57"/>
+      <c r="V145" s="57"/>
+      <c r="W145" s="57"/>
+      <c r="X145" s="57"/>
+      <c r="Y145" s="57"/>
+      <c r="Z145" s="57"/>
+      <c r="AA145" s="57"/>
+      <c r="AB145" s="57"/>
+      <c r="AC145" s="57"/>
     </row>
     <row r="146" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="53"/>
-      <c r="B146" s="55"/>
-      <c r="C146" s="56"/>
-      <c r="D146" s="56"/>
-      <c r="E146" s="56"/>
-      <c r="F146" s="58"/>
-      <c r="G146" s="58"/>
-      <c r="H146" s="58"/>
-      <c r="I146" s="58"/>
-      <c r="J146" s="58"/>
-      <c r="K146" s="58"/>
-      <c r="L146" s="58"/>
-      <c r="M146" s="58"/>
-      <c r="N146" s="58"/>
-      <c r="O146" s="58"/>
-      <c r="P146" s="58"/>
-      <c r="Q146" s="58"/>
-      <c r="R146" s="58"/>
-      <c r="S146" s="58"/>
-      <c r="T146" s="58"/>
-      <c r="U146" s="58"/>
-      <c r="V146" s="58"/>
-      <c r="W146" s="58"/>
-      <c r="X146" s="58"/>
-      <c r="Y146" s="58"/>
-      <c r="Z146" s="58"/>
-      <c r="AA146" s="58"/>
-      <c r="AB146" s="58"/>
-      <c r="AC146" s="58"/>
+      <c r="A146" s="52"/>
+      <c r="B146" s="54"/>
+      <c r="C146" s="55"/>
+      <c r="D146" s="55"/>
+      <c r="E146" s="55"/>
+      <c r="F146" s="57"/>
+      <c r="G146" s="57"/>
+      <c r="H146" s="57"/>
+      <c r="I146" s="57"/>
+      <c r="J146" s="57"/>
+      <c r="K146" s="57"/>
+      <c r="L146" s="57"/>
+      <c r="M146" s="57"/>
+      <c r="N146" s="57"/>
+      <c r="O146" s="57"/>
+      <c r="P146" s="57"/>
+      <c r="Q146" s="57"/>
+      <c r="R146" s="57"/>
+      <c r="S146" s="57"/>
+      <c r="T146" s="57"/>
+      <c r="U146" s="57"/>
+      <c r="V146" s="57"/>
+      <c r="W146" s="57"/>
+      <c r="X146" s="57"/>
+      <c r="Y146" s="57"/>
+      <c r="Z146" s="57"/>
+      <c r="AA146" s="57"/>
+      <c r="AB146" s="57"/>
+      <c r="AC146" s="57"/>
     </row>
     <row r="147" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="53"/>
-      <c r="B147" s="55"/>
-      <c r="C147" s="56"/>
-      <c r="D147" s="56"/>
-      <c r="E147" s="56"/>
-      <c r="F147" s="58"/>
-      <c r="G147" s="58"/>
-      <c r="H147" s="58"/>
-      <c r="I147" s="58"/>
-      <c r="J147" s="58"/>
-      <c r="K147" s="58"/>
-      <c r="L147" s="58"/>
-      <c r="M147" s="58"/>
-      <c r="N147" s="58"/>
-      <c r="O147" s="58"/>
-      <c r="P147" s="58"/>
-      <c r="Q147" s="58"/>
-      <c r="R147" s="58"/>
-      <c r="S147" s="58"/>
-      <c r="T147" s="58"/>
-      <c r="U147" s="58"/>
-      <c r="V147" s="58"/>
-      <c r="W147" s="58"/>
-      <c r="X147" s="58"/>
-      <c r="Y147" s="58"/>
-      <c r="Z147" s="58"/>
-      <c r="AA147" s="58"/>
-      <c r="AB147" s="58"/>
-      <c r="AC147" s="58"/>
+      <c r="A147" s="52"/>
+      <c r="B147" s="54"/>
+      <c r="C147" s="55"/>
+      <c r="D147" s="55"/>
+      <c r="E147" s="55"/>
+      <c r="F147" s="57"/>
+      <c r="G147" s="57"/>
+      <c r="H147" s="57"/>
+      <c r="I147" s="57"/>
+      <c r="J147" s="57"/>
+      <c r="K147" s="57"/>
+      <c r="L147" s="57"/>
+      <c r="M147" s="57"/>
+      <c r="N147" s="57"/>
+      <c r="O147" s="57"/>
+      <c r="P147" s="57"/>
+      <c r="Q147" s="57"/>
+      <c r="R147" s="57"/>
+      <c r="S147" s="57"/>
+      <c r="T147" s="57"/>
+      <c r="U147" s="57"/>
+      <c r="V147" s="57"/>
+      <c r="W147" s="57"/>
+      <c r="X147" s="57"/>
+      <c r="Y147" s="57"/>
+      <c r="Z147" s="57"/>
+      <c r="AA147" s="57"/>
+      <c r="AB147" s="57"/>
+      <c r="AC147" s="57"/>
     </row>
     <row r="148" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="53"/>
-      <c r="B148" s="54"/>
-      <c r="C148" s="54"/>
-      <c r="D148" s="54"/>
-      <c r="E148" s="54"/>
-      <c r="F148" s="58"/>
-      <c r="G148" s="58"/>
-      <c r="H148" s="58"/>
-      <c r="I148" s="58"/>
-      <c r="J148" s="58"/>
-      <c r="K148" s="58"/>
-      <c r="L148" s="58"/>
-      <c r="M148" s="58"/>
-      <c r="N148" s="58"/>
-      <c r="O148" s="58"/>
-      <c r="P148" s="58"/>
-      <c r="Q148" s="58"/>
-      <c r="R148" s="58"/>
-      <c r="S148" s="58"/>
-      <c r="T148" s="58"/>
-      <c r="U148" s="58"/>
-      <c r="V148" s="58"/>
-      <c r="W148" s="58"/>
-      <c r="X148" s="58"/>
-      <c r="Y148" s="58"/>
-      <c r="Z148" s="58"/>
-      <c r="AA148" s="58"/>
-      <c r="AB148" s="58"/>
-      <c r="AC148" s="58"/>
+      <c r="A148" s="52"/>
+      <c r="B148" s="53"/>
+      <c r="C148" s="53"/>
+      <c r="D148" s="53"/>
+      <c r="E148" s="53"/>
+      <c r="F148" s="57"/>
+      <c r="G148" s="57"/>
+      <c r="H148" s="57"/>
+      <c r="I148" s="57"/>
+      <c r="J148" s="57"/>
+      <c r="K148" s="57"/>
+      <c r="L148" s="57"/>
+      <c r="M148" s="57"/>
+      <c r="N148" s="57"/>
+      <c r="O148" s="57"/>
+      <c r="P148" s="57"/>
+      <c r="Q148" s="57"/>
+      <c r="R148" s="57"/>
+      <c r="S148" s="57"/>
+      <c r="T148" s="57"/>
+      <c r="U148" s="57"/>
+      <c r="V148" s="57"/>
+      <c r="W148" s="57"/>
+      <c r="X148" s="57"/>
+      <c r="Y148" s="57"/>
+      <c r="Z148" s="57"/>
+      <c r="AA148" s="57"/>
+      <c r="AB148" s="57"/>
+      <c r="AC148" s="57"/>
     </row>
     <row r="149" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="53"/>
-      <c r="B149" s="54"/>
-      <c r="C149" s="55"/>
-      <c r="D149" s="55"/>
-      <c r="E149" s="55"/>
-      <c r="F149" s="58"/>
-      <c r="G149" s="58"/>
-      <c r="H149" s="58"/>
-      <c r="I149" s="58"/>
-      <c r="J149" s="58"/>
-      <c r="K149" s="58"/>
-      <c r="L149" s="58"/>
-      <c r="M149" s="58"/>
-      <c r="N149" s="58"/>
-      <c r="O149" s="58"/>
-      <c r="P149" s="58"/>
-      <c r="Q149" s="58"/>
-      <c r="R149" s="58"/>
-      <c r="S149" s="58"/>
-      <c r="T149" s="58"/>
-      <c r="U149" s="58"/>
-      <c r="V149" s="58"/>
-      <c r="W149" s="58"/>
-      <c r="X149" s="58"/>
-      <c r="Y149" s="58"/>
-      <c r="Z149" s="58"/>
-      <c r="AA149" s="58"/>
-      <c r="AB149" s="58"/>
-      <c r="AC149" s="58"/>
+      <c r="A149" s="52"/>
+      <c r="B149" s="53"/>
+      <c r="C149" s="54"/>
+      <c r="D149" s="54"/>
+      <c r="E149" s="54"/>
+      <c r="F149" s="57"/>
+      <c r="G149" s="57"/>
+      <c r="H149" s="57"/>
+      <c r="I149" s="57"/>
+      <c r="J149" s="57"/>
+      <c r="K149" s="57"/>
+      <c r="L149" s="57"/>
+      <c r="M149" s="57"/>
+      <c r="N149" s="57"/>
+      <c r="O149" s="57"/>
+      <c r="P149" s="57"/>
+      <c r="Q149" s="57"/>
+      <c r="R149" s="57"/>
+      <c r="S149" s="57"/>
+      <c r="T149" s="57"/>
+      <c r="U149" s="57"/>
+      <c r="V149" s="57"/>
+      <c r="W149" s="57"/>
+      <c r="X149" s="57"/>
+      <c r="Y149" s="57"/>
+      <c r="Z149" s="57"/>
+      <c r="AA149" s="57"/>
+      <c r="AB149" s="57"/>
+      <c r="AC149" s="57"/>
     </row>
     <row r="150" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="53"/>
-      <c r="B150" s="55"/>
-      <c r="C150" s="56"/>
-      <c r="D150" s="56"/>
-      <c r="E150" s="56"/>
-      <c r="F150" s="58"/>
-      <c r="G150" s="58"/>
-      <c r="H150" s="58"/>
-      <c r="I150" s="58"/>
-      <c r="J150" s="58"/>
-      <c r="K150" s="58"/>
-      <c r="L150" s="58"/>
-      <c r="M150" s="58"/>
-      <c r="N150" s="58"/>
-      <c r="O150" s="58"/>
-      <c r="P150" s="58"/>
-      <c r="Q150" s="58"/>
-      <c r="R150" s="58"/>
-      <c r="S150" s="58"/>
-      <c r="T150" s="58"/>
-      <c r="U150" s="58"/>
-      <c r="V150" s="58"/>
-      <c r="W150" s="58"/>
-      <c r="X150" s="58"/>
-      <c r="Y150" s="58"/>
-      <c r="Z150" s="58"/>
-      <c r="AA150" s="58"/>
-      <c r="AB150" s="58"/>
-      <c r="AC150" s="58"/>
+      <c r="A150" s="52"/>
+      <c r="B150" s="54"/>
+      <c r="C150" s="55"/>
+      <c r="D150" s="55"/>
+      <c r="E150" s="55"/>
+      <c r="F150" s="57"/>
+      <c r="G150" s="57"/>
+      <c r="H150" s="57"/>
+      <c r="I150" s="57"/>
+      <c r="J150" s="57"/>
+      <c r="K150" s="57"/>
+      <c r="L150" s="57"/>
+      <c r="M150" s="57"/>
+      <c r="N150" s="57"/>
+      <c r="O150" s="57"/>
+      <c r="P150" s="57"/>
+      <c r="Q150" s="57"/>
+      <c r="R150" s="57"/>
+      <c r="S150" s="57"/>
+      <c r="T150" s="57"/>
+      <c r="U150" s="57"/>
+      <c r="V150" s="57"/>
+      <c r="W150" s="57"/>
+      <c r="X150" s="57"/>
+      <c r="Y150" s="57"/>
+      <c r="Z150" s="57"/>
+      <c r="AA150" s="57"/>
+      <c r="AB150" s="57"/>
+      <c r="AC150" s="57"/>
     </row>
     <row r="151" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="53"/>
-      <c r="B151" s="55"/>
-      <c r="C151" s="56"/>
-      <c r="D151" s="56"/>
-      <c r="E151" s="56"/>
-      <c r="F151" s="58"/>
-      <c r="G151" s="58"/>
-      <c r="H151" s="58"/>
-      <c r="I151" s="58"/>
-      <c r="J151" s="58"/>
-      <c r="K151" s="58"/>
-      <c r="L151" s="58"/>
-      <c r="M151" s="58"/>
-      <c r="N151" s="58"/>
-      <c r="O151" s="58"/>
-      <c r="P151" s="58"/>
-      <c r="Q151" s="58"/>
-      <c r="R151" s="58"/>
-      <c r="S151" s="58"/>
-      <c r="T151" s="58"/>
-      <c r="U151" s="58"/>
-      <c r="V151" s="58"/>
-      <c r="W151" s="58"/>
-      <c r="X151" s="58"/>
-      <c r="Y151" s="58"/>
-      <c r="Z151" s="58"/>
-      <c r="AA151" s="58"/>
-      <c r="AB151" s="58"/>
-      <c r="AC151" s="58"/>
+      <c r="A151" s="52"/>
+      <c r="B151" s="54"/>
+      <c r="C151" s="55"/>
+      <c r="D151" s="55"/>
+      <c r="E151" s="55"/>
+      <c r="F151" s="57"/>
+      <c r="G151" s="57"/>
+      <c r="H151" s="57"/>
+      <c r="I151" s="57"/>
+      <c r="J151" s="57"/>
+      <c r="K151" s="57"/>
+      <c r="L151" s="57"/>
+      <c r="M151" s="57"/>
+      <c r="N151" s="57"/>
+      <c r="O151" s="57"/>
+      <c r="P151" s="57"/>
+      <c r="Q151" s="57"/>
+      <c r="R151" s="57"/>
+      <c r="S151" s="57"/>
+      <c r="T151" s="57"/>
+      <c r="U151" s="57"/>
+      <c r="V151" s="57"/>
+      <c r="W151" s="57"/>
+      <c r="X151" s="57"/>
+      <c r="Y151" s="57"/>
+      <c r="Z151" s="57"/>
+      <c r="AA151" s="57"/>
+      <c r="AB151" s="57"/>
+      <c r="AC151" s="57"/>
     </row>
     <row r="152" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="53"/>
-      <c r="B152" s="55"/>
-      <c r="C152" s="56"/>
-      <c r="D152" s="56"/>
-      <c r="E152" s="56"/>
-      <c r="F152" s="58"/>
-      <c r="G152" s="58"/>
-      <c r="H152" s="58"/>
-      <c r="I152" s="58"/>
-      <c r="J152" s="58"/>
-      <c r="K152" s="58"/>
-      <c r="L152" s="58"/>
-      <c r="M152" s="58"/>
-      <c r="N152" s="58"/>
-      <c r="O152" s="58"/>
-      <c r="P152" s="58"/>
-      <c r="Q152" s="58"/>
-      <c r="R152" s="58"/>
-      <c r="S152" s="58"/>
-      <c r="T152" s="58"/>
-      <c r="U152" s="58"/>
-      <c r="V152" s="58"/>
-      <c r="W152" s="58"/>
-      <c r="X152" s="58"/>
-      <c r="Y152" s="58"/>
-      <c r="Z152" s="58"/>
-      <c r="AA152" s="58"/>
-      <c r="AB152" s="58"/>
-      <c r="AC152" s="58"/>
+      <c r="A152" s="52"/>
+      <c r="B152" s="54"/>
+      <c r="C152" s="55"/>
+      <c r="D152" s="55"/>
+      <c r="E152" s="55"/>
+      <c r="F152" s="57"/>
+      <c r="G152" s="57"/>
+      <c r="H152" s="57"/>
+      <c r="I152" s="57"/>
+      <c r="J152" s="57"/>
+      <c r="K152" s="57"/>
+      <c r="L152" s="57"/>
+      <c r="M152" s="57"/>
+      <c r="N152" s="57"/>
+      <c r="O152" s="57"/>
+      <c r="P152" s="57"/>
+      <c r="Q152" s="57"/>
+      <c r="R152" s="57"/>
+      <c r="S152" s="57"/>
+      <c r="T152" s="57"/>
+      <c r="U152" s="57"/>
+      <c r="V152" s="57"/>
+      <c r="W152" s="57"/>
+      <c r="X152" s="57"/>
+      <c r="Y152" s="57"/>
+      <c r="Z152" s="57"/>
+      <c r="AA152" s="57"/>
+      <c r="AB152" s="57"/>
+      <c r="AC152" s="57"/>
     </row>
     <row r="153" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="53"/>
-      <c r="B153" s="55"/>
-      <c r="C153" s="56"/>
-      <c r="D153" s="56"/>
-      <c r="E153" s="56"/>
-      <c r="F153" s="58"/>
-      <c r="G153" s="58"/>
-      <c r="H153" s="58"/>
-      <c r="I153" s="58"/>
-      <c r="J153" s="58"/>
-      <c r="K153" s="58"/>
-      <c r="L153" s="58"/>
-      <c r="M153" s="58"/>
-      <c r="N153" s="58"/>
-      <c r="O153" s="58"/>
-      <c r="P153" s="58"/>
-      <c r="Q153" s="58"/>
-      <c r="R153" s="58"/>
-      <c r="S153" s="58"/>
-      <c r="T153" s="58"/>
-      <c r="U153" s="58"/>
-      <c r="V153" s="58"/>
-      <c r="W153" s="58"/>
-      <c r="X153" s="58"/>
-      <c r="Y153" s="58"/>
-      <c r="Z153" s="58"/>
-      <c r="AA153" s="58"/>
-      <c r="AB153" s="58"/>
-      <c r="AC153" s="58"/>
+      <c r="A153" s="52"/>
+      <c r="B153" s="54"/>
+      <c r="C153" s="55"/>
+      <c r="D153" s="55"/>
+      <c r="E153" s="55"/>
+      <c r="F153" s="57"/>
+      <c r="G153" s="57"/>
+      <c r="H153" s="57"/>
+      <c r="I153" s="57"/>
+      <c r="J153" s="57"/>
+      <c r="K153" s="57"/>
+      <c r="L153" s="57"/>
+      <c r="M153" s="57"/>
+      <c r="N153" s="57"/>
+      <c r="O153" s="57"/>
+      <c r="P153" s="57"/>
+      <c r="Q153" s="57"/>
+      <c r="R153" s="57"/>
+      <c r="S153" s="57"/>
+      <c r="T153" s="57"/>
+      <c r="U153" s="57"/>
+      <c r="V153" s="57"/>
+      <c r="W153" s="57"/>
+      <c r="X153" s="57"/>
+      <c r="Y153" s="57"/>
+      <c r="Z153" s="57"/>
+      <c r="AA153" s="57"/>
+      <c r="AB153" s="57"/>
+      <c r="AC153" s="57"/>
     </row>
     <row r="154" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="53"/>
-      <c r="B154" s="55"/>
-      <c r="C154" s="56"/>
-      <c r="D154" s="56"/>
-      <c r="E154" s="56"/>
-      <c r="F154" s="58"/>
-      <c r="G154" s="58"/>
-      <c r="H154" s="58"/>
-      <c r="I154" s="58"/>
-      <c r="J154" s="58"/>
-      <c r="K154" s="58"/>
-      <c r="L154" s="58"/>
-      <c r="M154" s="58"/>
-      <c r="N154" s="58"/>
-      <c r="O154" s="58"/>
-      <c r="P154" s="58"/>
-      <c r="Q154" s="58"/>
-      <c r="R154" s="58"/>
-      <c r="S154" s="58"/>
-      <c r="T154" s="58"/>
-      <c r="U154" s="58"/>
-      <c r="V154" s="58"/>
-      <c r="W154" s="58"/>
-      <c r="X154" s="58"/>
-      <c r="Y154" s="58"/>
-      <c r="Z154" s="58"/>
-      <c r="AA154" s="58"/>
-      <c r="AB154" s="58"/>
-      <c r="AC154" s="58"/>
+      <c r="A154" s="52"/>
+      <c r="B154" s="54"/>
+      <c r="C154" s="55"/>
+      <c r="D154" s="55"/>
+      <c r="E154" s="55"/>
+      <c r="F154" s="57"/>
+      <c r="G154" s="57"/>
+      <c r="H154" s="57"/>
+      <c r="I154" s="57"/>
+      <c r="J154" s="57"/>
+      <c r="K154" s="57"/>
+      <c r="L154" s="57"/>
+      <c r="M154" s="57"/>
+      <c r="N154" s="57"/>
+      <c r="O154" s="57"/>
+      <c r="P154" s="57"/>
+      <c r="Q154" s="57"/>
+      <c r="R154" s="57"/>
+      <c r="S154" s="57"/>
+      <c r="T154" s="57"/>
+      <c r="U154" s="57"/>
+      <c r="V154" s="57"/>
+      <c r="W154" s="57"/>
+      <c r="X154" s="57"/>
+      <c r="Y154" s="57"/>
+      <c r="Z154" s="57"/>
+      <c r="AA154" s="57"/>
+      <c r="AB154" s="57"/>
+      <c r="AC154" s="57"/>
     </row>
     <row r="155" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="53"/>
-      <c r="B155" s="55"/>
-      <c r="C155" s="56"/>
-      <c r="D155" s="56"/>
-      <c r="E155" s="56"/>
-      <c r="F155" s="58"/>
-      <c r="G155" s="58"/>
-      <c r="H155" s="58"/>
-      <c r="I155" s="58"/>
-      <c r="J155" s="58"/>
-      <c r="K155" s="58"/>
-      <c r="L155" s="58"/>
-      <c r="M155" s="58"/>
-      <c r="N155" s="58"/>
-      <c r="O155" s="58"/>
-      <c r="P155" s="58"/>
-      <c r="Q155" s="58"/>
-      <c r="R155" s="58"/>
-      <c r="S155" s="58"/>
-      <c r="T155" s="58"/>
-      <c r="U155" s="58"/>
-      <c r="V155" s="58"/>
-      <c r="W155" s="58"/>
-      <c r="X155" s="58"/>
-      <c r="Y155" s="58"/>
-      <c r="Z155" s="58"/>
-      <c r="AA155" s="58"/>
-      <c r="AB155" s="58"/>
-      <c r="AC155" s="58"/>
+      <c r="A155" s="52"/>
+      <c r="B155" s="54"/>
+      <c r="C155" s="55"/>
+      <c r="D155" s="55"/>
+      <c r="E155" s="55"/>
+      <c r="F155" s="57"/>
+      <c r="G155" s="57"/>
+      <c r="H155" s="57"/>
+      <c r="I155" s="57"/>
+      <c r="J155" s="57"/>
+      <c r="K155" s="57"/>
+      <c r="L155" s="57"/>
+      <c r="M155" s="57"/>
+      <c r="N155" s="57"/>
+      <c r="O155" s="57"/>
+      <c r="P155" s="57"/>
+      <c r="Q155" s="57"/>
+      <c r="R155" s="57"/>
+      <c r="S155" s="57"/>
+      <c r="T155" s="57"/>
+      <c r="U155" s="57"/>
+      <c r="V155" s="57"/>
+      <c r="W155" s="57"/>
+      <c r="X155" s="57"/>
+      <c r="Y155" s="57"/>
+      <c r="Z155" s="57"/>
+      <c r="AA155" s="57"/>
+      <c r="AB155" s="57"/>
+      <c r="AC155" s="57"/>
     </row>
     <row r="156" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="53"/>
-      <c r="B156" s="55"/>
-      <c r="C156" s="56"/>
-      <c r="D156" s="56"/>
-      <c r="E156" s="56"/>
-      <c r="F156" s="52"/>
-      <c r="G156" s="52"/>
-      <c r="H156" s="52"/>
-      <c r="I156" s="52"/>
-      <c r="J156" s="52"/>
-      <c r="K156" s="52"/>
-      <c r="L156" s="52"/>
-      <c r="M156" s="52"/>
-      <c r="N156" s="52"/>
-      <c r="O156" s="52"/>
-      <c r="P156" s="52"/>
-      <c r="Q156" s="52"/>
-      <c r="R156" s="52"/>
-      <c r="S156" s="52"/>
-      <c r="T156" s="52"/>
-      <c r="U156" s="52"/>
-      <c r="V156" s="52"/>
-      <c r="W156" s="52"/>
-      <c r="X156" s="52"/>
-      <c r="Y156" s="52"/>
-      <c r="Z156" s="52"/>
-      <c r="AA156" s="52"/>
-      <c r="AB156" s="52"/>
-      <c r="AC156" s="52"/>
+      <c r="A156" s="52"/>
+      <c r="B156" s="54"/>
+      <c r="C156" s="55"/>
+      <c r="D156" s="55"/>
+      <c r="E156" s="55"/>
+      <c r="F156" s="51"/>
+      <c r="G156" s="51"/>
+      <c r="H156" s="51"/>
+      <c r="I156" s="51"/>
+      <c r="J156" s="51"/>
+      <c r="K156" s="51"/>
+      <c r="L156" s="51"/>
+      <c r="M156" s="51"/>
+      <c r="N156" s="51"/>
+      <c r="O156" s="51"/>
+      <c r="P156" s="51"/>
+      <c r="Q156" s="51"/>
+      <c r="R156" s="51"/>
+      <c r="S156" s="51"/>
+      <c r="T156" s="51"/>
+      <c r="U156" s="51"/>
+      <c r="V156" s="51"/>
+      <c r="W156" s="51"/>
+      <c r="X156" s="51"/>
+      <c r="Y156" s="51"/>
+      <c r="Z156" s="51"/>
+      <c r="AA156" s="51"/>
+      <c r="AB156" s="51"/>
+      <c r="AC156" s="51"/>
     </row>
     <row r="157" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="53"/>
-      <c r="B157" s="55"/>
-      <c r="C157" s="56"/>
-      <c r="D157" s="56"/>
-      <c r="E157" s="56"/>
-      <c r="F157" s="52"/>
-      <c r="G157" s="52"/>
-      <c r="H157" s="52"/>
-      <c r="I157" s="52"/>
-      <c r="J157" s="52"/>
-      <c r="K157" s="52"/>
-      <c r="L157" s="52"/>
-      <c r="M157" s="52"/>
-      <c r="N157" s="52"/>
-      <c r="O157" s="52"/>
-      <c r="P157" s="52"/>
-      <c r="Q157" s="52"/>
-      <c r="R157" s="52"/>
-      <c r="S157" s="52"/>
-      <c r="T157" s="52"/>
-      <c r="U157" s="52"/>
-      <c r="V157" s="52"/>
-      <c r="W157" s="52"/>
-      <c r="X157" s="52"/>
-      <c r="Y157" s="52"/>
-      <c r="Z157" s="52"/>
-      <c r="AA157" s="52"/>
-      <c r="AB157" s="52"/>
-      <c r="AC157" s="52"/>
+      <c r="A157" s="52"/>
+      <c r="B157" s="54"/>
+      <c r="C157" s="55"/>
+      <c r="D157" s="55"/>
+      <c r="E157" s="55"/>
+      <c r="F157" s="51"/>
+      <c r="G157" s="51"/>
+      <c r="H157" s="51"/>
+      <c r="I157" s="51"/>
+      <c r="J157" s="51"/>
+      <c r="K157" s="51"/>
+      <c r="L157" s="51"/>
+      <c r="M157" s="51"/>
+      <c r="N157" s="51"/>
+      <c r="O157" s="51"/>
+      <c r="P157" s="51"/>
+      <c r="Q157" s="51"/>
+      <c r="R157" s="51"/>
+      <c r="S157" s="51"/>
+      <c r="T157" s="51"/>
+      <c r="U157" s="51"/>
+      <c r="V157" s="51"/>
+      <c r="W157" s="51"/>
+      <c r="X157" s="51"/>
+      <c r="Y157" s="51"/>
+      <c r="Z157" s="51"/>
+      <c r="AA157" s="51"/>
+      <c r="AB157" s="51"/>
+      <c r="AC157" s="51"/>
     </row>
     <row r="158" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="53"/>
-      <c r="B158" s="55"/>
-      <c r="C158" s="56"/>
-      <c r="D158" s="56"/>
-      <c r="E158" s="56"/>
-      <c r="F158" s="58"/>
-      <c r="G158" s="58"/>
-      <c r="H158" s="58"/>
-      <c r="I158" s="58"/>
-      <c r="J158" s="58"/>
-      <c r="K158" s="58"/>
-      <c r="L158" s="58"/>
-      <c r="M158" s="58"/>
-      <c r="N158" s="58"/>
-      <c r="O158" s="58"/>
-      <c r="P158" s="58"/>
-      <c r="Q158" s="58"/>
-      <c r="R158" s="58"/>
-      <c r="S158" s="58"/>
-      <c r="T158" s="58"/>
-      <c r="U158" s="58"/>
-      <c r="V158" s="58"/>
-      <c r="W158" s="58"/>
-      <c r="X158" s="58"/>
-      <c r="Y158" s="58"/>
-      <c r="Z158" s="58"/>
-      <c r="AA158" s="58"/>
-      <c r="AB158" s="58"/>
-      <c r="AC158" s="58"/>
+      <c r="A158" s="52"/>
+      <c r="B158" s="54"/>
+      <c r="C158" s="55"/>
+      <c r="D158" s="55"/>
+      <c r="E158" s="55"/>
+      <c r="F158" s="57"/>
+      <c r="G158" s="57"/>
+      <c r="H158" s="57"/>
+      <c r="I158" s="57"/>
+      <c r="J158" s="57"/>
+      <c r="K158" s="57"/>
+      <c r="L158" s="57"/>
+      <c r="M158" s="57"/>
+      <c r="N158" s="57"/>
+      <c r="O158" s="57"/>
+      <c r="P158" s="57"/>
+      <c r="Q158" s="57"/>
+      <c r="R158" s="57"/>
+      <c r="S158" s="57"/>
+      <c r="T158" s="57"/>
+      <c r="U158" s="57"/>
+      <c r="V158" s="57"/>
+      <c r="W158" s="57"/>
+      <c r="X158" s="57"/>
+      <c r="Y158" s="57"/>
+      <c r="Z158" s="57"/>
+      <c r="AA158" s="57"/>
+      <c r="AB158" s="57"/>
+      <c r="AC158" s="57"/>
     </row>
     <row r="159" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="53"/>
-      <c r="B159" s="55"/>
-      <c r="C159" s="56"/>
-      <c r="D159" s="56"/>
-      <c r="E159" s="56"/>
-      <c r="F159" s="58"/>
-      <c r="G159" s="58"/>
-      <c r="H159" s="58"/>
-      <c r="I159" s="58"/>
-      <c r="J159" s="58"/>
-      <c r="K159" s="58"/>
-      <c r="L159" s="58"/>
-      <c r="M159" s="58"/>
-      <c r="N159" s="58"/>
-      <c r="O159" s="58"/>
-      <c r="P159" s="58"/>
-      <c r="Q159" s="58"/>
-      <c r="R159" s="58"/>
-      <c r="S159" s="58"/>
-      <c r="T159" s="58"/>
-      <c r="U159" s="58"/>
-      <c r="V159" s="58"/>
-      <c r="W159" s="58"/>
-      <c r="X159" s="58"/>
-      <c r="Y159" s="58"/>
-      <c r="Z159" s="58"/>
-      <c r="AA159" s="58"/>
-      <c r="AB159" s="58"/>
-      <c r="AC159" s="58"/>
+      <c r="A159" s="52"/>
+      <c r="B159" s="54"/>
+      <c r="C159" s="55"/>
+      <c r="D159" s="55"/>
+      <c r="E159" s="55"/>
+      <c r="F159" s="57"/>
+      <c r="G159" s="57"/>
+      <c r="H159" s="57"/>
+      <c r="I159" s="57"/>
+      <c r="J159" s="57"/>
+      <c r="K159" s="57"/>
+      <c r="L159" s="57"/>
+      <c r="M159" s="57"/>
+      <c r="N159" s="57"/>
+      <c r="O159" s="57"/>
+      <c r="P159" s="57"/>
+      <c r="Q159" s="57"/>
+      <c r="R159" s="57"/>
+      <c r="S159" s="57"/>
+      <c r="T159" s="57"/>
+      <c r="U159" s="57"/>
+      <c r="V159" s="57"/>
+      <c r="W159" s="57"/>
+      <c r="X159" s="57"/>
+      <c r="Y159" s="57"/>
+      <c r="Z159" s="57"/>
+      <c r="AA159" s="57"/>
+      <c r="AB159" s="57"/>
+      <c r="AC159" s="57"/>
     </row>
     <row r="160" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="53"/>
-      <c r="B160" s="55"/>
-      <c r="C160" s="56"/>
-      <c r="D160" s="56"/>
-      <c r="E160" s="56"/>
-      <c r="F160" s="58"/>
-      <c r="G160" s="58"/>
-      <c r="H160" s="58"/>
-      <c r="I160" s="58"/>
-      <c r="J160" s="58"/>
-      <c r="K160" s="58"/>
-      <c r="L160" s="58"/>
-      <c r="M160" s="58"/>
-      <c r="N160" s="58"/>
-      <c r="O160" s="58"/>
-      <c r="P160" s="58"/>
-      <c r="Q160" s="58"/>
-      <c r="R160" s="58"/>
-      <c r="S160" s="58"/>
-      <c r="T160" s="58"/>
-      <c r="U160" s="58"/>
-      <c r="V160" s="58"/>
-      <c r="W160" s="58"/>
-      <c r="X160" s="58"/>
-      <c r="Y160" s="58"/>
-      <c r="Z160" s="58"/>
-      <c r="AA160" s="58"/>
-      <c r="AB160" s="58"/>
-      <c r="AC160" s="58"/>
+      <c r="A160" s="52"/>
+      <c r="B160" s="54"/>
+      <c r="C160" s="55"/>
+      <c r="D160" s="55"/>
+      <c r="E160" s="55"/>
+      <c r="F160" s="57"/>
+      <c r="G160" s="57"/>
+      <c r="H160" s="57"/>
+      <c r="I160" s="57"/>
+      <c r="J160" s="57"/>
+      <c r="K160" s="57"/>
+      <c r="L160" s="57"/>
+      <c r="M160" s="57"/>
+      <c r="N160" s="57"/>
+      <c r="O160" s="57"/>
+      <c r="P160" s="57"/>
+      <c r="Q160" s="57"/>
+      <c r="R160" s="57"/>
+      <c r="S160" s="57"/>
+      <c r="T160" s="57"/>
+      <c r="U160" s="57"/>
+      <c r="V160" s="57"/>
+      <c r="W160" s="57"/>
+      <c r="X160" s="57"/>
+      <c r="Y160" s="57"/>
+      <c r="Z160" s="57"/>
+      <c r="AA160" s="57"/>
+      <c r="AB160" s="57"/>
+      <c r="AC160" s="57"/>
     </row>
     <row r="161" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="53"/>
-      <c r="B161" s="55"/>
-      <c r="C161" s="56"/>
-      <c r="D161" s="56"/>
-      <c r="E161" s="56"/>
-      <c r="F161" s="58"/>
-      <c r="G161" s="58"/>
-      <c r="H161" s="58"/>
-      <c r="I161" s="58"/>
-      <c r="J161" s="58"/>
-      <c r="K161" s="58"/>
-      <c r="L161" s="58"/>
-      <c r="M161" s="58"/>
-      <c r="N161" s="58"/>
-      <c r="O161" s="58"/>
-      <c r="P161" s="58"/>
-      <c r="Q161" s="58"/>
-      <c r="R161" s="58"/>
-      <c r="S161" s="58"/>
-      <c r="T161" s="58"/>
-      <c r="U161" s="58"/>
-      <c r="V161" s="58"/>
-      <c r="W161" s="58"/>
-      <c r="X161" s="58"/>
-      <c r="Y161" s="58"/>
-      <c r="Z161" s="58"/>
-      <c r="AA161" s="58"/>
-      <c r="AB161" s="58"/>
-      <c r="AC161" s="58"/>
+      <c r="A161" s="52"/>
+      <c r="B161" s="54"/>
+      <c r="C161" s="55"/>
+      <c r="D161" s="55"/>
+      <c r="E161" s="55"/>
+      <c r="F161" s="57"/>
+      <c r="G161" s="57"/>
+      <c r="H161" s="57"/>
+      <c r="I161" s="57"/>
+      <c r="J161" s="57"/>
+      <c r="K161" s="57"/>
+      <c r="L161" s="57"/>
+      <c r="M161" s="57"/>
+      <c r="N161" s="57"/>
+      <c r="O161" s="57"/>
+      <c r="P161" s="57"/>
+      <c r="Q161" s="57"/>
+      <c r="R161" s="57"/>
+      <c r="S161" s="57"/>
+      <c r="T161" s="57"/>
+      <c r="U161" s="57"/>
+      <c r="V161" s="57"/>
+      <c r="W161" s="57"/>
+      <c r="X161" s="57"/>
+      <c r="Y161" s="57"/>
+      <c r="Z161" s="57"/>
+      <c r="AA161" s="57"/>
+      <c r="AB161" s="57"/>
+      <c r="AC161" s="57"/>
     </row>
     <row r="162" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="53"/>
-      <c r="B162" s="54"/>
-      <c r="C162" s="58"/>
-      <c r="D162" s="58"/>
-      <c r="E162" s="58"/>
-      <c r="F162" s="58"/>
-      <c r="G162" s="58"/>
-      <c r="H162" s="58"/>
-      <c r="I162" s="58"/>
-      <c r="J162" s="58"/>
-      <c r="K162" s="58"/>
-      <c r="L162" s="58"/>
-      <c r="M162" s="58"/>
-      <c r="N162" s="58"/>
-      <c r="O162" s="58"/>
-      <c r="P162" s="58"/>
-      <c r="Q162" s="58"/>
-      <c r="R162" s="58"/>
-      <c r="S162" s="58"/>
-      <c r="T162" s="58"/>
-      <c r="U162" s="58"/>
-      <c r="V162" s="58"/>
-      <c r="W162" s="58"/>
-      <c r="X162" s="58"/>
-      <c r="Y162" s="58"/>
-      <c r="Z162" s="58"/>
-      <c r="AA162" s="58"/>
-      <c r="AB162" s="58"/>
-      <c r="AC162" s="58"/>
+      <c r="A162" s="52"/>
+      <c r="B162" s="53"/>
+      <c r="C162" s="57"/>
+      <c r="D162" s="57"/>
+      <c r="E162" s="57"/>
+      <c r="F162" s="57"/>
+      <c r="G162" s="57"/>
+      <c r="H162" s="57"/>
+      <c r="I162" s="57"/>
+      <c r="J162" s="57"/>
+      <c r="K162" s="57"/>
+      <c r="L162" s="57"/>
+      <c r="M162" s="57"/>
+      <c r="N162" s="57"/>
+      <c r="O162" s="57"/>
+      <c r="P162" s="57"/>
+      <c r="Q162" s="57"/>
+      <c r="R162" s="57"/>
+      <c r="S162" s="57"/>
+      <c r="T162" s="57"/>
+      <c r="U162" s="57"/>
+      <c r="V162" s="57"/>
+      <c r="W162" s="57"/>
+      <c r="X162" s="57"/>
+      <c r="Y162" s="57"/>
+      <c r="Z162" s="57"/>
+      <c r="AA162" s="57"/>
+      <c r="AB162" s="57"/>
+      <c r="AC162" s="57"/>
     </row>
     <row r="163" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="53"/>
-      <c r="B163" s="54"/>
-      <c r="C163" s="54"/>
-      <c r="D163" s="54"/>
-      <c r="E163" s="54"/>
-      <c r="F163" s="52"/>
-      <c r="G163" s="52"/>
-      <c r="H163" s="52"/>
-      <c r="I163" s="52"/>
-      <c r="J163" s="52"/>
-      <c r="K163" s="52"/>
-      <c r="L163" s="52"/>
-      <c r="M163" s="52"/>
-      <c r="N163" s="52"/>
-      <c r="O163" s="52"/>
-      <c r="P163" s="52"/>
-      <c r="Q163" s="52"/>
-      <c r="R163" s="52"/>
-      <c r="S163" s="52"/>
-      <c r="T163" s="52"/>
-      <c r="U163" s="52"/>
-      <c r="V163" s="52"/>
-      <c r="W163" s="52"/>
-      <c r="X163" s="52"/>
-      <c r="Y163" s="52"/>
-      <c r="Z163" s="52"/>
-      <c r="AA163" s="52"/>
-      <c r="AB163" s="52"/>
-      <c r="AC163" s="52"/>
+      <c r="A163" s="52"/>
+      <c r="B163" s="53"/>
+      <c r="C163" s="53"/>
+      <c r="D163" s="53"/>
+      <c r="E163" s="53"/>
+      <c r="F163" s="51"/>
+      <c r="G163" s="51"/>
+      <c r="H163" s="51"/>
+      <c r="I163" s="51"/>
+      <c r="J163" s="51"/>
+      <c r="K163" s="51"/>
+      <c r="L163" s="51"/>
+      <c r="M163" s="51"/>
+      <c r="N163" s="51"/>
+      <c r="O163" s="51"/>
+      <c r="P163" s="51"/>
+      <c r="Q163" s="51"/>
+      <c r="R163" s="51"/>
+      <c r="S163" s="51"/>
+      <c r="T163" s="51"/>
+      <c r="U163" s="51"/>
+      <c r="V163" s="51"/>
+      <c r="W163" s="51"/>
+      <c r="X163" s="51"/>
+      <c r="Y163" s="51"/>
+      <c r="Z163" s="51"/>
+      <c r="AA163" s="51"/>
+      <c r="AB163" s="51"/>
+      <c r="AC163" s="51"/>
     </row>
     <row r="164" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="53"/>
-      <c r="B164" s="54"/>
-      <c r="C164" s="55"/>
-      <c r="D164" s="55"/>
-      <c r="E164" s="55"/>
-      <c r="F164" s="52"/>
-      <c r="G164" s="52"/>
-      <c r="H164" s="52"/>
-      <c r="I164" s="52"/>
-      <c r="J164" s="52"/>
-      <c r="K164" s="52"/>
-      <c r="L164" s="52"/>
-      <c r="M164" s="52"/>
-      <c r="N164" s="52"/>
-      <c r="O164" s="52"/>
-      <c r="P164" s="52"/>
-      <c r="Q164" s="52"/>
-      <c r="R164" s="52"/>
-      <c r="S164" s="52"/>
-      <c r="T164" s="52"/>
-      <c r="U164" s="52"/>
-      <c r="V164" s="52"/>
-      <c r="W164" s="52"/>
-      <c r="X164" s="52"/>
-      <c r="Y164" s="52"/>
-      <c r="Z164" s="52"/>
-      <c r="AA164" s="52"/>
-      <c r="AB164" s="52"/>
-      <c r="AC164" s="52"/>
+      <c r="A164" s="52"/>
+      <c r="B164" s="53"/>
+      <c r="C164" s="54"/>
+      <c r="D164" s="54"/>
+      <c r="E164" s="54"/>
+      <c r="F164" s="51"/>
+      <c r="G164" s="51"/>
+      <c r="H164" s="51"/>
+      <c r="I164" s="51"/>
+      <c r="J164" s="51"/>
+      <c r="K164" s="51"/>
+      <c r="L164" s="51"/>
+      <c r="M164" s="51"/>
+      <c r="N164" s="51"/>
+      <c r="O164" s="51"/>
+      <c r="P164" s="51"/>
+      <c r="Q164" s="51"/>
+      <c r="R164" s="51"/>
+      <c r="S164" s="51"/>
+      <c r="T164" s="51"/>
+      <c r="U164" s="51"/>
+      <c r="V164" s="51"/>
+      <c r="W164" s="51"/>
+      <c r="X164" s="51"/>
+      <c r="Y164" s="51"/>
+      <c r="Z164" s="51"/>
+      <c r="AA164" s="51"/>
+      <c r="AB164" s="51"/>
+      <c r="AC164" s="51"/>
     </row>
     <row r="165" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="53"/>
-      <c r="B165" s="55"/>
-      <c r="C165" s="56"/>
-      <c r="D165" s="57"/>
-      <c r="E165" s="57"/>
-      <c r="F165" s="52"/>
-      <c r="G165" s="52"/>
-      <c r="H165" s="52"/>
-      <c r="I165" s="52"/>
-      <c r="J165" s="52"/>
-      <c r="K165" s="52"/>
-      <c r="L165" s="52"/>
-      <c r="M165" s="52"/>
-      <c r="N165" s="52"/>
-      <c r="O165" s="52"/>
-      <c r="P165" s="52"/>
-      <c r="Q165" s="52"/>
-      <c r="R165" s="52"/>
-      <c r="S165" s="52"/>
-      <c r="T165" s="52"/>
-      <c r="U165" s="52"/>
-      <c r="V165" s="52"/>
-      <c r="W165" s="52"/>
-      <c r="X165" s="52"/>
-      <c r="Y165" s="52"/>
-      <c r="Z165" s="52"/>
-      <c r="AA165" s="52"/>
-      <c r="AB165" s="52"/>
-      <c r="AC165" s="52"/>
+      <c r="A165" s="52"/>
+      <c r="B165" s="54"/>
+      <c r="C165" s="55"/>
+      <c r="D165" s="56"/>
+      <c r="E165" s="56"/>
+      <c r="F165" s="51"/>
+      <c r="G165" s="51"/>
+      <c r="H165" s="51"/>
+      <c r="I165" s="51"/>
+      <c r="J165" s="51"/>
+      <c r="K165" s="51"/>
+      <c r="L165" s="51"/>
+      <c r="M165" s="51"/>
+      <c r="N165" s="51"/>
+      <c r="O165" s="51"/>
+      <c r="P165" s="51"/>
+      <c r="Q165" s="51"/>
+      <c r="R165" s="51"/>
+      <c r="S165" s="51"/>
+      <c r="T165" s="51"/>
+      <c r="U165" s="51"/>
+      <c r="V165" s="51"/>
+      <c r="W165" s="51"/>
+      <c r="X165" s="51"/>
+      <c r="Y165" s="51"/>
+      <c r="Z165" s="51"/>
+      <c r="AA165" s="51"/>
+      <c r="AB165" s="51"/>
+      <c r="AC165" s="51"/>
     </row>
     <row r="166" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="53"/>
-      <c r="B166" s="55"/>
-      <c r="C166" s="56"/>
-      <c r="D166" s="57"/>
-      <c r="E166" s="57"/>
-      <c r="F166" s="52"/>
-      <c r="G166" s="52"/>
-      <c r="H166" s="52"/>
-      <c r="I166" s="52"/>
-      <c r="J166" s="52"/>
-      <c r="K166" s="52"/>
-      <c r="L166" s="52"/>
-      <c r="M166" s="52"/>
-      <c r="N166" s="52"/>
-      <c r="O166" s="52"/>
-      <c r="P166" s="52"/>
-      <c r="Q166" s="52"/>
-      <c r="R166" s="52"/>
-      <c r="S166" s="52"/>
-      <c r="T166" s="52"/>
-      <c r="U166" s="52"/>
-      <c r="V166" s="52"/>
-      <c r="W166" s="52"/>
-      <c r="X166" s="52"/>
-      <c r="Y166" s="52"/>
-      <c r="Z166" s="52"/>
-      <c r="AA166" s="52"/>
-      <c r="AB166" s="52"/>
-      <c r="AC166" s="52"/>
+      <c r="A166" s="52"/>
+      <c r="B166" s="54"/>
+      <c r="C166" s="55"/>
+      <c r="D166" s="56"/>
+      <c r="E166" s="56"/>
+      <c r="F166" s="51"/>
+      <c r="G166" s="51"/>
+      <c r="H166" s="51"/>
+      <c r="I166" s="51"/>
+      <c r="J166" s="51"/>
+      <c r="K166" s="51"/>
+      <c r="L166" s="51"/>
+      <c r="M166" s="51"/>
+      <c r="N166" s="51"/>
+      <c r="O166" s="51"/>
+      <c r="P166" s="51"/>
+      <c r="Q166" s="51"/>
+      <c r="R166" s="51"/>
+      <c r="S166" s="51"/>
+      <c r="T166" s="51"/>
+      <c r="U166" s="51"/>
+      <c r="V166" s="51"/>
+      <c r="W166" s="51"/>
+      <c r="X166" s="51"/>
+      <c r="Y166" s="51"/>
+      <c r="Z166" s="51"/>
+      <c r="AA166" s="51"/>
+      <c r="AB166" s="51"/>
+      <c r="AC166" s="51"/>
     </row>
     <row r="167" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="53"/>
-      <c r="B167" s="55"/>
-      <c r="C167" s="56"/>
-      <c r="D167" s="57"/>
-      <c r="E167" s="57"/>
-      <c r="F167" s="52"/>
-      <c r="G167" s="52"/>
-      <c r="H167" s="52"/>
-      <c r="I167" s="52"/>
-      <c r="J167" s="52"/>
-      <c r="K167" s="52"/>
-      <c r="L167" s="52"/>
-      <c r="M167" s="52"/>
-      <c r="N167" s="52"/>
-      <c r="O167" s="52"/>
-      <c r="P167" s="52"/>
-      <c r="Q167" s="52"/>
-      <c r="R167" s="52"/>
-      <c r="S167" s="52"/>
-      <c r="T167" s="52"/>
-      <c r="U167" s="52"/>
-      <c r="V167" s="52"/>
-      <c r="W167" s="52"/>
-      <c r="X167" s="52"/>
-      <c r="Y167" s="52"/>
-      <c r="Z167" s="52"/>
-      <c r="AA167" s="52"/>
-      <c r="AB167" s="52"/>
-      <c r="AC167" s="52"/>
+      <c r="A167" s="52"/>
+      <c r="B167" s="54"/>
+      <c r="C167" s="55"/>
+      <c r="D167" s="56"/>
+      <c r="E167" s="56"/>
+      <c r="F167" s="51"/>
+      <c r="G167" s="51"/>
+      <c r="H167" s="51"/>
+      <c r="I167" s="51"/>
+      <c r="J167" s="51"/>
+      <c r="K167" s="51"/>
+      <c r="L167" s="51"/>
+      <c r="M167" s="51"/>
+      <c r="N167" s="51"/>
+      <c r="O167" s="51"/>
+      <c r="P167" s="51"/>
+      <c r="Q167" s="51"/>
+      <c r="R167" s="51"/>
+      <c r="S167" s="51"/>
+      <c r="T167" s="51"/>
+      <c r="U167" s="51"/>
+      <c r="V167" s="51"/>
+      <c r="W167" s="51"/>
+      <c r="X167" s="51"/>
+      <c r="Y167" s="51"/>
+      <c r="Z167" s="51"/>
+      <c r="AA167" s="51"/>
+      <c r="AB167" s="51"/>
+      <c r="AC167" s="51"/>
     </row>
     <row r="168" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="53"/>
-      <c r="B168" s="55"/>
-      <c r="C168" s="56"/>
-      <c r="D168" s="57"/>
-      <c r="E168" s="57"/>
-      <c r="F168" s="52"/>
-      <c r="G168" s="52"/>
-      <c r="H168" s="52"/>
-      <c r="I168" s="52"/>
-      <c r="J168" s="52"/>
-      <c r="K168" s="52"/>
-      <c r="L168" s="52"/>
-      <c r="M168" s="52"/>
-      <c r="N168" s="52"/>
-      <c r="O168" s="52"/>
-      <c r="P168" s="52"/>
-      <c r="Q168" s="52"/>
-      <c r="R168" s="52"/>
-      <c r="S168" s="52"/>
-      <c r="T168" s="52"/>
-      <c r="U168" s="52"/>
-      <c r="V168" s="52"/>
-      <c r="W168" s="52"/>
-      <c r="X168" s="52"/>
-      <c r="Y168" s="52"/>
-      <c r="Z168" s="52"/>
-      <c r="AA168" s="52"/>
-      <c r="AB168" s="52"/>
-      <c r="AC168" s="52"/>
+      <c r="A168" s="52"/>
+      <c r="B168" s="54"/>
+      <c r="C168" s="55"/>
+      <c r="D168" s="56"/>
+      <c r="E168" s="56"/>
+      <c r="F168" s="51"/>
+      <c r="G168" s="51"/>
+      <c r="H168" s="51"/>
+      <c r="I168" s="51"/>
+      <c r="J168" s="51"/>
+      <c r="K168" s="51"/>
+      <c r="L168" s="51"/>
+      <c r="M168" s="51"/>
+      <c r="N168" s="51"/>
+      <c r="O168" s="51"/>
+      <c r="P168" s="51"/>
+      <c r="Q168" s="51"/>
+      <c r="R168" s="51"/>
+      <c r="S168" s="51"/>
+      <c r="T168" s="51"/>
+      <c r="U168" s="51"/>
+      <c r="V168" s="51"/>
+      <c r="W168" s="51"/>
+      <c r="X168" s="51"/>
+      <c r="Y168" s="51"/>
+      <c r="Z168" s="51"/>
+      <c r="AA168" s="51"/>
+      <c r="AB168" s="51"/>
+      <c r="AC168" s="51"/>
     </row>
     <row r="169" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="53"/>
-      <c r="B169" s="55"/>
-      <c r="C169" s="56"/>
-      <c r="D169" s="57"/>
-      <c r="E169" s="57"/>
-      <c r="F169" s="52"/>
-      <c r="G169" s="52"/>
-      <c r="H169" s="52"/>
-      <c r="I169" s="52"/>
-      <c r="J169" s="52"/>
-      <c r="K169" s="52"/>
-      <c r="L169" s="52"/>
-      <c r="M169" s="52"/>
-      <c r="N169" s="52"/>
-      <c r="O169" s="52"/>
-      <c r="P169" s="52"/>
-      <c r="Q169" s="52"/>
-      <c r="R169" s="52"/>
-      <c r="S169" s="52"/>
-      <c r="T169" s="52"/>
-      <c r="U169" s="52"/>
-      <c r="V169" s="52"/>
-      <c r="W169" s="52"/>
-      <c r="X169" s="52"/>
-      <c r="Y169" s="52"/>
-      <c r="Z169" s="52"/>
-      <c r="AA169" s="52"/>
-      <c r="AB169" s="52"/>
-      <c r="AC169" s="52"/>
+      <c r="A169" s="52"/>
+      <c r="B169" s="54"/>
+      <c r="C169" s="55"/>
+      <c r="D169" s="56"/>
+      <c r="E169" s="56"/>
+      <c r="F169" s="51"/>
+      <c r="G169" s="51"/>
+      <c r="H169" s="51"/>
+      <c r="I169" s="51"/>
+      <c r="J169" s="51"/>
+      <c r="K169" s="51"/>
+      <c r="L169" s="51"/>
+      <c r="M169" s="51"/>
+      <c r="N169" s="51"/>
+      <c r="O169" s="51"/>
+      <c r="P169" s="51"/>
+      <c r="Q169" s="51"/>
+      <c r="R169" s="51"/>
+      <c r="S169" s="51"/>
+      <c r="T169" s="51"/>
+      <c r="U169" s="51"/>
+      <c r="V169" s="51"/>
+      <c r="W169" s="51"/>
+      <c r="X169" s="51"/>
+      <c r="Y169" s="51"/>
+      <c r="Z169" s="51"/>
+      <c r="AA169" s="51"/>
+      <c r="AB169" s="51"/>
+      <c r="AC169" s="51"/>
     </row>
     <row r="170" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="53"/>
-      <c r="B170" s="54"/>
-      <c r="C170" s="54"/>
-      <c r="D170" s="54"/>
-      <c r="E170" s="54"/>
-      <c r="F170" s="52"/>
-      <c r="G170" s="52"/>
-      <c r="H170" s="52"/>
-      <c r="I170" s="52"/>
-      <c r="J170" s="52"/>
-      <c r="K170" s="52"/>
-      <c r="L170" s="52"/>
-      <c r="M170" s="52"/>
-      <c r="N170" s="52"/>
-      <c r="O170" s="52"/>
-      <c r="P170" s="52"/>
-      <c r="Q170" s="52"/>
-      <c r="R170" s="52"/>
-      <c r="S170" s="52"/>
-      <c r="T170" s="52"/>
-      <c r="U170" s="52"/>
-      <c r="V170" s="52"/>
-      <c r="W170" s="52"/>
-      <c r="X170" s="52"/>
-      <c r="Y170" s="52"/>
-      <c r="Z170" s="52"/>
-      <c r="AA170" s="52"/>
-      <c r="AB170" s="52"/>
-      <c r="AC170" s="52"/>
+      <c r="A170" s="52"/>
+      <c r="B170" s="53"/>
+      <c r="C170" s="53"/>
+      <c r="D170" s="53"/>
+      <c r="E170" s="53"/>
+      <c r="F170" s="51"/>
+      <c r="G170" s="51"/>
+      <c r="H170" s="51"/>
+      <c r="I170" s="51"/>
+      <c r="J170" s="51"/>
+      <c r="K170" s="51"/>
+      <c r="L170" s="51"/>
+      <c r="M170" s="51"/>
+      <c r="N170" s="51"/>
+      <c r="O170" s="51"/>
+      <c r="P170" s="51"/>
+      <c r="Q170" s="51"/>
+      <c r="R170" s="51"/>
+      <c r="S170" s="51"/>
+      <c r="T170" s="51"/>
+      <c r="U170" s="51"/>
+      <c r="V170" s="51"/>
+      <c r="W170" s="51"/>
+      <c r="X170" s="51"/>
+      <c r="Y170" s="51"/>
+      <c r="Z170" s="51"/>
+      <c r="AA170" s="51"/>
+      <c r="AB170" s="51"/>
+      <c r="AC170" s="51"/>
     </row>
     <row r="171" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="53"/>
-      <c r="B171" s="54"/>
-      <c r="C171" s="55"/>
-      <c r="D171" s="55"/>
-      <c r="E171" s="55"/>
-      <c r="F171" s="52"/>
-      <c r="G171" s="52"/>
-      <c r="H171" s="52"/>
-      <c r="I171" s="52"/>
-      <c r="J171" s="52"/>
-      <c r="K171" s="52"/>
-      <c r="L171" s="52"/>
-      <c r="M171" s="52"/>
-      <c r="N171" s="52"/>
-      <c r="O171" s="52"/>
-      <c r="P171" s="52"/>
-      <c r="Q171" s="52"/>
-      <c r="R171" s="52"/>
-      <c r="S171" s="52"/>
-      <c r="T171" s="52"/>
-      <c r="U171" s="52"/>
-      <c r="V171" s="52"/>
-      <c r="W171" s="52"/>
-      <c r="X171" s="52"/>
-      <c r="Y171" s="52"/>
-      <c r="Z171" s="52"/>
-      <c r="AA171" s="52"/>
-      <c r="AB171" s="52"/>
-      <c r="AC171" s="52"/>
+      <c r="A171" s="52"/>
+      <c r="B171" s="53"/>
+      <c r="C171" s="54"/>
+      <c r="D171" s="54"/>
+      <c r="E171" s="54"/>
+      <c r="F171" s="51"/>
+      <c r="G171" s="51"/>
+      <c r="H171" s="51"/>
+      <c r="I171" s="51"/>
+      <c r="J171" s="51"/>
+      <c r="K171" s="51"/>
+      <c r="L171" s="51"/>
+      <c r="M171" s="51"/>
+      <c r="N171" s="51"/>
+      <c r="O171" s="51"/>
+      <c r="P171" s="51"/>
+      <c r="Q171" s="51"/>
+      <c r="R171" s="51"/>
+      <c r="S171" s="51"/>
+      <c r="T171" s="51"/>
+      <c r="U171" s="51"/>
+      <c r="V171" s="51"/>
+      <c r="W171" s="51"/>
+      <c r="X171" s="51"/>
+      <c r="Y171" s="51"/>
+      <c r="Z171" s="51"/>
+      <c r="AA171" s="51"/>
+      <c r="AB171" s="51"/>
+      <c r="AC171" s="51"/>
     </row>
     <row r="172" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="53"/>
-      <c r="B172" s="54"/>
-      <c r="C172" s="56"/>
-      <c r="D172" s="56"/>
-      <c r="E172" s="56"/>
-      <c r="F172" s="52"/>
-      <c r="G172" s="52"/>
-      <c r="H172" s="52"/>
-      <c r="I172" s="52"/>
-      <c r="J172" s="52"/>
-      <c r="K172" s="52"/>
-      <c r="L172" s="52"/>
-      <c r="M172" s="52"/>
-      <c r="N172" s="52"/>
-      <c r="O172" s="52"/>
-      <c r="P172" s="52"/>
-      <c r="Q172" s="52"/>
-      <c r="R172" s="52"/>
-      <c r="S172" s="52"/>
-      <c r="T172" s="52"/>
-      <c r="U172" s="52"/>
-      <c r="V172" s="52"/>
-      <c r="W172" s="52"/>
-      <c r="X172" s="52"/>
-      <c r="Y172" s="52"/>
-      <c r="Z172" s="52"/>
-      <c r="AA172" s="52"/>
-      <c r="AB172" s="52"/>
-      <c r="AC172" s="52"/>
+      <c r="A172" s="52"/>
+      <c r="B172" s="53"/>
+      <c r="C172" s="55"/>
+      <c r="D172" s="55"/>
+      <c r="E172" s="55"/>
+      <c r="F172" s="51"/>
+      <c r="G172" s="51"/>
+      <c r="H172" s="51"/>
+      <c r="I172" s="51"/>
+      <c r="J172" s="51"/>
+      <c r="K172" s="51"/>
+      <c r="L172" s="51"/>
+      <c r="M172" s="51"/>
+      <c r="N172" s="51"/>
+      <c r="O172" s="51"/>
+      <c r="P172" s="51"/>
+      <c r="Q172" s="51"/>
+      <c r="R172" s="51"/>
+      <c r="S172" s="51"/>
+      <c r="T172" s="51"/>
+      <c r="U172" s="51"/>
+      <c r="V172" s="51"/>
+      <c r="W172" s="51"/>
+      <c r="X172" s="51"/>
+      <c r="Y172" s="51"/>
+      <c r="Z172" s="51"/>
+      <c r="AA172" s="51"/>
+      <c r="AB172" s="51"/>
+      <c r="AC172" s="51"/>
     </row>
     <row r="173" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="53"/>
-      <c r="B173" s="54"/>
-      <c r="C173" s="56"/>
-      <c r="D173" s="56"/>
-      <c r="E173" s="56"/>
-      <c r="F173" s="52"/>
-      <c r="G173" s="52"/>
-      <c r="H173" s="52"/>
-      <c r="I173" s="52"/>
-      <c r="J173" s="52"/>
-      <c r="K173" s="52"/>
-      <c r="L173" s="52"/>
-      <c r="M173" s="52"/>
-      <c r="N173" s="52"/>
-      <c r="O173" s="52"/>
-      <c r="P173" s="52"/>
-      <c r="Q173" s="52"/>
-      <c r="R173" s="52"/>
-      <c r="S173" s="52"/>
-      <c r="T173" s="52"/>
-      <c r="U173" s="52"/>
-      <c r="V173" s="52"/>
-      <c r="W173" s="52"/>
-      <c r="X173" s="52"/>
-      <c r="Y173" s="52"/>
-      <c r="Z173" s="52"/>
-      <c r="AA173" s="52"/>
-      <c r="AB173" s="52"/>
-      <c r="AC173" s="52"/>
+      <c r="A173" s="52"/>
+      <c r="B173" s="53"/>
+      <c r="C173" s="55"/>
+      <c r="D173" s="55"/>
+      <c r="E173" s="55"/>
+      <c r="F173" s="51"/>
+      <c r="G173" s="51"/>
+      <c r="H173" s="51"/>
+      <c r="I173" s="51"/>
+      <c r="J173" s="51"/>
+      <c r="K173" s="51"/>
+      <c r="L173" s="51"/>
+      <c r="M173" s="51"/>
+      <c r="N173" s="51"/>
+      <c r="O173" s="51"/>
+      <c r="P173" s="51"/>
+      <c r="Q173" s="51"/>
+      <c r="R173" s="51"/>
+      <c r="S173" s="51"/>
+      <c r="T173" s="51"/>
+      <c r="U173" s="51"/>
+      <c r="V173" s="51"/>
+      <c r="W173" s="51"/>
+      <c r="X173" s="51"/>
+      <c r="Y173" s="51"/>
+      <c r="Z173" s="51"/>
+      <c r="AA173" s="51"/>
+      <c r="AB173" s="51"/>
+      <c r="AC173" s="51"/>
     </row>
     <row r="174" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="53"/>
-      <c r="B174" s="54"/>
-      <c r="C174" s="56"/>
-      <c r="D174" s="56"/>
-      <c r="E174" s="56"/>
-      <c r="F174" s="58"/>
-      <c r="G174" s="58"/>
-      <c r="H174" s="58"/>
-      <c r="I174" s="58"/>
-      <c r="J174" s="58"/>
-      <c r="K174" s="58"/>
-      <c r="L174" s="58"/>
-      <c r="M174" s="58"/>
-      <c r="N174" s="58"/>
-      <c r="O174" s="52"/>
-      <c r="P174" s="52"/>
-      <c r="Q174" s="52"/>
-      <c r="R174" s="52"/>
-      <c r="S174" s="52"/>
-      <c r="T174" s="52"/>
-      <c r="U174" s="52"/>
-      <c r="V174" s="52"/>
-      <c r="W174" s="52"/>
-      <c r="X174" s="52"/>
-      <c r="Y174" s="52"/>
-      <c r="Z174" s="52"/>
-      <c r="AA174" s="52"/>
-      <c r="AB174" s="52"/>
-      <c r="AC174" s="52"/>
+      <c r="A174" s="52"/>
+      <c r="B174" s="53"/>
+      <c r="C174" s="55"/>
+      <c r="D174" s="55"/>
+      <c r="E174" s="55"/>
+      <c r="F174" s="57"/>
+      <c r="G174" s="57"/>
+      <c r="H174" s="57"/>
+      <c r="I174" s="57"/>
+      <c r="J174" s="57"/>
+      <c r="K174" s="57"/>
+      <c r="L174" s="57"/>
+      <c r="M174" s="57"/>
+      <c r="N174" s="57"/>
+      <c r="O174" s="51"/>
+      <c r="P174" s="51"/>
+      <c r="Q174" s="51"/>
+      <c r="R174" s="51"/>
+      <c r="S174" s="51"/>
+      <c r="T174" s="51"/>
+      <c r="U174" s="51"/>
+      <c r="V174" s="51"/>
+      <c r="W174" s="51"/>
+      <c r="X174" s="51"/>
+      <c r="Y174" s="51"/>
+      <c r="Z174" s="51"/>
+      <c r="AA174" s="51"/>
+      <c r="AB174" s="51"/>
+      <c r="AC174" s="51"/>
     </row>
     <row r="175" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="53"/>
-      <c r="B175" s="54"/>
-      <c r="C175" s="56"/>
-      <c r="D175" s="56"/>
-      <c r="E175" s="56"/>
-      <c r="F175" s="58"/>
-      <c r="G175" s="58"/>
-      <c r="H175" s="58"/>
-      <c r="I175" s="58"/>
-      <c r="J175" s="58"/>
-      <c r="K175" s="58"/>
-      <c r="L175" s="58"/>
-      <c r="M175" s="58"/>
-      <c r="N175" s="58"/>
-      <c r="O175" s="52"/>
-      <c r="P175" s="52"/>
-      <c r="Q175" s="52"/>
-      <c r="R175" s="52"/>
-      <c r="S175" s="52"/>
-      <c r="T175" s="52"/>
-      <c r="U175" s="52"/>
-      <c r="V175" s="52"/>
-      <c r="W175" s="52"/>
-      <c r="X175" s="52"/>
-      <c r="Y175" s="52"/>
-      <c r="Z175" s="52"/>
-      <c r="AA175" s="52"/>
-      <c r="AB175" s="52"/>
-      <c r="AC175" s="52"/>
+      <c r="A175" s="52"/>
+      <c r="B175" s="53"/>
+      <c r="C175" s="55"/>
+      <c r="D175" s="55"/>
+      <c r="E175" s="55"/>
+      <c r="F175" s="57"/>
+      <c r="G175" s="57"/>
+      <c r="H175" s="57"/>
+      <c r="I175" s="57"/>
+      <c r="J175" s="57"/>
+      <c r="K175" s="57"/>
+      <c r="L175" s="57"/>
+      <c r="M175" s="57"/>
+      <c r="N175" s="57"/>
+      <c r="O175" s="51"/>
+      <c r="P175" s="51"/>
+      <c r="Q175" s="51"/>
+      <c r="R175" s="51"/>
+      <c r="S175" s="51"/>
+      <c r="T175" s="51"/>
+      <c r="U175" s="51"/>
+      <c r="V175" s="51"/>
+      <c r="W175" s="51"/>
+      <c r="X175" s="51"/>
+      <c r="Y175" s="51"/>
+      <c r="Z175" s="51"/>
+      <c r="AA175" s="51"/>
+      <c r="AB175" s="51"/>
+      <c r="AC175" s="51"/>
     </row>
     <row r="176" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="53"/>
-      <c r="B176" s="54"/>
-      <c r="C176" s="56"/>
-      <c r="D176" s="56"/>
-      <c r="E176" s="56"/>
-      <c r="F176" s="58"/>
-      <c r="G176" s="58"/>
-      <c r="H176" s="58"/>
-      <c r="I176" s="58"/>
-      <c r="J176" s="58"/>
-      <c r="K176" s="58"/>
-      <c r="L176" s="58"/>
-      <c r="M176" s="58"/>
-      <c r="N176" s="58"/>
-      <c r="O176" s="52"/>
-      <c r="P176" s="52"/>
-      <c r="Q176" s="52"/>
-      <c r="R176" s="52"/>
-      <c r="S176" s="52"/>
-      <c r="T176" s="52"/>
-      <c r="U176" s="52"/>
-      <c r="V176" s="52"/>
-      <c r="W176" s="52"/>
-      <c r="X176" s="52"/>
-      <c r="Y176" s="52"/>
-      <c r="Z176" s="52"/>
-      <c r="AA176" s="52"/>
-      <c r="AB176" s="52"/>
-      <c r="AC176" s="52"/>
+      <c r="A176" s="52"/>
+      <c r="B176" s="53"/>
+      <c r="C176" s="55"/>
+      <c r="D176" s="55"/>
+      <c r="E176" s="55"/>
+      <c r="F176" s="57"/>
+      <c r="G176" s="57"/>
+      <c r="H176" s="57"/>
+      <c r="I176" s="57"/>
+      <c r="J176" s="57"/>
+      <c r="K176" s="57"/>
+      <c r="L176" s="57"/>
+      <c r="M176" s="57"/>
+      <c r="N176" s="57"/>
+      <c r="O176" s="51"/>
+      <c r="P176" s="51"/>
+      <c r="Q176" s="51"/>
+      <c r="R176" s="51"/>
+      <c r="S176" s="51"/>
+      <c r="T176" s="51"/>
+      <c r="U176" s="51"/>
+      <c r="V176" s="51"/>
+      <c r="W176" s="51"/>
+      <c r="X176" s="51"/>
+      <c r="Y176" s="51"/>
+      <c r="Z176" s="51"/>
+      <c r="AA176" s="51"/>
+      <c r="AB176" s="51"/>
+      <c r="AC176" s="51"/>
     </row>
     <row r="177" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="53"/>
-      <c r="B177" s="54"/>
-      <c r="C177" s="54"/>
-      <c r="D177" s="54"/>
-      <c r="E177" s="54"/>
-      <c r="F177" s="58"/>
-      <c r="G177" s="58"/>
-      <c r="H177" s="58"/>
-      <c r="I177" s="58"/>
-      <c r="J177" s="58"/>
-      <c r="K177" s="58"/>
-      <c r="L177" s="58"/>
-      <c r="M177" s="58"/>
-      <c r="N177" s="58"/>
-      <c r="O177" s="52"/>
-      <c r="P177" s="52"/>
-      <c r="Q177" s="52"/>
-      <c r="R177" s="52"/>
-      <c r="S177" s="52"/>
-      <c r="T177" s="52"/>
-      <c r="U177" s="52"/>
-      <c r="V177" s="52"/>
-      <c r="W177" s="52"/>
-      <c r="X177" s="52"/>
-      <c r="Y177" s="52"/>
-      <c r="Z177" s="52"/>
-      <c r="AA177" s="52"/>
-      <c r="AB177" s="52"/>
-      <c r="AC177" s="52"/>
+      <c r="A177" s="52"/>
+      <c r="B177" s="53"/>
+      <c r="C177" s="53"/>
+      <c r="D177" s="53"/>
+      <c r="E177" s="53"/>
+      <c r="F177" s="57"/>
+      <c r="G177" s="57"/>
+      <c r="H177" s="57"/>
+      <c r="I177" s="57"/>
+      <c r="J177" s="57"/>
+      <c r="K177" s="57"/>
+      <c r="L177" s="57"/>
+      <c r="M177" s="57"/>
+      <c r="N177" s="57"/>
+      <c r="O177" s="51"/>
+      <c r="P177" s="51"/>
+      <c r="Q177" s="51"/>
+      <c r="R177" s="51"/>
+      <c r="S177" s="51"/>
+      <c r="T177" s="51"/>
+      <c r="U177" s="51"/>
+      <c r="V177" s="51"/>
+      <c r="W177" s="51"/>
+      <c r="X177" s="51"/>
+      <c r="Y177" s="51"/>
+      <c r="Z177" s="51"/>
+      <c r="AA177" s="51"/>
+      <c r="AB177" s="51"/>
+      <c r="AC177" s="51"/>
     </row>
     <row r="178" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="53"/>
-      <c r="B178" s="54"/>
-      <c r="C178" s="55"/>
-      <c r="D178" s="55"/>
-      <c r="E178" s="55"/>
-      <c r="F178" s="58"/>
-      <c r="G178" s="58"/>
-      <c r="H178" s="58"/>
-      <c r="I178" s="58"/>
-      <c r="J178" s="58"/>
-      <c r="K178" s="58"/>
-      <c r="L178" s="58"/>
-      <c r="M178" s="58"/>
-      <c r="N178" s="58"/>
-      <c r="O178" s="52"/>
-      <c r="P178" s="52"/>
-      <c r="Q178" s="52"/>
-      <c r="R178" s="52"/>
-      <c r="S178" s="52"/>
-      <c r="T178" s="52"/>
-      <c r="U178" s="52"/>
-      <c r="V178" s="52"/>
-      <c r="W178" s="52"/>
-      <c r="X178" s="52"/>
-      <c r="Y178" s="52"/>
-      <c r="Z178" s="52"/>
-      <c r="AA178" s="52"/>
-      <c r="AB178" s="52"/>
-      <c r="AC178" s="52"/>
+      <c r="A178" s="52"/>
+      <c r="B178" s="53"/>
+      <c r="C178" s="54"/>
+      <c r="D178" s="54"/>
+      <c r="E178" s="54"/>
+      <c r="F178" s="57"/>
+      <c r="G178" s="57"/>
+      <c r="H178" s="57"/>
+      <c r="I178" s="57"/>
+      <c r="J178" s="57"/>
+      <c r="K178" s="57"/>
+      <c r="L178" s="57"/>
+      <c r="M178" s="57"/>
+      <c r="N178" s="57"/>
+      <c r="O178" s="51"/>
+      <c r="P178" s="51"/>
+      <c r="Q178" s="51"/>
+      <c r="R178" s="51"/>
+      <c r="S178" s="51"/>
+      <c r="T178" s="51"/>
+      <c r="U178" s="51"/>
+      <c r="V178" s="51"/>
+      <c r="W178" s="51"/>
+      <c r="X178" s="51"/>
+      <c r="Y178" s="51"/>
+      <c r="Z178" s="51"/>
+      <c r="AA178" s="51"/>
+      <c r="AB178" s="51"/>
+      <c r="AC178" s="51"/>
     </row>
     <row r="179" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="53"/>
-      <c r="B179" s="54"/>
-      <c r="C179" s="56"/>
-      <c r="D179" s="56"/>
-      <c r="E179" s="56"/>
-      <c r="F179" s="58"/>
-      <c r="G179" s="58"/>
-      <c r="H179" s="58"/>
-      <c r="I179" s="58"/>
-      <c r="J179" s="58"/>
-      <c r="K179" s="58"/>
-      <c r="L179" s="58"/>
-      <c r="M179" s="58"/>
-      <c r="N179" s="58"/>
-      <c r="O179" s="52"/>
-      <c r="P179" s="52"/>
-      <c r="Q179" s="52"/>
-      <c r="R179" s="52"/>
-      <c r="S179" s="52"/>
-      <c r="T179" s="52"/>
-      <c r="U179" s="52"/>
-      <c r="V179" s="52"/>
-      <c r="W179" s="52"/>
-      <c r="X179" s="52"/>
-      <c r="Y179" s="52"/>
-      <c r="Z179" s="52"/>
-      <c r="AA179" s="52"/>
-      <c r="AB179" s="52"/>
-      <c r="AC179" s="52"/>
+      <c r="A179" s="52"/>
+      <c r="B179" s="53"/>
+      <c r="C179" s="55"/>
+      <c r="D179" s="55"/>
+      <c r="E179" s="55"/>
+      <c r="F179" s="57"/>
+      <c r="G179" s="57"/>
+      <c r="H179" s="57"/>
+      <c r="I179" s="57"/>
+      <c r="J179" s="57"/>
+      <c r="K179" s="57"/>
+      <c r="L179" s="57"/>
+      <c r="M179" s="57"/>
+      <c r="N179" s="57"/>
+      <c r="O179" s="51"/>
+      <c r="P179" s="51"/>
+      <c r="Q179" s="51"/>
+      <c r="R179" s="51"/>
+      <c r="S179" s="51"/>
+      <c r="T179" s="51"/>
+      <c r="U179" s="51"/>
+      <c r="V179" s="51"/>
+      <c r="W179" s="51"/>
+      <c r="X179" s="51"/>
+      <c r="Y179" s="51"/>
+      <c r="Z179" s="51"/>
+      <c r="AA179" s="51"/>
+      <c r="AB179" s="51"/>
+      <c r="AC179" s="51"/>
     </row>
     <row r="180" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="53"/>
-      <c r="B180" s="54"/>
-      <c r="C180" s="56"/>
-      <c r="D180" s="56"/>
-      <c r="E180" s="56"/>
-      <c r="F180" s="58"/>
-      <c r="G180" s="58"/>
-      <c r="H180" s="58"/>
-      <c r="I180" s="58"/>
-      <c r="J180" s="58"/>
-      <c r="K180" s="58"/>
-      <c r="L180" s="58"/>
-      <c r="M180" s="58"/>
-      <c r="N180" s="58"/>
-      <c r="O180" s="52"/>
-      <c r="P180" s="52"/>
-      <c r="Q180" s="52"/>
-      <c r="R180" s="52"/>
-      <c r="S180" s="52"/>
-      <c r="T180" s="52"/>
-      <c r="U180" s="52"/>
-      <c r="V180" s="52"/>
-      <c r="W180" s="52"/>
-      <c r="X180" s="52"/>
-      <c r="Y180" s="52"/>
-      <c r="Z180" s="52"/>
-      <c r="AA180" s="52"/>
-      <c r="AB180" s="52"/>
-      <c r="AC180" s="52"/>
+      <c r="A180" s="52"/>
+      <c r="B180" s="53"/>
+      <c r="C180" s="55"/>
+      <c r="D180" s="55"/>
+      <c r="E180" s="55"/>
+      <c r="F180" s="57"/>
+      <c r="G180" s="57"/>
+      <c r="H180" s="57"/>
+      <c r="I180" s="57"/>
+      <c r="J180" s="57"/>
+      <c r="K180" s="57"/>
+      <c r="L180" s="57"/>
+      <c r="M180" s="57"/>
+      <c r="N180" s="57"/>
+      <c r="O180" s="51"/>
+      <c r="P180" s="51"/>
+      <c r="Q180" s="51"/>
+      <c r="R180" s="51"/>
+      <c r="S180" s="51"/>
+      <c r="T180" s="51"/>
+      <c r="U180" s="51"/>
+      <c r="V180" s="51"/>
+      <c r="W180" s="51"/>
+      <c r="X180" s="51"/>
+      <c r="Y180" s="51"/>
+      <c r="Z180" s="51"/>
+      <c r="AA180" s="51"/>
+      <c r="AB180" s="51"/>
+      <c r="AC180" s="51"/>
     </row>
     <row r="181" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="53"/>
-      <c r="B181" s="54"/>
-      <c r="C181" s="56"/>
-      <c r="D181" s="56"/>
-      <c r="E181" s="56"/>
-      <c r="F181" s="58"/>
-      <c r="G181" s="58"/>
-      <c r="H181" s="58"/>
-      <c r="I181" s="58"/>
-      <c r="J181" s="58"/>
-      <c r="K181" s="58"/>
-      <c r="L181" s="58"/>
-      <c r="M181" s="58"/>
-      <c r="N181" s="58"/>
-      <c r="O181" s="52"/>
-      <c r="P181" s="52"/>
-      <c r="Q181" s="52"/>
-      <c r="R181" s="52"/>
-      <c r="S181" s="52"/>
-      <c r="T181" s="52"/>
-      <c r="U181" s="52"/>
-      <c r="V181" s="52"/>
-      <c r="W181" s="52"/>
-      <c r="X181" s="52"/>
-      <c r="Y181" s="52"/>
-      <c r="Z181" s="52"/>
-      <c r="AA181" s="52"/>
-      <c r="AB181" s="52"/>
-      <c r="AC181" s="52"/>
+      <c r="A181" s="52"/>
+      <c r="B181" s="53"/>
+      <c r="C181" s="55"/>
+      <c r="D181" s="55"/>
+      <c r="E181" s="55"/>
+      <c r="F181" s="57"/>
+      <c r="G181" s="57"/>
+      <c r="H181" s="57"/>
+      <c r="I181" s="57"/>
+      <c r="J181" s="57"/>
+      <c r="K181" s="57"/>
+      <c r="L181" s="57"/>
+      <c r="M181" s="57"/>
+      <c r="N181" s="57"/>
+      <c r="O181" s="51"/>
+      <c r="P181" s="51"/>
+      <c r="Q181" s="51"/>
+      <c r="R181" s="51"/>
+      <c r="S181" s="51"/>
+      <c r="T181" s="51"/>
+      <c r="U181" s="51"/>
+      <c r="V181" s="51"/>
+      <c r="W181" s="51"/>
+      <c r="X181" s="51"/>
+      <c r="Y181" s="51"/>
+      <c r="Z181" s="51"/>
+      <c r="AA181" s="51"/>
+      <c r="AB181" s="51"/>
+      <c r="AC181" s="51"/>
     </row>
     <row r="182" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="53"/>
-      <c r="B182" s="54"/>
-      <c r="C182" s="56"/>
-      <c r="D182" s="56"/>
-      <c r="E182" s="56"/>
-      <c r="F182" s="58"/>
-      <c r="G182" s="58"/>
-      <c r="H182" s="58"/>
-      <c r="I182" s="58"/>
-      <c r="J182" s="58"/>
-      <c r="K182" s="58"/>
-      <c r="L182" s="58"/>
-      <c r="M182" s="58"/>
-      <c r="N182" s="58"/>
-      <c r="O182" s="52"/>
-      <c r="P182" s="52"/>
-      <c r="Q182" s="52"/>
-      <c r="R182" s="52"/>
-      <c r="S182" s="52"/>
-      <c r="T182" s="52"/>
-      <c r="U182" s="52"/>
-      <c r="V182" s="52"/>
-      <c r="W182" s="52"/>
-      <c r="X182" s="52"/>
-      <c r="Y182" s="52"/>
-      <c r="Z182" s="52"/>
-      <c r="AA182" s="52"/>
-      <c r="AB182" s="52"/>
-      <c r="AC182" s="52"/>
+      <c r="A182" s="52"/>
+      <c r="B182" s="53"/>
+      <c r="C182" s="55"/>
+      <c r="D182" s="55"/>
+      <c r="E182" s="55"/>
+      <c r="F182" s="57"/>
+      <c r="G182" s="57"/>
+      <c r="H182" s="57"/>
+      <c r="I182" s="57"/>
+      <c r="J182" s="57"/>
+      <c r="K182" s="57"/>
+      <c r="L182" s="57"/>
+      <c r="M182" s="57"/>
+      <c r="N182" s="57"/>
+      <c r="O182" s="51"/>
+      <c r="P182" s="51"/>
+      <c r="Q182" s="51"/>
+      <c r="R182" s="51"/>
+      <c r="S182" s="51"/>
+      <c r="T182" s="51"/>
+      <c r="U182" s="51"/>
+      <c r="V182" s="51"/>
+      <c r="W182" s="51"/>
+      <c r="X182" s="51"/>
+      <c r="Y182" s="51"/>
+      <c r="Z182" s="51"/>
+      <c r="AA182" s="51"/>
+      <c r="AB182" s="51"/>
+      <c r="AC182" s="51"/>
     </row>
     <row r="183" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="53"/>
-      <c r="B183" s="54"/>
-      <c r="C183" s="56"/>
-      <c r="D183" s="56"/>
-      <c r="E183" s="56"/>
-      <c r="F183" s="58"/>
-      <c r="G183" s="58"/>
-      <c r="H183" s="58"/>
-      <c r="I183" s="58"/>
-      <c r="J183" s="58"/>
-      <c r="K183" s="58"/>
-      <c r="L183" s="58"/>
-      <c r="M183" s="58"/>
-      <c r="N183" s="58"/>
-      <c r="O183" s="52"/>
-      <c r="P183" s="52"/>
-      <c r="Q183" s="52"/>
-      <c r="R183" s="52"/>
-      <c r="S183" s="52"/>
-      <c r="T183" s="52"/>
-      <c r="U183" s="52"/>
-      <c r="V183" s="52"/>
-      <c r="W183" s="52"/>
-      <c r="X183" s="52"/>
-      <c r="Y183" s="52"/>
-      <c r="Z183" s="52"/>
-      <c r="AA183" s="52"/>
-      <c r="AB183" s="52"/>
-      <c r="AC183" s="52"/>
+      <c r="A183" s="52"/>
+      <c r="B183" s="53"/>
+      <c r="C183" s="55"/>
+      <c r="D183" s="55"/>
+      <c r="E183" s="55"/>
+      <c r="F183" s="57"/>
+      <c r="G183" s="57"/>
+      <c r="H183" s="57"/>
+      <c r="I183" s="57"/>
+      <c r="J183" s="57"/>
+      <c r="K183" s="57"/>
+      <c r="L183" s="57"/>
+      <c r="M183" s="57"/>
+      <c r="N183" s="57"/>
+      <c r="O183" s="51"/>
+      <c r="P183" s="51"/>
+      <c r="Q183" s="51"/>
+      <c r="R183" s="51"/>
+      <c r="S183" s="51"/>
+      <c r="T183" s="51"/>
+      <c r="U183" s="51"/>
+      <c r="V183" s="51"/>
+      <c r="W183" s="51"/>
+      <c r="X183" s="51"/>
+      <c r="Y183" s="51"/>
+      <c r="Z183" s="51"/>
+      <c r="AA183" s="51"/>
+      <c r="AB183" s="51"/>
+      <c r="AC183" s="51"/>
     </row>
     <row r="184" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="53"/>
-      <c r="B184" s="54"/>
-      <c r="C184" s="54"/>
-      <c r="D184" s="54"/>
-      <c r="E184" s="54"/>
-      <c r="F184" s="58"/>
-      <c r="G184" s="58"/>
-      <c r="H184" s="58"/>
-      <c r="I184" s="58"/>
-      <c r="J184" s="58"/>
-      <c r="K184" s="58"/>
-      <c r="L184" s="58"/>
-      <c r="M184" s="58"/>
-      <c r="N184" s="58"/>
-      <c r="O184" s="52"/>
-      <c r="P184" s="52"/>
-      <c r="Q184" s="52"/>
-      <c r="R184" s="52"/>
-      <c r="S184" s="52"/>
-      <c r="T184" s="52"/>
-      <c r="U184" s="52"/>
-      <c r="V184" s="52"/>
-      <c r="W184" s="52"/>
-      <c r="X184" s="52"/>
-      <c r="Y184" s="52"/>
-      <c r="Z184" s="52"/>
-      <c r="AA184" s="52"/>
-      <c r="AB184" s="52"/>
-      <c r="AC184" s="52"/>
+      <c r="A184" s="52"/>
+      <c r="B184" s="53"/>
+      <c r="C184" s="53"/>
+      <c r="D184" s="53"/>
+      <c r="E184" s="53"/>
+      <c r="F184" s="57"/>
+      <c r="G184" s="57"/>
+      <c r="H184" s="57"/>
+      <c r="I184" s="57"/>
+      <c r="J184" s="57"/>
+      <c r="K184" s="57"/>
+      <c r="L184" s="57"/>
+      <c r="M184" s="57"/>
+      <c r="N184" s="57"/>
+      <c r="O184" s="51"/>
+      <c r="P184" s="51"/>
+      <c r="Q184" s="51"/>
+      <c r="R184" s="51"/>
+      <c r="S184" s="51"/>
+      <c r="T184" s="51"/>
+      <c r="U184" s="51"/>
+      <c r="V184" s="51"/>
+      <c r="W184" s="51"/>
+      <c r="X184" s="51"/>
+      <c r="Y184" s="51"/>
+      <c r="Z184" s="51"/>
+      <c r="AA184" s="51"/>
+      <c r="AB184" s="51"/>
+      <c r="AC184" s="51"/>
     </row>
     <row r="185" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="53"/>
-      <c r="B185" s="59"/>
-      <c r="C185" s="59"/>
-      <c r="D185" s="59"/>
-      <c r="E185" s="59"/>
-      <c r="F185" s="58"/>
-      <c r="G185" s="58"/>
-      <c r="H185" s="58"/>
-      <c r="I185" s="58"/>
-      <c r="J185" s="58"/>
-      <c r="K185" s="58"/>
-      <c r="L185" s="58"/>
-      <c r="M185" s="58"/>
-      <c r="N185" s="58"/>
-      <c r="O185" s="52"/>
-      <c r="P185" s="52"/>
-      <c r="Q185" s="52"/>
-      <c r="R185" s="52"/>
-      <c r="S185" s="52"/>
-      <c r="T185" s="52"/>
-      <c r="U185" s="52"/>
-      <c r="V185" s="52"/>
-      <c r="W185" s="52"/>
-      <c r="X185" s="52"/>
-      <c r="Y185" s="52"/>
-      <c r="Z185" s="52"/>
-      <c r="AA185" s="52"/>
-      <c r="AB185" s="52"/>
-      <c r="AC185" s="52"/>
+      <c r="A185" s="52"/>
+      <c r="B185" s="58"/>
+      <c r="C185" s="58"/>
+      <c r="D185" s="58"/>
+      <c r="E185" s="58"/>
+      <c r="F185" s="57"/>
+      <c r="G185" s="57"/>
+      <c r="H185" s="57"/>
+      <c r="I185" s="57"/>
+      <c r="J185" s="57"/>
+      <c r="K185" s="57"/>
+      <c r="L185" s="57"/>
+      <c r="M185" s="57"/>
+      <c r="N185" s="57"/>
+      <c r="O185" s="51"/>
+      <c r="P185" s="51"/>
+      <c r="Q185" s="51"/>
+      <c r="R185" s="51"/>
+      <c r="S185" s="51"/>
+      <c r="T185" s="51"/>
+      <c r="U185" s="51"/>
+      <c r="V185" s="51"/>
+      <c r="W185" s="51"/>
+      <c r="X185" s="51"/>
+      <c r="Y185" s="51"/>
+      <c r="Z185" s="51"/>
+      <c r="AA185" s="51"/>
+      <c r="AB185" s="51"/>
+      <c r="AC185" s="51"/>
     </row>
     <row r="186" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="53"/>
-      <c r="B186" s="59"/>
-      <c r="C186" s="59"/>
-      <c r="D186" s="59"/>
-      <c r="E186" s="59"/>
-      <c r="F186" s="58"/>
-      <c r="G186" s="58"/>
-      <c r="H186" s="58"/>
-      <c r="I186" s="58"/>
-      <c r="J186" s="58"/>
-      <c r="K186" s="58"/>
-      <c r="L186" s="58"/>
-      <c r="M186" s="58"/>
-      <c r="N186" s="58"/>
-      <c r="O186" s="52"/>
-      <c r="P186" s="52"/>
-      <c r="Q186" s="52"/>
-      <c r="R186" s="52"/>
-      <c r="S186" s="52"/>
-      <c r="T186" s="52"/>
-      <c r="U186" s="52"/>
-      <c r="V186" s="52"/>
-      <c r="W186" s="52"/>
-      <c r="X186" s="52"/>
-      <c r="Y186" s="52"/>
-      <c r="Z186" s="52"/>
-      <c r="AA186" s="52"/>
-      <c r="AB186" s="52"/>
-      <c r="AC186" s="52"/>
+      <c r="A186" s="52"/>
+      <c r="B186" s="58"/>
+      <c r="C186" s="58"/>
+      <c r="D186" s="58"/>
+      <c r="E186" s="58"/>
+      <c r="F186" s="57"/>
+      <c r="G186" s="57"/>
+      <c r="H186" s="57"/>
+      <c r="I186" s="57"/>
+      <c r="J186" s="57"/>
+      <c r="K186" s="57"/>
+      <c r="L186" s="57"/>
+      <c r="M186" s="57"/>
+      <c r="N186" s="57"/>
+      <c r="O186" s="51"/>
+      <c r="P186" s="51"/>
+      <c r="Q186" s="51"/>
+      <c r="R186" s="51"/>
+      <c r="S186" s="51"/>
+      <c r="T186" s="51"/>
+      <c r="U186" s="51"/>
+      <c r="V186" s="51"/>
+      <c r="W186" s="51"/>
+      <c r="X186" s="51"/>
+      <c r="Y186" s="51"/>
+      <c r="Z186" s="51"/>
+      <c r="AA186" s="51"/>
+      <c r="AB186" s="51"/>
+      <c r="AC186" s="51"/>
     </row>
     <row r="187" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="53"/>
-      <c r="B187" s="59"/>
-      <c r="C187" s="59"/>
-      <c r="D187" s="59"/>
-      <c r="E187" s="59"/>
-      <c r="F187" s="58"/>
-      <c r="G187" s="58"/>
-      <c r="H187" s="58"/>
-      <c r="I187" s="58"/>
-      <c r="J187" s="58"/>
-      <c r="K187" s="58"/>
-      <c r="L187" s="58"/>
-      <c r="M187" s="58"/>
-      <c r="N187" s="58"/>
-      <c r="O187" s="52"/>
-      <c r="P187" s="52"/>
-      <c r="Q187" s="52"/>
-      <c r="R187" s="52"/>
-      <c r="S187" s="52"/>
-      <c r="T187" s="52"/>
-      <c r="U187" s="52"/>
-      <c r="V187" s="52"/>
-      <c r="W187" s="52"/>
-      <c r="X187" s="52"/>
-      <c r="Y187" s="52"/>
-      <c r="Z187" s="52"/>
-      <c r="AA187" s="52"/>
-      <c r="AB187" s="52"/>
-      <c r="AC187" s="52"/>
+      <c r="A187" s="52"/>
+      <c r="B187" s="58"/>
+      <c r="C187" s="58"/>
+      <c r="D187" s="58"/>
+      <c r="E187" s="58"/>
+      <c r="F187" s="57"/>
+      <c r="G187" s="57"/>
+      <c r="H187" s="57"/>
+      <c r="I187" s="57"/>
+      <c r="J187" s="57"/>
+      <c r="K187" s="57"/>
+      <c r="L187" s="57"/>
+      <c r="M187" s="57"/>
+      <c r="N187" s="57"/>
+      <c r="O187" s="51"/>
+      <c r="P187" s="51"/>
+      <c r="Q187" s="51"/>
+      <c r="R187" s="51"/>
+      <c r="S187" s="51"/>
+      <c r="T187" s="51"/>
+      <c r="U187" s="51"/>
+      <c r="V187" s="51"/>
+      <c r="W187" s="51"/>
+      <c r="X187" s="51"/>
+      <c r="Y187" s="51"/>
+      <c r="Z187" s="51"/>
+      <c r="AA187" s="51"/>
+      <c r="AB187" s="51"/>
+      <c r="AC187" s="51"/>
     </row>
     <row r="188" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="53"/>
-      <c r="B188" s="59"/>
-      <c r="C188" s="59"/>
-      <c r="D188" s="59"/>
-      <c r="E188" s="59"/>
-      <c r="F188" s="58"/>
-      <c r="G188" s="58"/>
-      <c r="H188" s="58"/>
-      <c r="I188" s="58"/>
-      <c r="J188" s="58"/>
-      <c r="K188" s="58"/>
-      <c r="L188" s="58"/>
-      <c r="M188" s="58"/>
-      <c r="N188" s="58"/>
-      <c r="O188" s="52"/>
-      <c r="P188" s="52"/>
-      <c r="Q188" s="52"/>
-      <c r="R188" s="52"/>
-      <c r="S188" s="52"/>
-      <c r="T188" s="52"/>
-      <c r="U188" s="52"/>
-      <c r="V188" s="52"/>
-      <c r="W188" s="52"/>
-      <c r="X188" s="52"/>
-      <c r="Y188" s="52"/>
-      <c r="Z188" s="52"/>
-      <c r="AA188" s="52"/>
-      <c r="AB188" s="52"/>
-      <c r="AC188" s="52"/>
+      <c r="A188" s="52"/>
+      <c r="B188" s="58"/>
+      <c r="C188" s="58"/>
+      <c r="D188" s="58"/>
+      <c r="E188" s="58"/>
+      <c r="F188" s="57"/>
+      <c r="G188" s="57"/>
+      <c r="H188" s="57"/>
+      <c r="I188" s="57"/>
+      <c r="J188" s="57"/>
+      <c r="K188" s="57"/>
+      <c r="L188" s="57"/>
+      <c r="M188" s="57"/>
+      <c r="N188" s="57"/>
+      <c r="O188" s="51"/>
+      <c r="P188" s="51"/>
+      <c r="Q188" s="51"/>
+      <c r="R188" s="51"/>
+      <c r="S188" s="51"/>
+      <c r="T188" s="51"/>
+      <c r="U188" s="51"/>
+      <c r="V188" s="51"/>
+      <c r="W188" s="51"/>
+      <c r="X188" s="51"/>
+      <c r="Y188" s="51"/>
+      <c r="Z188" s="51"/>
+      <c r="AA188" s="51"/>
+      <c r="AB188" s="51"/>
+      <c r="AC188" s="51"/>
     </row>
     <row r="189" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="53"/>
-      <c r="B189" s="59"/>
-      <c r="C189" s="59"/>
-      <c r="D189" s="59"/>
-      <c r="E189" s="59"/>
-      <c r="F189" s="58"/>
-      <c r="G189" s="58"/>
-      <c r="H189" s="58"/>
-      <c r="I189" s="58"/>
-      <c r="J189" s="58"/>
-      <c r="K189" s="58"/>
-      <c r="L189" s="58"/>
-      <c r="M189" s="58"/>
-      <c r="N189" s="58"/>
-      <c r="O189" s="52"/>
-      <c r="P189" s="52"/>
-      <c r="Q189" s="52"/>
-      <c r="R189" s="52"/>
-      <c r="S189" s="52"/>
-      <c r="T189" s="52"/>
-      <c r="U189" s="52"/>
-      <c r="V189" s="52"/>
-      <c r="W189" s="52"/>
-      <c r="X189" s="52"/>
-      <c r="Y189" s="52"/>
-      <c r="Z189" s="52"/>
-      <c r="AA189" s="52"/>
-      <c r="AB189" s="52"/>
-      <c r="AC189" s="52"/>
+      <c r="A189" s="52"/>
+      <c r="B189" s="58"/>
+      <c r="C189" s="58"/>
+      <c r="D189" s="58"/>
+      <c r="E189" s="58"/>
+      <c r="F189" s="57"/>
+      <c r="G189" s="57"/>
+      <c r="H189" s="57"/>
+      <c r="I189" s="57"/>
+      <c r="J189" s="57"/>
+      <c r="K189" s="57"/>
+      <c r="L189" s="57"/>
+      <c r="M189" s="57"/>
+      <c r="N189" s="57"/>
+      <c r="O189" s="51"/>
+      <c r="P189" s="51"/>
+      <c r="Q189" s="51"/>
+      <c r="R189" s="51"/>
+      <c r="S189" s="51"/>
+      <c r="T189" s="51"/>
+      <c r="U189" s="51"/>
+      <c r="V189" s="51"/>
+      <c r="W189" s="51"/>
+      <c r="X189" s="51"/>
+      <c r="Y189" s="51"/>
+      <c r="Z189" s="51"/>
+      <c r="AA189" s="51"/>
+      <c r="AB189" s="51"/>
+      <c r="AC189" s="51"/>
     </row>
     <row r="190" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="53"/>
-      <c r="B190" s="59"/>
-      <c r="C190" s="59"/>
-      <c r="D190" s="59"/>
-      <c r="E190" s="59"/>
-      <c r="F190" s="58"/>
-      <c r="G190" s="58"/>
-      <c r="H190" s="58"/>
-      <c r="I190" s="58"/>
-      <c r="J190" s="58"/>
-      <c r="K190" s="58"/>
-      <c r="L190" s="58"/>
-      <c r="M190" s="58"/>
-      <c r="N190" s="58"/>
-      <c r="O190" s="52"/>
-      <c r="P190" s="52"/>
-      <c r="Q190" s="52"/>
-      <c r="R190" s="52"/>
-      <c r="S190" s="52"/>
-      <c r="T190" s="52"/>
-      <c r="U190" s="52"/>
-      <c r="V190" s="52"/>
-      <c r="W190" s="52"/>
-      <c r="X190" s="52"/>
-      <c r="Y190" s="52"/>
-      <c r="Z190" s="52"/>
-      <c r="AA190" s="52"/>
-      <c r="AB190" s="52"/>
-      <c r="AC190" s="52"/>
+      <c r="A190" s="52"/>
+      <c r="B190" s="58"/>
+      <c r="C190" s="58"/>
+      <c r="D190" s="58"/>
+      <c r="E190" s="58"/>
+      <c r="F190" s="57"/>
+      <c r="G190" s="57"/>
+      <c r="H190" s="57"/>
+      <c r="I190" s="57"/>
+      <c r="J190" s="57"/>
+      <c r="K190" s="57"/>
+      <c r="L190" s="57"/>
+      <c r="M190" s="57"/>
+      <c r="N190" s="57"/>
+      <c r="O190" s="51"/>
+      <c r="P190" s="51"/>
+      <c r="Q190" s="51"/>
+      <c r="R190" s="51"/>
+      <c r="S190" s="51"/>
+      <c r="T190" s="51"/>
+      <c r="U190" s="51"/>
+      <c r="V190" s="51"/>
+      <c r="W190" s="51"/>
+      <c r="X190" s="51"/>
+      <c r="Y190" s="51"/>
+      <c r="Z190" s="51"/>
+      <c r="AA190" s="51"/>
+      <c r="AB190" s="51"/>
+      <c r="AC190" s="51"/>
     </row>
     <row r="191" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="53"/>
-      <c r="B191" s="59"/>
-      <c r="C191" s="59"/>
-      <c r="D191" s="59"/>
-      <c r="E191" s="59"/>
-      <c r="F191" s="52"/>
-      <c r="G191" s="52"/>
-      <c r="H191" s="52"/>
-      <c r="I191" s="52"/>
-      <c r="J191" s="52"/>
-      <c r="K191" s="52"/>
-      <c r="L191" s="52"/>
-      <c r="M191" s="52"/>
-      <c r="N191" s="52"/>
-      <c r="O191" s="52"/>
-      <c r="P191" s="52"/>
-      <c r="Q191" s="52"/>
-      <c r="R191" s="52"/>
-      <c r="S191" s="52"/>
-      <c r="T191" s="52"/>
-      <c r="U191" s="52"/>
-      <c r="V191" s="52"/>
-      <c r="W191" s="52"/>
-      <c r="X191" s="52"/>
-      <c r="Y191" s="52"/>
-      <c r="Z191" s="52"/>
-      <c r="AA191" s="52"/>
-      <c r="AB191" s="52"/>
-      <c r="AC191" s="52"/>
+      <c r="A191" s="52"/>
+      <c r="B191" s="58"/>
+      <c r="C191" s="58"/>
+      <c r="D191" s="58"/>
+      <c r="E191" s="58"/>
+      <c r="F191" s="51"/>
+      <c r="G191" s="51"/>
+      <c r="H191" s="51"/>
+      <c r="I191" s="51"/>
+      <c r="J191" s="51"/>
+      <c r="K191" s="51"/>
+      <c r="L191" s="51"/>
+      <c r="M191" s="51"/>
+      <c r="N191" s="51"/>
+      <c r="O191" s="51"/>
+      <c r="P191" s="51"/>
+      <c r="Q191" s="51"/>
+      <c r="R191" s="51"/>
+      <c r="S191" s="51"/>
+      <c r="T191" s="51"/>
+      <c r="U191" s="51"/>
+      <c r="V191" s="51"/>
+      <c r="W191" s="51"/>
+      <c r="X191" s="51"/>
+      <c r="Y191" s="51"/>
+      <c r="Z191" s="51"/>
+      <c r="AA191" s="51"/>
+      <c r="AB191" s="51"/>
+      <c r="AC191" s="51"/>
     </row>
     <row r="192" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="53"/>
-      <c r="B192" s="59"/>
-      <c r="C192" s="59"/>
-      <c r="D192" s="59"/>
-      <c r="E192" s="59"/>
-      <c r="F192" s="52"/>
-      <c r="G192" s="52"/>
-      <c r="H192" s="52"/>
-      <c r="I192" s="52"/>
-      <c r="J192" s="52"/>
-      <c r="K192" s="52"/>
-      <c r="L192" s="52"/>
-      <c r="M192" s="52"/>
-      <c r="N192" s="52"/>
-      <c r="O192" s="52"/>
-      <c r="P192" s="52"/>
-      <c r="Q192" s="52"/>
-      <c r="R192" s="52"/>
-      <c r="S192" s="52"/>
-      <c r="T192" s="52"/>
-      <c r="U192" s="52"/>
-      <c r="V192" s="52"/>
-      <c r="W192" s="52"/>
-      <c r="X192" s="52"/>
-      <c r="Y192" s="52"/>
-      <c r="Z192" s="52"/>
-      <c r="AA192" s="52"/>
-      <c r="AB192" s="52"/>
-      <c r="AC192" s="52"/>
+      <c r="A192" s="52"/>
+      <c r="B192" s="58"/>
+      <c r="C192" s="58"/>
+      <c r="D192" s="58"/>
+      <c r="E192" s="58"/>
+      <c r="F192" s="51"/>
+      <c r="G192" s="51"/>
+      <c r="H192" s="51"/>
+      <c r="I192" s="51"/>
+      <c r="J192" s="51"/>
+      <c r="K192" s="51"/>
+      <c r="L192" s="51"/>
+      <c r="M192" s="51"/>
+      <c r="N192" s="51"/>
+      <c r="O192" s="51"/>
+      <c r="P192" s="51"/>
+      <c r="Q192" s="51"/>
+      <c r="R192" s="51"/>
+      <c r="S192" s="51"/>
+      <c r="T192" s="51"/>
+      <c r="U192" s="51"/>
+      <c r="V192" s="51"/>
+      <c r="W192" s="51"/>
+      <c r="X192" s="51"/>
+      <c r="Y192" s="51"/>
+      <c r="Z192" s="51"/>
+      <c r="AA192" s="51"/>
+      <c r="AB192" s="51"/>
+      <c r="AC192" s="51"/>
     </row>
     <row r="193" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="47"/>
-      <c r="B193" s="30"/>
+      <c r="A193" s="46"/>
+      <c r="B193" s="29"/>
       <c r="C193" s="73"/>
       <c r="D193" s="73"/>
       <c r="E193" s="73"/>
@@ -21926,36 +21921,36 @@
   <dimension ref="M10:M17"/>
   <sheetFormatPr defaultRowHeight="22.1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="41"/>
+    <col min="1" max="16384" width="9.140625" style="40"/>
   </cols>
   <sheetData>
     <row r="10" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M10" s="44" t="s">
+      <c r="M10" s="43" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="11" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M11" s="41" t="s">
+      <c r="M11" s="40" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="12" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M12" s="41" t="s">
+      <c r="M12" s="40" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="13" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M13" s="41" t="s">
+      <c r="M13" s="40" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="14" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M14" s="41" t="s">
+      <c r="M14" s="40" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="17" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M17" s="44"/>
+      <c r="M17" s="43"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21969,24 +21964,24 @@
   <dimension ref="B1:M17"/>
   <sheetFormatPr defaultRowHeight="22.1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="41"/>
+    <col min="1" max="16384" width="9.140625" style="40"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="40" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="M10" s="44"/>
+      <c r="M10" s="43"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="40" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="17" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M17" s="44"/>
+      <c r="M17" s="43"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
